--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131238351</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131239702</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>131239654</v>
       </c>
       <c r="B4" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131239936</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131238307</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131238351</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131239702</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>131239654</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131239936</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131238307</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131238351</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131239702</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>131239654</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131239936</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131238307</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131238351</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131239702</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>131239654</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131239936</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131238307</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131238351</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131239702</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>131239654</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131239936</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131238307</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1217,103 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131599422</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79258</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>464210</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6758193</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1970-01-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131238351</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131239702</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>131239654</v>
       </c>
       <c r="B4" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131239936</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131238307</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131599422</v>
+        <v>131587086</v>
       </c>
       <c r="B7" t="n">
-        <v>79258</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,34 +1230,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464210</v>
+        <v>464056</v>
       </c>
       <c r="R7" t="n">
-        <v>6758193</v>
+        <v>6758091</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,12 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,6 +1318,5702 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131592130</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>464070</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6758175</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131589374</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>464029</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6758112</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131605369</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>464271</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6757950</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131604477</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>464463</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6758106</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131587093</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>464056</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6758091</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131601638</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>464298</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6758264</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 bild gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131593794</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>464022</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6758156</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131595645</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83240</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>464112</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6758222</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5 st Miljöbilder bland annat på en bäck</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131586783</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>464041</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6758056</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131604098</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>464410</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6758165</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>4 bilder, tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131594186</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>464035</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6758187</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131600419</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>464251</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6758281</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1 bild, stubbe</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131591075</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>464053</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6758144</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131601488</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>464297</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6758284</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131593946</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>464018</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6758172</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131602481</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>464282</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6758242</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet. Bild på vedsvamp i samma område</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131600576</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>464283</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6758311</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131586743</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>464052</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6758047</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131604893</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>464457</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6758015</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131604566</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>464472</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6758091</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131604670</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>464483</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6758032</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131603524</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>464384</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6758179</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131604756</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57086</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>464541</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6758017</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131600797</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99033</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>464314</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6758387</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131591546</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>464053</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6758144</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131597701</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>464192</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6758156</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131594493</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>464034</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6758248</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2 bilder, bäck</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131586714</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57086</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>464060</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6758044</v>
+      </c>
+      <c r="S35" t="n">
+        <v>50</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131600974</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>464341</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6758413</v>
+      </c>
+      <c r="S36" t="n">
+        <v>50</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131586494</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>464066</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6757982</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131586581</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>464051</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6758034</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131603322</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>464265</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6758140</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131600594</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>464296</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6758304</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131599422</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>464210</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6758193</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131597848</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>464205</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6758160</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131600551</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>464263</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6758298</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131603307</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>464265</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6758140</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131600442</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79850</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>464251</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6758281</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131603971</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>464384</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6758179</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131586790</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>464046</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6758049</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131599244</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>464210</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6758193</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131594252</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57086</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>464049</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6758189</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131586702</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>464051</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6758034</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131605450</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>464189</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6757919</v>
+      </c>
+      <c r="S51" t="n">
+        <v>50</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131601417</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>464317</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6758312</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131604599</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>464472</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6758076</v>
+      </c>
+      <c r="S53" t="n">
+        <v>50</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131605027</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>464394</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6758039</v>
+      </c>
+      <c r="S54" t="n">
+        <v>50</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131586572</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>464052</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6758021</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131605468</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>464189</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6757919</v>
+      </c>
+      <c r="S56" t="n">
+        <v>50</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131596208</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>464135</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6758234</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131595863</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>464112</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6758222</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131587027</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57086</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>464056</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6758091</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131586922</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>464054</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6758066</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131601410</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>464317</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6758312</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>1 bild, ringhack och garn</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131604358</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>464439</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6758140</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131602531</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>464282</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6758242</v>
+      </c>
+      <c r="S63" t="n">
+        <v>50</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131239936</v>
+        <v>131238307</v>
       </c>
       <c r="B5" t="n">
         <v>57898</v>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464233</v>
+        <v>464077</v>
       </c>
       <c r="R5" t="n">
-        <v>6757895</v>
+        <v>6758050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack samt miljöbilder för området. Källa på en av bilderna.</t>
+          <t>Ringhack samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131238307</v>
+        <v>131239936</v>
       </c>
       <c r="B6" t="n">
         <v>57898</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464077</v>
+        <v>464233</v>
       </c>
       <c r="R6" t="n">
-        <v>6758050</v>
+        <v>6757895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack samt miljöbilder för området</t>
+          <t>Ringhack samt miljöbilder för området. Källa på en av bilderna.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131587086</v>
+        <v>131605369</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,42 +1230,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464056</v>
+        <v>464271</v>
       </c>
       <c r="R7" t="n">
-        <v>6758091</v>
+        <v>6757950</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,12 +1295,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1321,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131592130</v>
+        <v>131604477</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,34 +1336,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464070</v>
+        <v>464463</v>
       </c>
       <c r="R8" t="n">
-        <v>6758175</v>
+        <v>6758106</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,6 +1401,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131589374</v>
+        <v>131592130</v>
       </c>
       <c r="B9" t="n">
         <v>79260</v>
@@ -1453,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464029</v>
+        <v>464070</v>
       </c>
       <c r="R9" t="n">
-        <v>6758112</v>
+        <v>6758175</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1529,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131605369</v>
+        <v>131589374</v>
       </c>
       <c r="B10" t="n">
         <v>79260</v>
@@ -1544,22 +1558,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464271</v>
+        <v>464029</v>
       </c>
       <c r="R10" t="n">
-        <v>6757950</v>
+        <v>6758112</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1591,18 +1602,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1621,7 +1626,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131604477</v>
+        <v>131587086</v>
       </c>
       <c r="B11" t="n">
         <v>57898</v>
@@ -1661,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464463</v>
+        <v>464056</v>
       </c>
       <c r="R11" t="n">
-        <v>6758106</v>
+        <v>6758091</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,11 +1702,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131601638</v>
+        <v>131593794</v>
       </c>
       <c r="B13" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,39 +1836,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464298</v>
+        <v>464022</v>
       </c>
       <c r="R13" t="n">
-        <v>6758264</v>
+        <v>6758156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1900,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1 bild gran</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131593794</v>
+        <v>131595645</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>83240</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,34 +1938,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464022</v>
+        <v>464112</v>
       </c>
       <c r="R14" t="n">
-        <v>6758156</v>
+        <v>6758222</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2005,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>5 st Miljöbilder bland annat på en bäck</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,6 +2014,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2034,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131595645</v>
+        <v>131586783</v>
       </c>
       <c r="B15" t="n">
-        <v>83240</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,26 +2044,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2072,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464112</v>
+        <v>464041</v>
       </c>
       <c r="R15" t="n">
-        <v>6758222</v>
+        <v>6758056</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,18 +2114,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>5 st Miljöbilder bland annat på en bäck</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2140,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131586783</v>
+        <v>131601638</v>
       </c>
       <c r="B16" t="n">
-        <v>57898</v>
+        <v>57895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,16 +2149,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2169,24 +2167,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464041</v>
+        <v>464298</v>
       </c>
       <c r="R16" t="n">
-        <v>6758056</v>
+        <v>6758264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,6 +2214,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3362,38 +3362,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131604670</v>
+        <v>131600797</v>
       </c>
       <c r="B28" t="n">
-        <v>57898</v>
+        <v>99033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>95</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3402,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464483</v>
+        <v>464314</v>
       </c>
       <c r="R28" t="n">
-        <v>6758032</v>
+        <v>6758387</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,11 +3437,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3469,10 +3463,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131603524</v>
+        <v>131591546</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,39 +3474,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464384</v>
+        <v>464053</v>
       </c>
       <c r="R29" t="n">
-        <v>6758179</v>
+        <v>6758144</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,11 +3534,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3576,50 +3560,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131604756</v>
+        <v>131597701</v>
       </c>
       <c r="B30" t="n">
-        <v>57086</v>
+        <v>79260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464541</v>
+        <v>464192</v>
       </c>
       <c r="R30" t="n">
-        <v>6758017</v>
+        <v>6758156</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3678,49 +3657,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131600797</v>
+        <v>131594493</v>
       </c>
       <c r="B31" t="n">
-        <v>99033</v>
+        <v>79260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464314</v>
+        <v>464034</v>
       </c>
       <c r="R31" t="n">
-        <v>6758387</v>
+        <v>6758248</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,12 +3733,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2 bilder, bäck</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3779,48 +3763,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131591546</v>
+        <v>131586714</v>
       </c>
       <c r="B32" t="n">
-        <v>79260</v>
+        <v>57086</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464053</v>
+        <v>464060</v>
       </c>
       <c r="R32" t="n">
-        <v>6758144</v>
+        <v>6758044</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3876,45 +3865,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131597701</v>
+        <v>131604756</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>57086</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464192</v>
+        <v>464541</v>
       </c>
       <c r="R33" t="n">
-        <v>6758156</v>
+        <v>6758017</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131594493</v>
+        <v>131604670</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3984,37 +3978,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464034</v>
+        <v>464483</v>
       </c>
       <c r="R34" t="n">
-        <v>6758248</v>
+        <v>6758032</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4051,7 +4047,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>2 bilder, bäck</t>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4060,7 +4056,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4079,38 +4074,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131586714</v>
+        <v>131603524</v>
       </c>
       <c r="B35" t="n">
-        <v>57086</v>
+        <v>57898</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4119,13 +4114,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464060</v>
+        <v>464384</v>
       </c>
       <c r="R35" t="n">
-        <v>6758044</v>
+        <v>6758179</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4155,6 +4150,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,7 +4283,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131586494</v>
+        <v>131603322</v>
       </c>
       <c r="B37" t="n">
         <v>79260</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464066</v>
+        <v>464265</v>
       </c>
       <c r="R37" t="n">
-        <v>6757982</v>
+        <v>6758140</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131586581</v>
+        <v>131600594</v>
       </c>
       <c r="B38" t="n">
         <v>79260</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464051</v>
+        <v>464296</v>
       </c>
       <c r="R38" t="n">
-        <v>6758034</v>
+        <v>6758304</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,6 +4451,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4477,7 +4482,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131603322</v>
+        <v>131586494</v>
       </c>
       <c r="B39" t="n">
         <v>79260</v>
@@ -4512,10 +4517,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464265</v>
+        <v>464066</v>
       </c>
       <c r="R39" t="n">
-        <v>6758140</v>
+        <v>6757982</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4574,7 +4579,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131600594</v>
+        <v>131586581</v>
       </c>
       <c r="B40" t="n">
         <v>79260</v>
@@ -4609,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464296</v>
+        <v>464051</v>
       </c>
       <c r="R40" t="n">
-        <v>6758304</v>
+        <v>6758034</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4645,11 +4650,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4870,10 +4870,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131600551</v>
+        <v>131603971</v>
       </c>
       <c r="B43" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4881,39 +4881,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464263</v>
+        <v>464384</v>
       </c>
       <c r="R43" t="n">
-        <v>6758298</v>
+        <v>6758179</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4946,6 +4941,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4972,10 +4972,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131603307</v>
+        <v>131600442</v>
       </c>
       <c r="B44" t="n">
-        <v>57898</v>
+        <v>79850</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4983,39 +4983,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464265</v>
+        <v>464251</v>
       </c>
       <c r="R44" t="n">
-        <v>6758140</v>
+        <v>6758281</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,11 +5043,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5079,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131600442</v>
+        <v>131600551</v>
       </c>
       <c r="B45" t="n">
-        <v>79850</v>
+        <v>57898</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5090,34 +5080,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464251</v>
+        <v>464263</v>
       </c>
       <c r="R45" t="n">
-        <v>6758281</v>
+        <v>6758298</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5176,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131603971</v>
+        <v>131603307</v>
       </c>
       <c r="B46" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5187,34 +5182,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464384</v>
+        <v>464265</v>
       </c>
       <c r="R46" t="n">
-        <v>6758179</v>
+        <v>6758140</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131238307</v>
+        <v>131239936</v>
       </c>
       <c r="B5" t="n">
         <v>57898</v>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464077</v>
+        <v>464233</v>
       </c>
       <c r="R5" t="n">
-        <v>6758050</v>
+        <v>6757895</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack samt miljöbilder för området</t>
+          <t>Ringhack samt miljöbilder för området. Källa på en av bilderna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131239936</v>
+        <v>131238307</v>
       </c>
       <c r="B6" t="n">
         <v>57898</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464233</v>
+        <v>464077</v>
       </c>
       <c r="R6" t="n">
-        <v>6757895</v>
+        <v>6758050</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack samt miljöbilder för området. Källa på en av bilderna.</t>
+          <t>Ringhack samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131605369</v>
+        <v>131592130</v>
       </c>
       <c r="B7" t="n">
         <v>79260</v>
@@ -1248,22 +1248,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464271</v>
+        <v>464070</v>
       </c>
       <c r="R7" t="n">
-        <v>6757950</v>
+        <v>6758175</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,18 +1292,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131604477</v>
+        <v>131589374</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1336,39 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464463</v>
+        <v>464029</v>
       </c>
       <c r="R8" t="n">
-        <v>6758106</v>
+        <v>6758112</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,11 +1387,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131592130</v>
+        <v>131587086</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,34 +1424,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464070</v>
+        <v>464056</v>
       </c>
       <c r="R9" t="n">
-        <v>6758175</v>
+        <v>6758091</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131589374</v>
+        <v>131604477</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,34 +1526,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464029</v>
+        <v>464463</v>
       </c>
       <c r="R10" t="n">
-        <v>6758112</v>
+        <v>6758106</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,6 +1591,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131587086</v>
+        <v>131605369</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,42 +1633,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464056</v>
+        <v>464271</v>
       </c>
       <c r="R11" t="n">
-        <v>6758091</v>
+        <v>6757950</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,12 +1698,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131604098</v>
+        <v>131594186</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,39 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464410</v>
+        <v>464035</v>
       </c>
       <c r="R17" t="n">
-        <v>6758165</v>
+        <v>6758187</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131594186</v>
+        <v>131604098</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,34 +2358,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464035</v>
+        <v>464410</v>
       </c>
       <c r="R18" t="n">
-        <v>6758187</v>
+        <v>6758165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,42 +2567,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R20" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,6 +2627,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,37 +2669,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R21" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,7 +3056,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131586743</v>
+        <v>131604893</v>
       </c>
       <c r="B25" t="n">
         <v>79260</v>
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464052</v>
+        <v>464457</v>
       </c>
       <c r="R25" t="n">
-        <v>6758047</v>
+        <v>6758015</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3127,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3153,7 +3158,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131604893</v>
+        <v>131586743</v>
       </c>
       <c r="B26" t="n">
         <v>79260</v>
@@ -3188,13 +3193,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464457</v>
+        <v>464052</v>
       </c>
       <c r="R26" t="n">
-        <v>6758015</v>
+        <v>6758047</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3224,11 +3229,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3362,37 +3362,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131600797</v>
+        <v>131586714</v>
       </c>
       <c r="B28" t="n">
-        <v>99033</v>
+        <v>57086</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>95</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3401,13 +3402,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464314</v>
+        <v>464060</v>
       </c>
       <c r="R28" t="n">
-        <v>6758387</v>
+        <v>6758044</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3763,7 +3764,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131586714</v>
+        <v>131604756</v>
       </c>
       <c r="B32" t="n">
         <v>57086</v>
@@ -3803,13 +3804,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464060</v>
+        <v>464541</v>
       </c>
       <c r="R32" t="n">
-        <v>6758044</v>
+        <v>6758017</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3865,38 +3866,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131604756</v>
+        <v>131603524</v>
       </c>
       <c r="B33" t="n">
-        <v>57086</v>
+        <v>57898</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3905,10 +3906,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464541</v>
+        <v>464384</v>
       </c>
       <c r="R33" t="n">
-        <v>6758017</v>
+        <v>6758179</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,6 +3942,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,38 +4080,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131603524</v>
+        <v>131600797</v>
       </c>
       <c r="B35" t="n">
-        <v>57898</v>
+        <v>99033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>95</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464384</v>
+        <v>464314</v>
       </c>
       <c r="R35" t="n">
-        <v>6758179</v>
+        <v>6758387</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,7 +4283,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131603322</v>
+        <v>131586494</v>
       </c>
       <c r="B37" t="n">
         <v>79260</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464265</v>
+        <v>464066</v>
       </c>
       <c r="R37" t="n">
-        <v>6758140</v>
+        <v>6757982</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131600594</v>
+        <v>131586581</v>
       </c>
       <c r="B38" t="n">
         <v>79260</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464296</v>
+        <v>464051</v>
       </c>
       <c r="R38" t="n">
-        <v>6758304</v>
+        <v>6758034</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,11 +4451,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4482,7 +4477,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131586494</v>
+        <v>131603322</v>
       </c>
       <c r="B39" t="n">
         <v>79260</v>
@@ -4517,10 +4512,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464066</v>
+        <v>464265</v>
       </c>
       <c r="R39" t="n">
-        <v>6757982</v>
+        <v>6758140</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4579,7 +4574,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131586581</v>
+        <v>131600594</v>
       </c>
       <c r="B40" t="n">
         <v>79260</v>
@@ -4614,10 +4609,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464051</v>
+        <v>464296</v>
       </c>
       <c r="R40" t="n">
-        <v>6758034</v>
+        <v>6758304</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4650,6 +4645,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4972,10 +4972,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131600442</v>
+        <v>131600551</v>
       </c>
       <c r="B44" t="n">
-        <v>79850</v>
+        <v>57898</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4983,34 +4983,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464251</v>
+        <v>464263</v>
       </c>
       <c r="R44" t="n">
-        <v>6758281</v>
+        <v>6758298</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5069,7 +5074,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131600551</v>
+        <v>131603307</v>
       </c>
       <c r="B45" t="n">
         <v>57898</v>
@@ -5109,10 +5114,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464263</v>
+        <v>464265</v>
       </c>
       <c r="R45" t="n">
-        <v>6758298</v>
+        <v>6758140</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5145,6 +5150,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,10 +5181,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131603307</v>
+        <v>131600442</v>
       </c>
       <c r="B46" t="n">
-        <v>57898</v>
+        <v>79850</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5182,39 +5192,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464265</v>
+        <v>464251</v>
       </c>
       <c r="R46" t="n">
-        <v>6758140</v>
+        <v>6758281</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5247,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6096,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131586572</v>
+        <v>131605468</v>
       </c>
       <c r="B55" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6107,37 +6107,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464052</v>
+        <v>464189</v>
       </c>
       <c r="R55" t="n">
-        <v>6758021</v>
+        <v>6757919</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6193,10 +6201,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131605468</v>
+        <v>131586572</v>
       </c>
       <c r="B56" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6204,45 +6212,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464189</v>
+        <v>464052</v>
       </c>
       <c r="R56" t="n">
-        <v>6757919</v>
+        <v>6758021</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6298,10 +6298,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131596208</v>
+        <v>131586922</v>
       </c>
       <c r="B57" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6309,34 +6309,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464135</v>
+        <v>464054</v>
       </c>
       <c r="R57" t="n">
-        <v>6758234</v>
+        <v>6758066</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6395,45 +6400,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131595863</v>
+        <v>131587027</v>
       </c>
       <c r="B58" t="n">
-        <v>79260</v>
+        <v>57086</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464112</v>
+        <v>464056</v>
       </c>
       <c r="R58" t="n">
-        <v>6758222</v>
+        <v>6758091</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6466,6 +6476,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6492,38 +6507,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131587027</v>
+        <v>131601410</v>
       </c>
       <c r="B59" t="n">
-        <v>57086</v>
+        <v>57898</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6532,10 +6547,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464056</v>
+        <v>464317</v>
       </c>
       <c r="R59" t="n">
-        <v>6758091</v>
+        <v>6758312</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6572,7 +6587,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Spillning under tjädertall</t>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6599,7 +6614,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131586922</v>
+        <v>131604358</v>
       </c>
       <c r="B60" t="n">
         <v>57898</v>
@@ -6630,7 +6645,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6639,10 +6654,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464054</v>
+        <v>464439</v>
       </c>
       <c r="R60" t="n">
-        <v>6758066</v>
+        <v>6758140</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6675,6 +6690,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6701,10 +6721,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131601410</v>
+        <v>131596208</v>
       </c>
       <c r="B61" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6712,39 +6732,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464317</v>
+        <v>464135</v>
       </c>
       <c r="R61" t="n">
-        <v>6758312</v>
+        <v>6758234</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6777,11 +6792,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6808,10 +6818,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131604358</v>
+        <v>131595863</v>
       </c>
       <c r="B62" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6819,39 +6829,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464439</v>
+        <v>464112</v>
       </c>
       <c r="R62" t="n">
-        <v>6758140</v>
+        <v>6758222</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6884,11 +6889,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131604477</v>
+        <v>131605369</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,42 +1526,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464463</v>
+        <v>464271</v>
       </c>
       <c r="R10" t="n">
-        <v>6758106</v>
+        <v>6757950</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1595,7 +1593,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,6 +1602,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1622,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131605369</v>
+        <v>131604477</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,40 +1632,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464271</v>
+        <v>464463</v>
       </c>
       <c r="R11" t="n">
-        <v>6757950</v>
+        <v>6758106</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,7 +1701,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,7 +1710,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,37 +2567,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R20" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2627,11 +2632,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B21" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,42 +2669,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R21" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2734,6 +2729,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131604893</v>
+        <v>131604566</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,37 +3067,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464457</v>
+        <v>464472</v>
       </c>
       <c r="R25" t="n">
-        <v>6758015</v>
+        <v>6758091</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3131,7 +3136,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3158,7 +3163,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131586743</v>
+        <v>131604893</v>
       </c>
       <c r="B26" t="n">
         <v>79260</v>
@@ -3193,13 +3198,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464052</v>
+        <v>464457</v>
       </c>
       <c r="R26" t="n">
-        <v>6758047</v>
+        <v>6758015</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3229,6 +3234,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3255,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131604566</v>
+        <v>131586743</v>
       </c>
       <c r="B27" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3266,39 +3276,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464472</v>
+        <v>464052</v>
       </c>
       <c r="R27" t="n">
-        <v>6758091</v>
+        <v>6758047</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3331,11 +3336,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3362,7 +3362,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131586714</v>
+        <v>131604756</v>
       </c>
       <c r="B28" t="n">
         <v>57086</v>
@@ -3402,13 +3402,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464060</v>
+        <v>464541</v>
       </c>
       <c r="R28" t="n">
-        <v>6758044</v>
+        <v>6758017</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131591546</v>
+        <v>131603524</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,34 +3475,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464053</v>
+        <v>464384</v>
       </c>
       <c r="R29" t="n">
-        <v>6758144</v>
+        <v>6758179</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,6 +3540,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3561,10 +3571,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131597701</v>
+        <v>131604670</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3572,34 +3582,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464192</v>
+        <v>464483</v>
       </c>
       <c r="R30" t="n">
-        <v>6758156</v>
+        <v>6758032</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,6 +3647,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3658,48 +3678,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131594493</v>
+        <v>131600797</v>
       </c>
       <c r="B31" t="n">
-        <v>79260</v>
+        <v>99033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464034</v>
+        <v>464314</v>
       </c>
       <c r="R31" t="n">
-        <v>6758248</v>
+        <v>6758387</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3734,18 +3755,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3764,50 +3779,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131604756</v>
+        <v>131591546</v>
       </c>
       <c r="B32" t="n">
-        <v>57086</v>
+        <v>79260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464541</v>
+        <v>464053</v>
       </c>
       <c r="R32" t="n">
-        <v>6758017</v>
+        <v>6758144</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3866,10 +3876,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131603524</v>
+        <v>131597701</v>
       </c>
       <c r="B33" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,39 +3887,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464384</v>
+        <v>464192</v>
       </c>
       <c r="R33" t="n">
-        <v>6758179</v>
+        <v>6758156</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,11 +3947,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3973,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131604670</v>
+        <v>131594493</v>
       </c>
       <c r="B34" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3984,39 +3984,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464483</v>
+        <v>464034</v>
       </c>
       <c r="R34" t="n">
-        <v>6758032</v>
+        <v>6758248</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,7 +4051,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt med ringhack</t>
+          <t>2 bilder, bäck</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4062,6 +4060,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4080,37 +4079,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131600797</v>
+        <v>131586714</v>
       </c>
       <c r="B35" t="n">
-        <v>99033</v>
+        <v>57086</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>95</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4119,13 +4119,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464314</v>
+        <v>464060</v>
       </c>
       <c r="R35" t="n">
-        <v>6758387</v>
+        <v>6758044</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131586494</v>
+        <v>131603322</v>
       </c>
       <c r="B37" t="n">
         <v>79260</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464066</v>
+        <v>464265</v>
       </c>
       <c r="R37" t="n">
-        <v>6757982</v>
+        <v>6758140</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131586581</v>
+        <v>131600594</v>
       </c>
       <c r="B38" t="n">
         <v>79260</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464051</v>
+        <v>464296</v>
       </c>
       <c r="R38" t="n">
-        <v>6758034</v>
+        <v>6758304</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,6 +4451,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4477,7 +4482,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131603322</v>
+        <v>131586494</v>
       </c>
       <c r="B39" t="n">
         <v>79260</v>
@@ -4512,10 +4517,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464265</v>
+        <v>464066</v>
       </c>
       <c r="R39" t="n">
-        <v>6758140</v>
+        <v>6757982</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4574,7 +4579,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131600594</v>
+        <v>131586581</v>
       </c>
       <c r="B40" t="n">
         <v>79260</v>
@@ -4609,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464296</v>
+        <v>464051</v>
       </c>
       <c r="R40" t="n">
-        <v>6758304</v>
+        <v>6758034</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4645,11 +4650,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -7015,6 +7015,116 @@
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>131603229</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>464268</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6758184</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>2 bilzer. 3 och 3,5 meter upp,  4 och 5 cm i diameter</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131592130</v>
+        <v>131587086</v>
       </c>
       <c r="B7" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,34 +1230,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464070</v>
+        <v>464056</v>
       </c>
       <c r="R7" t="n">
-        <v>6758175</v>
+        <v>6758091</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131589374</v>
+        <v>131604477</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,34 +1332,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464029</v>
+        <v>464463</v>
       </c>
       <c r="R8" t="n">
-        <v>6758112</v>
+        <v>6758106</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1397,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131587086</v>
+        <v>131592130</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,39 +1439,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464056</v>
+        <v>464070</v>
       </c>
       <c r="R9" t="n">
-        <v>6758091</v>
+        <v>6758175</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131605369</v>
+        <v>131589374</v>
       </c>
       <c r="B10" t="n">
         <v>79260</v>
@@ -1544,22 +1554,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464271</v>
+        <v>464029</v>
       </c>
       <c r="R10" t="n">
-        <v>6757950</v>
+        <v>6758112</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1591,18 +1598,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1621,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131604477</v>
+        <v>131605369</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,42 +1633,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464463</v>
+        <v>464271</v>
       </c>
       <c r="R11" t="n">
-        <v>6758106</v>
+        <v>6757950</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1701,7 +1700,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,6 +1709,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131594186</v>
+        <v>131604098</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,34 +2256,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464035</v>
+        <v>464410</v>
       </c>
       <c r="R17" t="n">
-        <v>6758187</v>
+        <v>6758165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2325,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131604098</v>
+        <v>131594186</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2358,39 +2363,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464410</v>
+        <v>464035</v>
       </c>
       <c r="R18" t="n">
-        <v>6758165</v>
+        <v>6758187</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131604566</v>
+        <v>131586743</v>
       </c>
       <c r="B25" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,39 +3067,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464472</v>
+        <v>464052</v>
       </c>
       <c r="R25" t="n">
-        <v>6758091</v>
+        <v>6758047</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,11 +3127,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3265,10 +3255,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131586743</v>
+        <v>131604566</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3276,34 +3266,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464052</v>
+        <v>464472</v>
       </c>
       <c r="R27" t="n">
-        <v>6758047</v>
+        <v>6758091</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,6 +3331,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3678,49 +3678,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131600797</v>
+        <v>131597701</v>
       </c>
       <c r="B31" t="n">
-        <v>99033</v>
+        <v>79260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464314</v>
+        <v>464192</v>
       </c>
       <c r="R31" t="n">
-        <v>6758387</v>
+        <v>6758156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3779,7 +3775,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131591546</v>
+        <v>131594493</v>
       </c>
       <c r="B32" t="n">
         <v>79260</v>
@@ -3808,16 +3804,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464053</v>
+        <v>464034</v>
       </c>
       <c r="R32" t="n">
-        <v>6758144</v>
+        <v>6758248</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3852,12 +3851,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 bilder, bäck</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3876,7 +3881,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131597701</v>
+        <v>131591546</v>
       </c>
       <c r="B33" t="n">
         <v>79260</v>
@@ -3911,10 +3916,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464192</v>
+        <v>464053</v>
       </c>
       <c r="R33" t="n">
-        <v>6758156</v>
+        <v>6758144</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,51 +3978,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131594493</v>
+        <v>131586714</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>57086</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464034</v>
+        <v>464060</v>
       </c>
       <c r="R34" t="n">
-        <v>6758248</v>
+        <v>6758044</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4049,18 +4056,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4079,38 +4080,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131586714</v>
+        <v>131600797</v>
       </c>
       <c r="B35" t="n">
-        <v>57086</v>
+        <v>99034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>95</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4119,13 +4119,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464060</v>
+        <v>464314</v>
       </c>
       <c r="R35" t="n">
-        <v>6758044</v>
+        <v>6758387</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131603322</v>
+        <v>131586494</v>
       </c>
       <c r="B37" t="n">
         <v>79260</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464265</v>
+        <v>464066</v>
       </c>
       <c r="R37" t="n">
-        <v>6758140</v>
+        <v>6757982</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131600594</v>
+        <v>131586581</v>
       </c>
       <c r="B38" t="n">
         <v>79260</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464296</v>
+        <v>464051</v>
       </c>
       <c r="R38" t="n">
-        <v>6758304</v>
+        <v>6758034</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,11 +4451,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4482,7 +4477,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131586494</v>
+        <v>131603322</v>
       </c>
       <c r="B39" t="n">
         <v>79260</v>
@@ -4517,10 +4512,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464066</v>
+        <v>464265</v>
       </c>
       <c r="R39" t="n">
-        <v>6757982</v>
+        <v>6758140</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4579,7 +4574,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131586581</v>
+        <v>131600594</v>
       </c>
       <c r="B40" t="n">
         <v>79260</v>
@@ -4614,10 +4609,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464051</v>
+        <v>464296</v>
       </c>
       <c r="R40" t="n">
-        <v>6758034</v>
+        <v>6758304</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4650,6 +4645,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4870,10 +4870,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131603971</v>
+        <v>131600551</v>
       </c>
       <c r="B43" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4881,34 +4881,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464384</v>
+        <v>464263</v>
       </c>
       <c r="R43" t="n">
-        <v>6758179</v>
+        <v>6758298</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4941,11 +4946,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4972,7 +4972,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131600551</v>
+        <v>131603307</v>
       </c>
       <c r="B44" t="n">
         <v>57898</v>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464263</v>
+        <v>464265</v>
       </c>
       <c r="R44" t="n">
-        <v>6758298</v>
+        <v>6758140</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,6 +5048,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5074,10 +5079,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131603307</v>
+        <v>131603971</v>
       </c>
       <c r="B45" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5085,39 +5090,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464265</v>
+        <v>464384</v>
       </c>
       <c r="R45" t="n">
-        <v>6758140</v>
+        <v>6758179</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>2 bilder, på tall</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5278,45 +5278,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131586790</v>
+        <v>131594252</v>
       </c>
       <c r="B47" t="n">
-        <v>79260</v>
+        <v>57086</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464046</v>
+        <v>464049</v>
       </c>
       <c r="R47" t="n">
-        <v>6758049</v>
+        <v>6758189</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,10 +5383,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131599244</v>
+        <v>131586790</v>
       </c>
       <c r="B48" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,39 +5394,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464210</v>
+        <v>464046</v>
       </c>
       <c r="R48" t="n">
-        <v>6758193</v>
+        <v>6758049</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,11 +5454,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5482,53 +5480,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131594252</v>
+        <v>131599244</v>
       </c>
       <c r="B49" t="n">
-        <v>57086</v>
+        <v>57895</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464049</v>
+        <v>464210</v>
       </c>
       <c r="R49" t="n">
-        <v>6758189</v>
+        <v>6758193</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5561,6 +5556,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5795,7 +5795,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131601417</v>
+        <v>131586572</v>
       </c>
       <c r="B52" t="n">
         <v>79260</v>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464317</v>
+        <v>464052</v>
       </c>
       <c r="R52" t="n">
-        <v>6758312</v>
+        <v>6758021</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5892,7 +5892,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131604599</v>
+        <v>131601417</v>
       </c>
       <c r="B53" t="n">
         <v>79260</v>
@@ -5927,13 +5927,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464472</v>
+        <v>464317</v>
       </c>
       <c r="R53" t="n">
-        <v>6758076</v>
+        <v>6758312</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5963,11 +5963,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5994,7 +5989,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131605027</v>
+        <v>131604599</v>
       </c>
       <c r="B54" t="n">
         <v>79260</v>
@@ -6029,10 +6024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464394</v>
+        <v>464472</v>
       </c>
       <c r="R54" t="n">
-        <v>6758039</v>
+        <v>6758076</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6069,7 +6064,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6096,10 +6091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131605468</v>
+        <v>131605027</v>
       </c>
       <c r="B55" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6107,42 +6102,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464189</v>
+        <v>464394</v>
       </c>
       <c r="R55" t="n">
-        <v>6757919</v>
+        <v>6758039</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6175,6 +6162,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6201,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131586572</v>
+        <v>131605468</v>
       </c>
       <c r="B56" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6212,37 +6204,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464052</v>
+        <v>464189</v>
       </c>
       <c r="R56" t="n">
-        <v>6758021</v>
+        <v>6757919</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6298,10 +6298,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131586922</v>
+        <v>131596208</v>
       </c>
       <c r="B57" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6309,39 +6309,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464054</v>
+        <v>464135</v>
       </c>
       <c r="R57" t="n">
-        <v>6758066</v>
+        <v>6758234</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6400,50 +6395,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131587027</v>
+        <v>131595863</v>
       </c>
       <c r="B58" t="n">
-        <v>57086</v>
+        <v>79260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464056</v>
+        <v>464112</v>
       </c>
       <c r="R58" t="n">
-        <v>6758091</v>
+        <v>6758222</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6476,11 +6466,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6507,38 +6492,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131601410</v>
+        <v>131587027</v>
       </c>
       <c r="B59" t="n">
-        <v>57898</v>
+        <v>57086</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6547,10 +6532,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464317</v>
+        <v>464056</v>
       </c>
       <c r="R59" t="n">
-        <v>6758312</v>
+        <v>6758091</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6587,7 +6572,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>1 bild, ringhack och garn</t>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6614,7 +6599,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131604358</v>
+        <v>131586922</v>
       </c>
       <c r="B60" t="n">
         <v>57898</v>
@@ -6645,7 +6630,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6654,10 +6639,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464439</v>
+        <v>464054</v>
       </c>
       <c r="R60" t="n">
-        <v>6758140</v>
+        <v>6758066</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6690,11 +6675,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6721,10 +6701,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131596208</v>
+        <v>131601410</v>
       </c>
       <c r="B61" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6732,34 +6712,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464135</v>
+        <v>464317</v>
       </c>
       <c r="R61" t="n">
-        <v>6758234</v>
+        <v>6758312</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6792,6 +6777,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6818,10 +6808,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131595863</v>
+        <v>131604358</v>
       </c>
       <c r="B62" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6829,34 +6819,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464112</v>
+        <v>464439</v>
       </c>
       <c r="R62" t="n">
-        <v>6758222</v>
+        <v>6758140</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6889,6 +6884,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131238351</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131239702</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>131239654</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131239936</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131238307</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>131587086</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131604477</v>
+        <v>131592130</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,39 +1332,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464463</v>
+        <v>464070</v>
       </c>
       <c r="R8" t="n">
-        <v>6758106</v>
+        <v>6758175</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131592130</v>
+        <v>131589374</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464070</v>
+        <v>464029</v>
       </c>
       <c r="R9" t="n">
-        <v>6758175</v>
+        <v>6758112</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131589374</v>
+        <v>131604477</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1536,34 +1526,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464029</v>
+        <v>464463</v>
       </c>
       <c r="R10" t="n">
-        <v>6758112</v>
+        <v>6758106</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,6 +1591,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,7 +1625,7 @@
         <v>131605369</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131587093</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131593794</v>
+        <v>131586783</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,34 +1836,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464022</v>
+        <v>464041</v>
       </c>
       <c r="R13" t="n">
-        <v>6758156</v>
+        <v>6758056</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,11 +1904,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,10 +1930,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131595645</v>
+        <v>131593794</v>
       </c>
       <c r="B14" t="n">
-        <v>83240</v>
+        <v>79261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1938,37 +1941,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464112</v>
+        <v>464022</v>
       </c>
       <c r="R14" t="n">
-        <v>6758222</v>
+        <v>6758156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 st Miljöbilder bland annat på en bäck</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,7 +2014,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2033,10 +2032,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131586783</v>
+        <v>131595645</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>83241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,31 +2043,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2076,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464041</v>
+        <v>464112</v>
       </c>
       <c r="R15" t="n">
-        <v>6758056</v>
+        <v>6758222</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,12 +2108,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5 st Miljöbilder bland annat på en bäck</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>131601638</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131604098</v>
+        <v>131594186</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,39 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464410</v>
+        <v>464035</v>
       </c>
       <c r="R17" t="n">
-        <v>6758165</v>
+        <v>6758187</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131594186</v>
+        <v>131600419</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>79880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2387,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464035</v>
+        <v>464251</v>
       </c>
       <c r="R18" t="n">
-        <v>6758187</v>
+        <v>6758281</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,7 +2422,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131600419</v>
+        <v>131604098</v>
       </c>
       <c r="B19" t="n">
-        <v>79879</v>
+        <v>57899</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,34 +2460,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464251</v>
+        <v>464410</v>
       </c>
       <c r="R19" t="n">
-        <v>6758281</v>
+        <v>6758165</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,42 +2567,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R20" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,6 +2627,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,37 +2669,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R21" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2763,7 +2763,7 @@
         <v>131593946</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>131602481</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>131600576</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>131586743</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>131604893</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>131604566</v>
       </c>
       <c r="B27" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3362,50 +3362,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131604756</v>
+        <v>131591546</v>
       </c>
       <c r="B28" t="n">
-        <v>57086</v>
+        <v>79261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464541</v>
+        <v>464053</v>
       </c>
       <c r="R28" t="n">
-        <v>6758017</v>
+        <v>6758144</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3464,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131603524</v>
+        <v>131597701</v>
       </c>
       <c r="B29" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3475,39 +3470,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464384</v>
+        <v>464192</v>
       </c>
       <c r="R29" t="n">
-        <v>6758179</v>
+        <v>6758156</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,11 +3530,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3571,10 +3556,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131604670</v>
+        <v>131594493</v>
       </c>
       <c r="B30" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3582,39 +3567,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464483</v>
+        <v>464034</v>
       </c>
       <c r="R30" t="n">
-        <v>6758032</v>
+        <v>6758248</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3651,7 +3634,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt med ringhack</t>
+          <t>2 bilder, bäck</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3660,6 +3643,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3678,48 +3662,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131597701</v>
+        <v>131586714</v>
       </c>
       <c r="B31" t="n">
-        <v>79260</v>
+        <v>57087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464192</v>
+        <v>464060</v>
       </c>
       <c r="R31" t="n">
-        <v>6758156</v>
+        <v>6758044</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3775,48 +3764,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131594493</v>
+        <v>131600797</v>
       </c>
       <c r="B32" t="n">
-        <v>79260</v>
+        <v>99035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464034</v>
+        <v>464314</v>
       </c>
       <c r="R32" t="n">
-        <v>6758248</v>
+        <v>6758387</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,18 +3841,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3881,45 +3865,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131591546</v>
+        <v>131604756</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>57087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464053</v>
+        <v>464541</v>
       </c>
       <c r="R33" t="n">
-        <v>6758144</v>
+        <v>6758017</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,38 +3967,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131586714</v>
+        <v>131604670</v>
       </c>
       <c r="B34" t="n">
-        <v>57086</v>
+        <v>57899</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4018,13 +4007,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464060</v>
+        <v>464483</v>
       </c>
       <c r="R34" t="n">
-        <v>6758044</v>
+        <v>6758032</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4054,6 +4043,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4080,37 +4074,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131600797</v>
+        <v>131603524</v>
       </c>
       <c r="B35" t="n">
-        <v>99034</v>
+        <v>57899</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>95</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464314</v>
+        <v>464384</v>
       </c>
       <c r="R35" t="n">
-        <v>6758387</v>
+        <v>6758179</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4184,7 +4184,7 @@
         <v>131600974</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>131586494</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>131586581</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>131603322</v>
       </c>
       <c r="B39" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>131600594</v>
       </c>
       <c r="B40" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131599422</v>
       </c>
       <c r="B41" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131597848</v>
+        <v>131603971</v>
       </c>
       <c r="B42" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464205</v>
+        <v>464384</v>
       </c>
       <c r="R42" t="n">
-        <v>6758160</v>
+        <v>6758179</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,6 +4844,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4870,10 +4875,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131600551</v>
+        <v>131600442</v>
       </c>
       <c r="B43" t="n">
-        <v>57898</v>
+        <v>79851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4881,39 +4886,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464263</v>
+        <v>464251</v>
       </c>
       <c r="R43" t="n">
-        <v>6758298</v>
+        <v>6758281</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4972,10 +4972,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131603307</v>
+        <v>131597848</v>
       </c>
       <c r="B44" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4983,39 +4983,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464265</v>
+        <v>464205</v>
       </c>
       <c r="R44" t="n">
-        <v>6758140</v>
+        <v>6758160</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,11 +5043,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5079,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131603971</v>
+        <v>131600551</v>
       </c>
       <c r="B45" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5090,34 +5080,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464384</v>
+        <v>464263</v>
       </c>
       <c r="R45" t="n">
-        <v>6758179</v>
+        <v>6758298</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5150,11 +5145,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5181,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131600442</v>
+        <v>131603307</v>
       </c>
       <c r="B46" t="n">
-        <v>79850</v>
+        <v>57899</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5192,34 +5182,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464251</v>
+        <v>464265</v>
       </c>
       <c r="R46" t="n">
-        <v>6758281</v>
+        <v>6758140</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5247,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,53 +5278,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131594252</v>
+        <v>131586790</v>
       </c>
       <c r="B47" t="n">
-        <v>57086</v>
+        <v>79261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464049</v>
+        <v>464046</v>
       </c>
       <c r="R47" t="n">
-        <v>6758189</v>
+        <v>6758049</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5383,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131586790</v>
+        <v>131599244</v>
       </c>
       <c r="B48" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5394,34 +5386,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464046</v>
+        <v>464210</v>
       </c>
       <c r="R48" t="n">
-        <v>6758049</v>
+        <v>6758193</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5454,6 +5451,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5480,50 +5482,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131599244</v>
+        <v>131594252</v>
       </c>
       <c r="B49" t="n">
-        <v>57895</v>
+        <v>57087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464210</v>
+        <v>464049</v>
       </c>
       <c r="R49" t="n">
-        <v>6758193</v>
+        <v>6758189</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5556,11 +5561,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5590,7 +5590,7 @@
         <v>131586702</v>
       </c>
       <c r="B50" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>131605450</v>
       </c>
       <c r="B51" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>131586572</v>
       </c>
       <c r="B52" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>131601417</v>
       </c>
       <c r="B53" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>131604599</v>
       </c>
       <c r="B54" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>131605027</v>
       </c>
       <c r="B55" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>131605468</v>
       </c>
       <c r="B56" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>131596208</v>
       </c>
       <c r="B57" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>131595863</v>
       </c>
       <c r="B58" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6492,38 +6492,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131587027</v>
+        <v>131604358</v>
       </c>
       <c r="B59" t="n">
-        <v>57086</v>
+        <v>57899</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6532,10 +6532,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464056</v>
+        <v>464439</v>
       </c>
       <c r="R59" t="n">
-        <v>6758091</v>
+        <v>6758140</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Spillning under tjädertall</t>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6599,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131586922</v>
+        <v>131601410</v>
       </c>
       <c r="B60" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6639,10 +6639,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464054</v>
+        <v>464317</v>
       </c>
       <c r="R60" t="n">
-        <v>6758066</v>
+        <v>6758312</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6675,6 +6675,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6701,38 +6706,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131601410</v>
+        <v>131587027</v>
       </c>
       <c r="B61" t="n">
-        <v>57898</v>
+        <v>57087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6741,10 +6746,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464317</v>
+        <v>464056</v>
       </c>
       <c r="R61" t="n">
-        <v>6758312</v>
+        <v>6758091</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6781,7 +6786,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>1 bild, ringhack och garn</t>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6808,10 +6813,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131604358</v>
+        <v>131586922</v>
       </c>
       <c r="B62" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6839,7 +6844,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6848,10 +6853,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464439</v>
+        <v>464054</v>
       </c>
       <c r="R62" t="n">
-        <v>6758140</v>
+        <v>6758066</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6884,11 +6889,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6918,7 +6918,7 @@
         <v>131602531</v>
       </c>
       <c r="B63" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>131603229</v>
       </c>
       <c r="B64" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>131238351</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131239702</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>131239654</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>131239936</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>131238307</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>131587086</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>131592130</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>131589374</v>
       </c>
       <c r="B9" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131604477</v>
+        <v>131605369</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,42 +1526,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464463</v>
+        <v>464271</v>
       </c>
       <c r="R10" t="n">
-        <v>6758106</v>
+        <v>6757950</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1595,7 +1593,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,6 +1602,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1622,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131605369</v>
+        <v>131604477</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,40 +1632,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464271</v>
+        <v>464463</v>
       </c>
       <c r="R11" t="n">
-        <v>6757950</v>
+        <v>6758106</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,7 +1701,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,7 +1710,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>131587093</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131586783</v>
+        <v>131593794</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,42 +1836,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464041</v>
+        <v>464022</v>
       </c>
       <c r="R13" t="n">
-        <v>6758056</v>
+        <v>6758156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,6 +1896,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131593794</v>
+        <v>131595645</v>
       </c>
       <c r="B14" t="n">
-        <v>79261</v>
+        <v>83244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,34 +1938,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464022</v>
+        <v>464112</v>
       </c>
       <c r="R14" t="n">
-        <v>6758156</v>
+        <v>6758222</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>5 st Miljöbilder bland annat på en bäck</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,6 +2014,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2032,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131595645</v>
+        <v>131601638</v>
       </c>
       <c r="B15" t="n">
-        <v>83241</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,37 +2044,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464112</v>
+        <v>464298</v>
       </c>
       <c r="R15" t="n">
-        <v>6758222</v>
+        <v>6758264</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,7 +2113,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5 st Miljöbilder bland annat på en bäck</t>
+          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2119,7 +2122,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2138,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131601638</v>
+        <v>131586783</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,16 +2151,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2167,21 +2169,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464298</v>
+        <v>464041</v>
       </c>
       <c r="R16" t="n">
-        <v>6758264</v>
+        <v>6758056</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,11 +2219,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,7 +2248,7 @@
         <v>131594186</v>
       </c>
       <c r="B17" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>131600419</v>
       </c>
       <c r="B18" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>131604098</v>
       </c>
       <c r="B19" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,37 +2567,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R20" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2627,11 +2632,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,42 +2669,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R21" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2734,6 +2729,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2763,7 +2763,7 @@
         <v>131593946</v>
       </c>
       <c r="B22" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>131602481</v>
       </c>
       <c r="B23" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>131600576</v>
       </c>
       <c r="B24" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>131586743</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3153,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131604893</v>
+        <v>131604566</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3164,37 +3164,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464457</v>
+        <v>464472</v>
       </c>
       <c r="R26" t="n">
-        <v>6758015</v>
+        <v>6758091</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3228,7 +3233,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3255,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131604566</v>
+        <v>131604893</v>
       </c>
       <c r="B27" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3266,42 +3271,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464472</v>
+        <v>464457</v>
       </c>
       <c r="R27" t="n">
-        <v>6758091</v>
+        <v>6758015</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2 bild, tall</t>
+          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3362,45 +3362,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131591546</v>
+        <v>131600797</v>
       </c>
       <c r="B28" t="n">
-        <v>79261</v>
+        <v>99038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464053</v>
+        <v>464314</v>
       </c>
       <c r="R28" t="n">
-        <v>6758144</v>
+        <v>6758387</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3459,10 +3463,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131597701</v>
+        <v>131591546</v>
       </c>
       <c r="B29" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3494,10 +3498,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464192</v>
+        <v>464053</v>
       </c>
       <c r="R29" t="n">
-        <v>6758156</v>
+        <v>6758144</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,10 +3560,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131594493</v>
+        <v>131597701</v>
       </c>
       <c r="B30" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3585,19 +3589,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464034</v>
+        <v>464192</v>
       </c>
       <c r="R30" t="n">
-        <v>6758248</v>
+        <v>6758156</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,18 +3633,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3662,53 +3657,51 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131586714</v>
+        <v>131594493</v>
       </c>
       <c r="B31" t="n">
-        <v>57087</v>
+        <v>79264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464060</v>
+        <v>464034</v>
       </c>
       <c r="R31" t="n">
-        <v>6758044</v>
+        <v>6758248</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3740,12 +3733,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2 bilder, bäck</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3764,37 +3763,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131600797</v>
+        <v>131604756</v>
       </c>
       <c r="B32" t="n">
-        <v>99035</v>
+        <v>57090</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>95</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464314</v>
+        <v>464541</v>
       </c>
       <c r="R32" t="n">
-        <v>6758387</v>
+        <v>6758017</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3865,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131604756</v>
+        <v>131586714</v>
       </c>
       <c r="B33" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464541</v>
+        <v>464060</v>
       </c>
       <c r="R33" t="n">
-        <v>6758017</v>
+        <v>6758044</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>131604670</v>
       </c>
       <c r="B34" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>131603524</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>131600974</v>
       </c>
       <c r="B36" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>131586494</v>
       </c>
       <c r="B37" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>131586581</v>
       </c>
       <c r="B38" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>131603322</v>
       </c>
       <c r="B39" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>131600594</v>
       </c>
       <c r="B40" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131599422</v>
       </c>
       <c r="B41" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>131603971</v>
       </c>
       <c r="B42" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4875,10 +4875,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131600442</v>
+        <v>131600551</v>
       </c>
       <c r="B43" t="n">
-        <v>79851</v>
+        <v>57902</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4886,34 +4886,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464251</v>
+        <v>464263</v>
       </c>
       <c r="R43" t="n">
-        <v>6758281</v>
+        <v>6758298</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4972,10 +4977,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131597848</v>
+        <v>131603307</v>
       </c>
       <c r="B44" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4983,34 +4988,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464205</v>
+        <v>464265</v>
       </c>
       <c r="R44" t="n">
-        <v>6758160</v>
+        <v>6758140</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5043,6 +5053,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5084,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131600551</v>
+        <v>131597848</v>
       </c>
       <c r="B45" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5080,39 +5095,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464263</v>
+        <v>464205</v>
       </c>
       <c r="R45" t="n">
-        <v>6758298</v>
+        <v>6758160</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5171,10 +5181,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131603307</v>
+        <v>131600442</v>
       </c>
       <c r="B46" t="n">
-        <v>57899</v>
+        <v>79854</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5182,39 +5192,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464265</v>
+        <v>464251</v>
       </c>
       <c r="R46" t="n">
-        <v>6758140</v>
+        <v>6758281</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5247,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131586790</v>
+        <v>131599244</v>
       </c>
       <c r="B47" t="n">
-        <v>79261</v>
+        <v>57899</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,34 +5289,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464046</v>
+        <v>464210</v>
       </c>
       <c r="R47" t="n">
-        <v>6758049</v>
+        <v>6758193</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5349,6 +5354,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5375,10 +5385,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131599244</v>
+        <v>131586790</v>
       </c>
       <c r="B48" t="n">
-        <v>57896</v>
+        <v>79264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5386,39 +5396,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464210</v>
+        <v>464046</v>
       </c>
       <c r="R48" t="n">
-        <v>6758193</v>
+        <v>6758049</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,11 +5456,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5485,7 +5485,7 @@
         <v>131594252</v>
       </c>
       <c r="B49" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>131586702</v>
       </c>
       <c r="B50" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>131605450</v>
       </c>
       <c r="B51" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>131586572</v>
       </c>
       <c r="B52" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>131601417</v>
       </c>
       <c r="B53" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>131604599</v>
       </c>
       <c r="B54" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>131605027</v>
       </c>
       <c r="B55" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>131605468</v>
       </c>
       <c r="B56" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6298,10 +6298,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131596208</v>
+        <v>131586922</v>
       </c>
       <c r="B57" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6309,34 +6309,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464135</v>
+        <v>464054</v>
       </c>
       <c r="R57" t="n">
-        <v>6758234</v>
+        <v>6758066</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6395,10 +6400,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131595863</v>
+        <v>131596208</v>
       </c>
       <c r="B58" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6430,10 +6435,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464112</v>
+        <v>464135</v>
       </c>
       <c r="R58" t="n">
-        <v>6758222</v>
+        <v>6758234</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6492,10 +6497,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131604358</v>
+        <v>131595863</v>
       </c>
       <c r="B59" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6503,39 +6508,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464439</v>
+        <v>464112</v>
       </c>
       <c r="R59" t="n">
-        <v>6758140</v>
+        <v>6758222</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6568,11 +6568,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6599,10 +6594,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131601410</v>
+        <v>131604358</v>
       </c>
       <c r="B60" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6630,7 +6625,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6639,10 +6634,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464317</v>
+        <v>464439</v>
       </c>
       <c r="R60" t="n">
-        <v>6758312</v>
+        <v>6758140</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6679,7 +6674,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>1 bild, ringhack och garn</t>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6706,38 +6701,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131587027</v>
+        <v>131601410</v>
       </c>
       <c r="B61" t="n">
-        <v>57087</v>
+        <v>57902</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6746,10 +6741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464056</v>
+        <v>464317</v>
       </c>
       <c r="R61" t="n">
-        <v>6758091</v>
+        <v>6758312</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6786,7 +6781,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Spillning under tjädertall</t>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6813,38 +6808,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131586922</v>
+        <v>131587027</v>
       </c>
       <c r="B62" t="n">
-        <v>57899</v>
+        <v>57090</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6853,10 +6848,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464054</v>
+        <v>464056</v>
       </c>
       <c r="R62" t="n">
-        <v>6758066</v>
+        <v>6758091</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6889,6 +6884,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6918,7 +6918,7 @@
         <v>131602531</v>
       </c>
       <c r="B63" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>131603229</v>
       </c>
       <c r="B64" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7124,6 +7124,6356 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>131806001</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92500</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>106596</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Nordlig parasitporing</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Antrodiella pallasii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Renvall &amp; al.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>464428</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6758134</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>131806044</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>464091</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6758171</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>131806025</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>464116</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6757815</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>131806043</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>464078</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6758160</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>131806066</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78930</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>353</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>464255</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6758034</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>131805997</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>464284</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6758164</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>131805980</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>464132</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6757988</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>131806056</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>464295</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6757996</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>131805986</v>
+      </c>
+      <c r="B73" t="n">
+        <v>4774</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>464254</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6758196</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>131806059</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>464438</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6758173</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>131806028</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>464181</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6757897</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>131806038</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>464420</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6758206</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>131806068</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>464196</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6757964</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>131805988</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>464189</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6758149</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>131806069</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91785</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4118</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tajgafiberskinn</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Fibricium subodoratum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(P.Karst. ex Bourdot &amp; Galzin) Spirin</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>464424</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6758134</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>131805999</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97903</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>464140</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6758185</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>131806042</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>464267</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6758179</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>131805976</v>
+      </c>
+      <c r="B82" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>464319</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6757939</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>131806041</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>464305</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6758161</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>131806029</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>464204</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6757960</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>131806050</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>464143</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6757875</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>131806049</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>464099</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6757847</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>131806060</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>464263</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6758180</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>131805998</v>
+      </c>
+      <c r="B88" t="n">
+        <v>92131</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>658</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>464399</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6758179</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>131806057</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>464303</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6758002</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>131805982</v>
+      </c>
+      <c r="B90" t="n">
+        <v>92555</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>464275</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6758081</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>131805971</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>464201</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6757851</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>131806040</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>464327</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6758158</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>131806048</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>464290</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6758088</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>131806051</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>464172</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6757903</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>131805977</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>464313</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6757941</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>131806032</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>464341</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6757956</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>131806052</v>
+      </c>
+      <c r="B97" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>464193</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6757936</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>131806030</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>464204</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6758031</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>131805972</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>464074</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6758064</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>131806002</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79288</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>464113</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6757861</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>131806000</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>464154</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6758193</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>131806026</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>464158</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6757887</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>131806058</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>464435</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6758156</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>131806036</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>464459</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6758165</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>131805978</v>
+      </c>
+      <c r="B105" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>464275</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6758069</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>131806003</v>
+      </c>
+      <c r="B106" t="n">
+        <v>80405</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>464137</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6758186</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>131806067</v>
+      </c>
+      <c r="B107" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>464196</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6757964</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>131806007</v>
+      </c>
+      <c r="B108" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>464255</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6758034</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>131805989</v>
+      </c>
+      <c r="B109" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>464196</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6758006</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>131806037</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>464449</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6758165</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>131806034</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>464383</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6758151</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>131805979</v>
+      </c>
+      <c r="B112" t="n">
+        <v>91832</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>464400</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6758180</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>131806031</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>464219</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6758055</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>131805970</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>464109</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6757856</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>131806039</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>464338</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6758168</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>131806027</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>464171</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6757887</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>131806061</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57902</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>464225</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6758200</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>131805987</v>
+      </c>
+      <c r="B118" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>464138</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6758188</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>131806035</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>464460</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6758144</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>131806033</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79264</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>464363</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6758150</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>131806004</v>
+      </c>
+      <c r="B121" t="n">
+        <v>81249</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>464261</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6758029</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>131805990</v>
+      </c>
+      <c r="B122" t="n">
+        <v>91782</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>112</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Fulåberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>464391</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6758144</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131587086</v>
+        <v>131592130</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,39 +1230,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464056</v>
+        <v>464070</v>
       </c>
       <c r="R7" t="n">
-        <v>6758091</v>
+        <v>6758175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131592130</v>
+        <v>131589374</v>
       </c>
       <c r="B8" t="n">
         <v>79264</v>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464070</v>
+        <v>464029</v>
       </c>
       <c r="R8" t="n">
-        <v>6758175</v>
+        <v>6758112</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131589374</v>
+        <v>131587086</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,34 +1424,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464029</v>
+        <v>464056</v>
       </c>
       <c r="R9" t="n">
-        <v>6758112</v>
+        <v>6758091</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131601638</v>
+        <v>131586783</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,16 +2044,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2062,21 +2062,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464298</v>
+        <v>464041</v>
       </c>
       <c r="R15" t="n">
-        <v>6758264</v>
+        <v>6758056</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,11 +2112,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2140,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131586783</v>
+        <v>131601638</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,16 +2149,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2169,24 +2167,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464041</v>
+        <v>464298</v>
       </c>
       <c r="R16" t="n">
-        <v>6758056</v>
+        <v>6758264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,6 +2214,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2347,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131600419</v>
+        <v>131604098</v>
       </c>
       <c r="B18" t="n">
-        <v>79883</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2358,34 +2358,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464251</v>
+        <v>464410</v>
       </c>
       <c r="R18" t="n">
-        <v>6758281</v>
+        <v>6758165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,7 +2427,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2449,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131604098</v>
+        <v>131600419</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>79883</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,39 +2465,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464410</v>
+        <v>464251</v>
       </c>
       <c r="R19" t="n">
-        <v>6758165</v>
+        <v>6758281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3056,7 +3056,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131586743</v>
+        <v>131604893</v>
       </c>
       <c r="B25" t="n">
         <v>79264</v>
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464052</v>
+        <v>464457</v>
       </c>
       <c r="R25" t="n">
-        <v>6758047</v>
+        <v>6758015</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3127,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3260,7 +3265,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131604893</v>
+        <v>131586743</v>
       </c>
       <c r="B27" t="n">
         <v>79264</v>
@@ -3295,13 +3300,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464457</v>
+        <v>464052</v>
       </c>
       <c r="R27" t="n">
-        <v>6758015</v>
+        <v>6758047</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3331,11 +3336,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3763,7 +3763,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131604756</v>
+        <v>131586714</v>
       </c>
       <c r="B32" t="n">
         <v>57090</v>
@@ -3803,13 +3803,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464541</v>
+        <v>464060</v>
       </c>
       <c r="R32" t="n">
-        <v>6758017</v>
+        <v>6758044</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3865,38 +3865,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131586714</v>
+        <v>131603524</v>
       </c>
       <c r="B33" t="n">
-        <v>57090</v>
+        <v>57902</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464060</v>
+        <v>464384</v>
       </c>
       <c r="R33" t="n">
-        <v>6758044</v>
+        <v>6758179</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3941,6 +3941,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,38 +4079,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131603524</v>
+        <v>131604756</v>
       </c>
       <c r="B35" t="n">
-        <v>57902</v>
+        <v>57090</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464384</v>
+        <v>464541</v>
       </c>
       <c r="R35" t="n">
-        <v>6758179</v>
+        <v>6758017</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4283,7 +4283,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131586494</v>
+        <v>131603322</v>
       </c>
       <c r="B37" t="n">
         <v>79264</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464066</v>
+        <v>464265</v>
       </c>
       <c r="R37" t="n">
-        <v>6757982</v>
+        <v>6758140</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131586581</v>
+        <v>131600594</v>
       </c>
       <c r="B38" t="n">
         <v>79264</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464051</v>
+        <v>464296</v>
       </c>
       <c r="R38" t="n">
-        <v>6758034</v>
+        <v>6758304</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,6 +4451,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4477,7 +4482,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131603322</v>
+        <v>131586581</v>
       </c>
       <c r="B39" t="n">
         <v>79264</v>
@@ -4512,10 +4517,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464265</v>
+        <v>464051</v>
       </c>
       <c r="R39" t="n">
-        <v>6758140</v>
+        <v>6758034</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4574,7 +4579,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131600594</v>
+        <v>131586494</v>
       </c>
       <c r="B40" t="n">
         <v>79264</v>
@@ -4609,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464296</v>
+        <v>464066</v>
       </c>
       <c r="R40" t="n">
-        <v>6758304</v>
+        <v>6757982</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4645,11 +4650,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4773,7 +4773,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131603971</v>
+        <v>131597848</v>
       </c>
       <c r="B42" t="n">
         <v>79264</v>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464384</v>
+        <v>464205</v>
       </c>
       <c r="R42" t="n">
-        <v>6758179</v>
+        <v>6758160</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,11 +4844,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4875,10 +4870,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131600551</v>
+        <v>131603971</v>
       </c>
       <c r="B43" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4886,39 +4881,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464263</v>
+        <v>464384</v>
       </c>
       <c r="R43" t="n">
-        <v>6758298</v>
+        <v>6758179</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,6 +4941,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5084,10 +5079,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131597848</v>
+        <v>131600551</v>
       </c>
       <c r="B45" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5095,34 +5090,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464205</v>
+        <v>464263</v>
       </c>
       <c r="R45" t="n">
-        <v>6758160</v>
+        <v>6758298</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131599244</v>
+        <v>131586790</v>
       </c>
       <c r="B47" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,39 +5289,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464210</v>
+        <v>464046</v>
       </c>
       <c r="R47" t="n">
-        <v>6758193</v>
+        <v>6758049</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5354,11 +5349,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5385,45 +5375,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131586790</v>
+        <v>131594252</v>
       </c>
       <c r="B48" t="n">
-        <v>79264</v>
+        <v>57090</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464046</v>
+        <v>464049</v>
       </c>
       <c r="R48" t="n">
-        <v>6758049</v>
+        <v>6758189</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,53 +5480,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131594252</v>
+        <v>131599244</v>
       </c>
       <c r="B49" t="n">
-        <v>57090</v>
+        <v>57899</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464049</v>
+        <v>464210</v>
       </c>
       <c r="R49" t="n">
-        <v>6758189</v>
+        <v>6758193</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5561,6 +5556,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5892,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131601417</v>
+        <v>131605468</v>
       </c>
       <c r="B53" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5903,37 +5903,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464317</v>
+        <v>464189</v>
       </c>
       <c r="R53" t="n">
-        <v>6758312</v>
+        <v>6757919</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5989,7 +5997,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131604599</v>
+        <v>131601417</v>
       </c>
       <c r="B54" t="n">
         <v>79264</v>
@@ -6024,13 +6032,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464472</v>
+        <v>464317</v>
       </c>
       <c r="R54" t="n">
-        <v>6758076</v>
+        <v>6758312</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6060,11 +6068,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6091,7 +6094,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131605027</v>
+        <v>131604599</v>
       </c>
       <c r="B55" t="n">
         <v>79264</v>
@@ -6126,10 +6129,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464394</v>
+        <v>464472</v>
       </c>
       <c r="R55" t="n">
-        <v>6758039</v>
+        <v>6758076</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6166,7 +6169,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6193,10 +6196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131605468</v>
+        <v>131605027</v>
       </c>
       <c r="B56" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6204,42 +6207,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464189</v>
+        <v>464394</v>
       </c>
       <c r="R56" t="n">
-        <v>6757919</v>
+        <v>6758039</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6272,6 +6267,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6298,7 +6298,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131586922</v>
+        <v>131601410</v>
       </c>
       <c r="B57" t="n">
         <v>57902</v>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464054</v>
+        <v>464317</v>
       </c>
       <c r="R57" t="n">
-        <v>6758066</v>
+        <v>6758312</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6374,6 +6374,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6594,7 +6599,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131604358</v>
+        <v>131586922</v>
       </c>
       <c r="B60" t="n">
         <v>57902</v>
@@ -6625,7 +6630,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6634,10 +6639,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464439</v>
+        <v>464054</v>
       </c>
       <c r="R60" t="n">
-        <v>6758140</v>
+        <v>6758066</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6670,11 +6675,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6701,38 +6701,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131601410</v>
+        <v>131587027</v>
       </c>
       <c r="B61" t="n">
-        <v>57902</v>
+        <v>57090</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464317</v>
+        <v>464056</v>
       </c>
       <c r="R61" t="n">
-        <v>6758312</v>
+        <v>6758091</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>1 bild, ringhack och garn</t>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6808,38 +6808,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131587027</v>
+        <v>131604358</v>
       </c>
       <c r="B62" t="n">
-        <v>57090</v>
+        <v>57902</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464056</v>
+        <v>464439</v>
       </c>
       <c r="R62" t="n">
-        <v>6758091</v>
+        <v>6758140</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Spillning under tjädertall</t>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7662,45 +7662,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131805997</v>
+        <v>131806056</v>
       </c>
       <c r="B70" t="n">
-        <v>92292</v>
+        <v>57902</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464284</v>
+        <v>464295</v>
       </c>
       <c r="R70" t="n">
-        <v>6758164</v>
+        <v>6757996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7732,7 +7737,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7742,7 +7747,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7769,45 +7774,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131805980</v>
+        <v>131805986</v>
       </c>
       <c r="B71" t="n">
-        <v>91832</v>
+        <v>4774</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464132</v>
+        <v>464254</v>
       </c>
       <c r="R71" t="n">
-        <v>6757988</v>
+        <v>6758196</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7839,7 +7849,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7849,7 +7859,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7876,50 +7886,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131806056</v>
+        <v>131805997</v>
       </c>
       <c r="B72" t="n">
-        <v>57902</v>
+        <v>92292</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464295</v>
+        <v>464284</v>
       </c>
       <c r="R72" t="n">
-        <v>6757996</v>
+        <v>6758164</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7951,7 +7956,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7961,7 +7966,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,50 +7993,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131805986</v>
+        <v>131805980</v>
       </c>
       <c r="B73" t="n">
-        <v>4774</v>
+        <v>91832</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464254</v>
+        <v>464132</v>
       </c>
       <c r="R73" t="n">
-        <v>6758196</v>
+        <v>6757988</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8100,10 +8100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131806059</v>
+        <v>131806028</v>
       </c>
       <c r="B74" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,39 +8111,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464438</v>
+        <v>464181</v>
       </c>
       <c r="R74" t="n">
-        <v>6758173</v>
+        <v>6757897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8175,7 +8170,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8185,7 +8180,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8212,10 +8207,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131806028</v>
+        <v>131806059</v>
       </c>
       <c r="B75" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8223,34 +8218,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464181</v>
+        <v>464438</v>
       </c>
       <c r="R75" t="n">
-        <v>6757897</v>
+        <v>6758173</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8538,32 +8538,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131805988</v>
+        <v>131806069</v>
       </c>
       <c r="B78" t="n">
-        <v>80398</v>
+        <v>91785</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>4118</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tajgafiberskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fibricium subodoratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst. ex Bourdot &amp; Galzin) Spirin</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8573,10 +8573,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464189</v>
+        <v>464424</v>
       </c>
       <c r="R78" t="n">
-        <v>6758149</v>
+        <v>6758134</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8618,32 +8618,17 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -8660,32 +8645,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131806069</v>
+        <v>131805988</v>
       </c>
       <c r="B79" t="n">
-        <v>91785</v>
+        <v>80398</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4118</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tajgafiberskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fibricium subodoratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst. ex Bourdot &amp; Galzin) Spirin</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8695,10 +8680,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464424</v>
+        <v>464189</v>
       </c>
       <c r="R79" t="n">
-        <v>6758134</v>
+        <v>6758149</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8730,7 +8715,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8740,17 +8725,32 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8874,10 +8874,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131806042</v>
+        <v>131805976</v>
       </c>
       <c r="B81" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8885,21 +8885,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464267</v>
+        <v>464319</v>
       </c>
       <c r="R81" t="n">
-        <v>6758179</v>
+        <v>6757939</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8981,10 +8981,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131805976</v>
+        <v>131806042</v>
       </c>
       <c r="B82" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8992,21 +8992,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464319</v>
+        <v>464267</v>
       </c>
       <c r="R82" t="n">
-        <v>6757939</v>
+        <v>6758179</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,7 +9088,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131806041</v>
+        <v>131806029</v>
       </c>
       <c r="B83" t="n">
         <v>79264</v>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464305</v>
+        <v>464204</v>
       </c>
       <c r="R83" t="n">
-        <v>6758161</v>
+        <v>6757960</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9195,7 +9195,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131806029</v>
+        <v>131806041</v>
       </c>
       <c r="B84" t="n">
         <v>79264</v>
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464204</v>
+        <v>464305</v>
       </c>
       <c r="R84" t="n">
-        <v>6757960</v>
+        <v>6758161</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9302,10 +9302,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131806050</v>
+        <v>131805998</v>
       </c>
       <c r="B85" t="n">
-        <v>57902</v>
+        <v>92131</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9313,39 +9313,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464143</v>
+        <v>464399</v>
       </c>
       <c r="R85" t="n">
-        <v>6757875</v>
+        <v>6758179</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9377,7 +9372,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9387,7 +9382,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9414,7 +9409,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131806049</v>
+        <v>131806060</v>
       </c>
       <c r="B86" t="n">
         <v>57902</v>
@@ -9445,7 +9440,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9454,10 +9449,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464099</v>
+        <v>464263</v>
       </c>
       <c r="R86" t="n">
-        <v>6757847</v>
+        <v>6758180</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9489,7 +9484,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9499,7 +9494,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9526,7 +9521,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131806060</v>
+        <v>131806050</v>
       </c>
       <c r="B87" t="n">
         <v>57902</v>
@@ -9566,10 +9561,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464263</v>
+        <v>464143</v>
       </c>
       <c r="R87" t="n">
-        <v>6758180</v>
+        <v>6757875</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9601,7 +9596,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9611,7 +9606,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9638,10 +9633,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131805998</v>
+        <v>131806049</v>
       </c>
       <c r="B88" t="n">
-        <v>92131</v>
+        <v>57902</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9649,34 +9644,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464399</v>
+        <v>464099</v>
       </c>
       <c r="R88" t="n">
-        <v>6758179</v>
+        <v>6757847</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9857,32 +9857,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131805982</v>
+        <v>131806040</v>
       </c>
       <c r="B90" t="n">
-        <v>92555</v>
+        <v>79264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464275</v>
+        <v>464327</v>
       </c>
       <c r="R90" t="n">
-        <v>6758081</v>
+        <v>6758158</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9964,10 +9964,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131805971</v>
+        <v>131805982</v>
       </c>
       <c r="B91" t="n">
-        <v>91795</v>
+        <v>92555</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9975,21 +9975,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9999,10 +9999,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464201</v>
+        <v>464275</v>
       </c>
       <c r="R91" t="n">
-        <v>6757851</v>
+        <v>6758081</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10071,32 +10071,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131806040</v>
+        <v>131805971</v>
       </c>
       <c r="B92" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10106,10 +10106,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464327</v>
+        <v>464201</v>
       </c>
       <c r="R92" t="n">
-        <v>6758158</v>
+        <v>6757851</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10178,7 +10178,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131806048</v>
+        <v>131806051</v>
       </c>
       <c r="B93" t="n">
         <v>57902</v>
@@ -10209,7 +10209,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10218,10 +10218,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464290</v>
+        <v>464172</v>
       </c>
       <c r="R93" t="n">
-        <v>6758088</v>
+        <v>6757903</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10253,7 +10253,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10290,7 +10290,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131806051</v>
+        <v>131806048</v>
       </c>
       <c r="B94" t="n">
         <v>57902</v>
@@ -10321,7 +10321,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10330,10 +10330,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464172</v>
+        <v>464290</v>
       </c>
       <c r="R94" t="n">
-        <v>6757903</v>
+        <v>6758088</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10509,10 +10509,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806032</v>
+        <v>131806052</v>
       </c>
       <c r="B96" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10520,34 +10520,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464341</v>
+        <v>464193</v>
       </c>
       <c r="R96" t="n">
-        <v>6757956</v>
+        <v>6757936</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10579,7 +10584,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10589,7 +10594,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10616,10 +10621,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806052</v>
+        <v>131806032</v>
       </c>
       <c r="B97" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10627,39 +10632,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464193</v>
+        <v>464341</v>
       </c>
       <c r="R97" t="n">
-        <v>6757936</v>
+        <v>6757956</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11268,10 +11268,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131806058</v>
+        <v>131805978</v>
       </c>
       <c r="B103" t="n">
-        <v>57902</v>
+        <v>91832</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11279,39 +11279,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464435</v>
+        <v>464275</v>
       </c>
       <c r="R103" t="n">
-        <v>6758156</v>
+        <v>6758069</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11343,7 +11338,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11353,7 +11348,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11487,45 +11482,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131805978</v>
+        <v>131806067</v>
       </c>
       <c r="B105" t="n">
-        <v>91832</v>
+        <v>5178</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464275</v>
+        <v>464196</v>
       </c>
       <c r="R105" t="n">
-        <v>6758069</v>
+        <v>6757964</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11716,38 +11716,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131806067</v>
+        <v>131806058</v>
       </c>
       <c r="B107" t="n">
-        <v>5178</v>
+        <v>57902</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -11756,10 +11756,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464196</v>
+        <v>464435</v>
       </c>
       <c r="R107" t="n">
-        <v>6757964</v>
+        <v>6758156</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11828,54 +11828,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131806007</v>
+        <v>131805989</v>
       </c>
       <c r="B108" t="n">
-        <v>99038</v>
+        <v>80398</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464255</v>
+        <v>464196</v>
       </c>
       <c r="R108" t="n">
-        <v>6758034</v>
+        <v>6758006</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11907,7 +11898,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11917,7 +11908,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11928,6 +11919,21 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -11944,45 +11950,54 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131805989</v>
+        <v>131806007</v>
       </c>
       <c r="B109" t="n">
-        <v>80398</v>
+        <v>99038</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464196</v>
+        <v>464255</v>
       </c>
       <c r="R109" t="n">
-        <v>6758006</v>
+        <v>6758034</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12014,7 +12029,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12024,7 +12039,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12035,21 +12050,6 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -12173,10 +12173,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131806034</v>
+        <v>131805979</v>
       </c>
       <c r="B111" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12184,21 +12184,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464383</v>
+        <v>464400</v>
       </c>
       <c r="R111" t="n">
-        <v>6758151</v>
+        <v>6758180</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12280,10 +12280,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131805979</v>
+        <v>131806034</v>
       </c>
       <c r="B112" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12291,21 +12291,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464400</v>
+        <v>464383</v>
       </c>
       <c r="R112" t="n">
-        <v>6758180</v>
+        <v>6758151</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12494,32 +12494,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131805970</v>
+        <v>131805990</v>
       </c>
       <c r="B114" t="n">
-        <v>91795</v>
+        <v>91782</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464109</v>
+        <v>464391</v>
       </c>
       <c r="R114" t="n">
-        <v>6757856</v>
+        <v>6758144</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12601,32 +12601,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131806039</v>
+        <v>131805970</v>
       </c>
       <c r="B115" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464338</v>
+        <v>464109</v>
       </c>
       <c r="R115" t="n">
-        <v>6758168</v>
+        <v>6757856</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12708,32 +12708,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131806027</v>
+        <v>131805987</v>
       </c>
       <c r="B116" t="n">
-        <v>79264</v>
+        <v>80398</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464171</v>
+        <v>464138</v>
       </c>
       <c r="R116" t="n">
-        <v>6757887</v>
+        <v>6758188</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12799,6 +12799,21 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -12815,10 +12830,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131806061</v>
+        <v>131806039</v>
       </c>
       <c r="B117" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12826,39 +12841,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464225</v>
+        <v>464338</v>
       </c>
       <c r="R117" t="n">
-        <v>6758200</v>
+        <v>6758168</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12890,7 +12900,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12900,7 +12910,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12927,32 +12937,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131805987</v>
+        <v>131806027</v>
       </c>
       <c r="B118" t="n">
-        <v>80398</v>
+        <v>79264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12962,10 +12972,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464138</v>
+        <v>464171</v>
       </c>
       <c r="R118" t="n">
-        <v>6758188</v>
+        <v>6757887</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12997,7 +13007,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13007,7 +13017,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13018,21 +13028,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13049,7 +13044,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131806035</v>
+        <v>131806033</v>
       </c>
       <c r="B119" t="n">
         <v>79264</v>
@@ -13084,10 +13079,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464460</v>
+        <v>464363</v>
       </c>
       <c r="R119" t="n">
-        <v>6758144</v>
+        <v>6758150</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13119,7 +13114,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13129,7 +13124,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13156,10 +13151,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131806033</v>
+        <v>131806004</v>
       </c>
       <c r="B120" t="n">
-        <v>79264</v>
+        <v>81249</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13167,21 +13162,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13191,10 +13186,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464363</v>
+        <v>464261</v>
       </c>
       <c r="R120" t="n">
-        <v>6758150</v>
+        <v>6758029</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13226,7 +13221,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13236,7 +13231,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13263,10 +13258,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131806004</v>
+        <v>131806061</v>
       </c>
       <c r="B121" t="n">
-        <v>81249</v>
+        <v>57902</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13274,34 +13269,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464261</v>
+        <v>464225</v>
       </c>
       <c r="R121" t="n">
-        <v>6758029</v>
+        <v>6758200</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13370,10 +13370,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131805990</v>
+        <v>131806035</v>
       </c>
       <c r="B122" t="n">
-        <v>91782</v>
+        <v>79264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13381,21 +13381,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13405,7 +13405,7 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464391</v>
+        <v>464460</v>
       </c>
       <c r="R122" t="n">
         <v>6758144</v>
@@ -13440,7 +13440,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD122" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131592130</v>
+        <v>131605369</v>
       </c>
       <c r="B7" t="n">
         <v>79264</v>
@@ -1248,19 +1248,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464070</v>
+        <v>464271</v>
       </c>
       <c r="R7" t="n">
-        <v>6758175</v>
+        <v>6757950</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,12 +1295,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131589374</v>
+        <v>131604477</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,34 +1336,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464029</v>
+        <v>464463</v>
       </c>
       <c r="R8" t="n">
-        <v>6758112</v>
+        <v>6758106</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1401,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131587086</v>
+        <v>131592130</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,39 +1443,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464056</v>
+        <v>464070</v>
       </c>
       <c r="R9" t="n">
-        <v>6758091</v>
+        <v>6758175</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1529,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131605369</v>
+        <v>131589374</v>
       </c>
       <c r="B10" t="n">
         <v>79264</v>
@@ -1544,22 +1558,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464271</v>
+        <v>464029</v>
       </c>
       <c r="R10" t="n">
-        <v>6757950</v>
+        <v>6758112</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1591,18 +1602,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1621,7 +1626,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131604477</v>
+        <v>131587086</v>
       </c>
       <c r="B11" t="n">
         <v>57902</v>
@@ -1661,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464463</v>
+        <v>464056</v>
       </c>
       <c r="R11" t="n">
-        <v>6758106</v>
+        <v>6758091</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,11 +1702,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131594186</v>
+        <v>131604098</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,34 +2256,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464035</v>
+        <v>464410</v>
       </c>
       <c r="R17" t="n">
-        <v>6758187</v>
+        <v>6758165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2325,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131604098</v>
+        <v>131594186</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2358,39 +2363,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464410</v>
+        <v>464035</v>
       </c>
       <c r="R18" t="n">
-        <v>6758165</v>
+        <v>6758187</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131604893</v>
+        <v>131604566</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,37 +3067,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464457</v>
+        <v>464472</v>
       </c>
       <c r="R25" t="n">
-        <v>6758015</v>
+        <v>6758091</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3131,7 +3136,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3158,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131604566</v>
+        <v>131586743</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3169,39 +3174,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464472</v>
+        <v>464052</v>
       </c>
       <c r="R26" t="n">
-        <v>6758091</v>
+        <v>6758047</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,11 +3234,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3265,7 +3260,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131586743</v>
+        <v>131604893</v>
       </c>
       <c r="B27" t="n">
         <v>79264</v>
@@ -3300,13 +3295,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464052</v>
+        <v>464457</v>
       </c>
       <c r="R27" t="n">
-        <v>6758047</v>
+        <v>6758015</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3336,6 +3331,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3362,49 +3362,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131600797</v>
+        <v>131591546</v>
       </c>
       <c r="B28" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464314</v>
+        <v>464053</v>
       </c>
       <c r="R28" t="n">
-        <v>6758387</v>
+        <v>6758144</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,7 +3459,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131591546</v>
+        <v>131597701</v>
       </c>
       <c r="B29" t="n">
         <v>79264</v>
@@ -3498,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464053</v>
+        <v>464192</v>
       </c>
       <c r="R29" t="n">
-        <v>6758144</v>
+        <v>6758156</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3560,7 +3556,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131597701</v>
+        <v>131594493</v>
       </c>
       <c r="B30" t="n">
         <v>79264</v>
@@ -3589,16 +3585,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464192</v>
+        <v>464034</v>
       </c>
       <c r="R30" t="n">
-        <v>6758156</v>
+        <v>6758248</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,12 +3632,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2 bilder, bäck</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3657,51 +3662,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131594493</v>
+        <v>131586714</v>
       </c>
       <c r="B31" t="n">
-        <v>79264</v>
+        <v>57090</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464034</v>
+        <v>464060</v>
       </c>
       <c r="R31" t="n">
-        <v>6758248</v>
+        <v>6758044</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3733,18 +3740,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3763,38 +3764,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131586714</v>
+        <v>131604670</v>
       </c>
       <c r="B32" t="n">
-        <v>57090</v>
+        <v>57902</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3803,13 +3804,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464060</v>
+        <v>464483</v>
       </c>
       <c r="R32" t="n">
-        <v>6758044</v>
+        <v>6758032</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3839,6 +3840,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3972,38 +3978,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131604670</v>
+        <v>131600797</v>
       </c>
       <c r="B34" t="n">
-        <v>57902</v>
+        <v>99038</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>95</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4012,10 +4017,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464483</v>
+        <v>464314</v>
       </c>
       <c r="R34" t="n">
-        <v>6758032</v>
+        <v>6758387</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4048,11 +4053,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,7 +4380,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131600594</v>
+        <v>131586494</v>
       </c>
       <c r="B38" t="n">
         <v>79264</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464296</v>
+        <v>464066</v>
       </c>
       <c r="R38" t="n">
-        <v>6758304</v>
+        <v>6757982</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,11 +4451,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4579,7 +4574,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131586494</v>
+        <v>131600594</v>
       </c>
       <c r="B40" t="n">
         <v>79264</v>
@@ -4614,10 +4609,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464066</v>
+        <v>464296</v>
       </c>
       <c r="R40" t="n">
-        <v>6757982</v>
+        <v>6758304</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4650,6 +4645,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4972,7 +4972,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131603307</v>
+        <v>131600551</v>
       </c>
       <c r="B44" t="n">
         <v>57902</v>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464265</v>
+        <v>464263</v>
       </c>
       <c r="R44" t="n">
-        <v>6758140</v>
+        <v>6758298</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,11 +5048,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5079,7 +5074,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131600551</v>
+        <v>131603307</v>
       </c>
       <c r="B45" t="n">
         <v>57902</v>
@@ -5119,10 +5114,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464263</v>
+        <v>464265</v>
       </c>
       <c r="R45" t="n">
-        <v>6758298</v>
+        <v>6758140</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,6 +5150,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5278,45 +5278,53 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131586790</v>
+        <v>131594252</v>
       </c>
       <c r="B47" t="n">
-        <v>79264</v>
+        <v>57090</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464046</v>
+        <v>464049</v>
       </c>
       <c r="R47" t="n">
-        <v>6758049</v>
+        <v>6758189</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,53 +5383,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131594252</v>
+        <v>131599244</v>
       </c>
       <c r="B48" t="n">
-        <v>57090</v>
+        <v>57899</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464049</v>
+        <v>464210</v>
       </c>
       <c r="R48" t="n">
-        <v>6758189</v>
+        <v>6758193</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5454,6 +5459,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5480,10 +5490,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131599244</v>
+        <v>131586790</v>
       </c>
       <c r="B49" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5491,39 +5501,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464210</v>
+        <v>464046</v>
       </c>
       <c r="R49" t="n">
-        <v>6758193</v>
+        <v>6758049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5556,11 +5561,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131586702</v>
+        <v>131605450</v>
       </c>
       <c r="B50" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,42 +5598,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464051</v>
+        <v>464189</v>
       </c>
       <c r="R50" t="n">
-        <v>6758034</v>
+        <v>6757919</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5665,12 +5663,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131605450</v>
+        <v>131586702</v>
       </c>
       <c r="B51" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,40 +5704,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464189</v>
+        <v>464051</v>
       </c>
       <c r="R51" t="n">
-        <v>6757919</v>
+        <v>6758034</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5765,18 +5771,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131586572</v>
+        <v>131605468</v>
       </c>
       <c r="B52" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5806,37 +5806,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464052</v>
+        <v>464189</v>
       </c>
       <c r="R52" t="n">
-        <v>6758021</v>
+        <v>6757919</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5892,10 +5900,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131605468</v>
+        <v>131601417</v>
       </c>
       <c r="B53" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5903,45 +5911,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464189</v>
+        <v>464317</v>
       </c>
       <c r="R53" t="n">
-        <v>6757919</v>
+        <v>6758312</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131601417</v>
+        <v>131604599</v>
       </c>
       <c r="B54" t="n">
         <v>79264</v>
@@ -6032,13 +6032,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464317</v>
+        <v>464472</v>
       </c>
       <c r="R54" t="n">
-        <v>6758312</v>
+        <v>6758076</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6068,6 +6068,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6094,7 +6099,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131604599</v>
+        <v>131605027</v>
       </c>
       <c r="B55" t="n">
         <v>79264</v>
@@ -6129,10 +6134,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464472</v>
+        <v>464394</v>
       </c>
       <c r="R55" t="n">
-        <v>6758076</v>
+        <v>6758039</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6169,7 +6174,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6196,7 +6201,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131605027</v>
+        <v>131586572</v>
       </c>
       <c r="B56" t="n">
         <v>79264</v>
@@ -6231,13 +6236,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464394</v>
+        <v>464052</v>
       </c>
       <c r="R56" t="n">
-        <v>6758039</v>
+        <v>6758021</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6267,11 +6272,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6298,10 +6298,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131601410</v>
+        <v>131596208</v>
       </c>
       <c r="B57" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6309,39 +6309,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464317</v>
+        <v>464135</v>
       </c>
       <c r="R57" t="n">
-        <v>6758312</v>
+        <v>6758234</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6374,11 +6369,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6405,7 +6395,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131596208</v>
+        <v>131595863</v>
       </c>
       <c r="B58" t="n">
         <v>79264</v>
@@ -6440,10 +6430,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464135</v>
+        <v>464112</v>
       </c>
       <c r="R58" t="n">
-        <v>6758234</v>
+        <v>6758222</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6502,45 +6492,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131595863</v>
+        <v>131587027</v>
       </c>
       <c r="B59" t="n">
-        <v>79264</v>
+        <v>57090</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464112</v>
+        <v>464056</v>
       </c>
       <c r="R59" t="n">
-        <v>6758222</v>
+        <v>6758091</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6573,6 +6568,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6701,38 +6701,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131587027</v>
+        <v>131604358</v>
       </c>
       <c r="B61" t="n">
-        <v>57090</v>
+        <v>57902</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464056</v>
+        <v>464439</v>
       </c>
       <c r="R61" t="n">
-        <v>6758091</v>
+        <v>6758140</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Spillning under tjädertall</t>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6808,7 +6808,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131604358</v>
+        <v>131601410</v>
       </c>
       <c r="B62" t="n">
         <v>57902</v>
@@ -6839,7 +6839,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464439</v>
+        <v>464317</v>
       </c>
       <c r="R62" t="n">
-        <v>6758140</v>
+        <v>6758312</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7127,32 +7127,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131806001</v>
+        <v>131806044</v>
       </c>
       <c r="B65" t="n">
-        <v>92500</v>
+        <v>79264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106596</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordlig parasitporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464428</v>
+        <v>464091</v>
       </c>
       <c r="R65" t="n">
-        <v>6758134</v>
+        <v>6758171</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7234,7 +7234,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131806044</v>
+        <v>131806025</v>
       </c>
       <c r="B66" t="n">
         <v>79264</v>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464091</v>
+        <v>464116</v>
       </c>
       <c r="R66" t="n">
-        <v>6758171</v>
+        <v>6757815</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7341,32 +7341,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131806025</v>
+        <v>131806001</v>
       </c>
       <c r="B67" t="n">
-        <v>79264</v>
+        <v>92500</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106596</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464116</v>
+        <v>464428</v>
       </c>
       <c r="R67" t="n">
-        <v>6757815</v>
+        <v>6758134</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7662,50 +7662,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131806056</v>
+        <v>131805997</v>
       </c>
       <c r="B70" t="n">
-        <v>57902</v>
+        <v>92292</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464295</v>
+        <v>464284</v>
       </c>
       <c r="R70" t="n">
-        <v>6757996</v>
+        <v>6758164</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7737,7 +7732,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7747,7 +7742,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7774,50 +7769,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131805986</v>
+        <v>131805980</v>
       </c>
       <c r="B71" t="n">
-        <v>4774</v>
+        <v>91832</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464254</v>
+        <v>464132</v>
       </c>
       <c r="R71" t="n">
-        <v>6758196</v>
+        <v>6757988</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7849,7 +7839,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7859,7 +7849,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,45 +7876,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131805997</v>
+        <v>131806056</v>
       </c>
       <c r="B72" t="n">
-        <v>92292</v>
+        <v>57902</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464284</v>
+        <v>464295</v>
       </c>
       <c r="R72" t="n">
-        <v>6758164</v>
+        <v>6757996</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7956,7 +7951,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7966,7 +7961,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7993,45 +7988,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131805980</v>
+        <v>131805986</v>
       </c>
       <c r="B73" t="n">
-        <v>91832</v>
+        <v>4774</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464132</v>
+        <v>464254</v>
       </c>
       <c r="R73" t="n">
-        <v>6757988</v>
+        <v>6758196</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8319,32 +8319,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131806038</v>
+        <v>131806069</v>
       </c>
       <c r="B76" t="n">
-        <v>79264</v>
+        <v>91785</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>4118</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgafiberskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fibricium subodoratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst. ex Bourdot &amp; Galzin) Spirin</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464420</v>
+        <v>464424</v>
       </c>
       <c r="R76" t="n">
-        <v>6758206</v>
+        <v>6758134</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8399,14 +8399,14 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
@@ -8538,32 +8538,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131806069</v>
+        <v>131806038</v>
       </c>
       <c r="B78" t="n">
-        <v>91785</v>
+        <v>79264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4118</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tajgafiberskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fibricium subodoratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst. ex Bourdot &amp; Galzin) Spirin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8573,10 +8573,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464424</v>
+        <v>464420</v>
       </c>
       <c r="R78" t="n">
-        <v>6758134</v>
+        <v>6758206</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8618,14 +8618,14 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -8767,32 +8767,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131805999</v>
+        <v>131806042</v>
       </c>
       <c r="B80" t="n">
-        <v>97903</v>
+        <v>79264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464140</v>
+        <v>464267</v>
       </c>
       <c r="R80" t="n">
-        <v>6758185</v>
+        <v>6758179</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8874,10 +8874,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131805976</v>
+        <v>131806029</v>
       </c>
       <c r="B81" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8885,21 +8885,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464319</v>
+        <v>464204</v>
       </c>
       <c r="R81" t="n">
-        <v>6757939</v>
+        <v>6757960</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8981,7 +8981,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131806042</v>
+        <v>131806041</v>
       </c>
       <c r="B82" t="n">
         <v>79264</v>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464267</v>
+        <v>464305</v>
       </c>
       <c r="R82" t="n">
-        <v>6758179</v>
+        <v>6758161</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,10 +9088,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131806029</v>
+        <v>131805976</v>
       </c>
       <c r="B83" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9099,21 +9099,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464204</v>
+        <v>464319</v>
       </c>
       <c r="R83" t="n">
-        <v>6757960</v>
+        <v>6757939</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9195,32 +9195,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131806041</v>
+        <v>131805999</v>
       </c>
       <c r="B84" t="n">
-        <v>79264</v>
+        <v>97903</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464305</v>
+        <v>464140</v>
       </c>
       <c r="R84" t="n">
-        <v>6758161</v>
+        <v>6758185</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9409,7 +9409,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131806060</v>
+        <v>131806050</v>
       </c>
       <c r="B86" t="n">
         <v>57902</v>
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464263</v>
+        <v>464143</v>
       </c>
       <c r="R86" t="n">
-        <v>6758180</v>
+        <v>6757875</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9521,7 +9521,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131806050</v>
+        <v>131806060</v>
       </c>
       <c r="B87" t="n">
         <v>57902</v>
@@ -9561,10 +9561,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464143</v>
+        <v>464263</v>
       </c>
       <c r="R87" t="n">
-        <v>6757875</v>
+        <v>6758180</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9857,32 +9857,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131806040</v>
+        <v>131805982</v>
       </c>
       <c r="B90" t="n">
-        <v>79264</v>
+        <v>92555</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464327</v>
+        <v>464275</v>
       </c>
       <c r="R90" t="n">
-        <v>6758158</v>
+        <v>6758081</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9964,10 +9964,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131805982</v>
+        <v>131805971</v>
       </c>
       <c r="B91" t="n">
-        <v>92555</v>
+        <v>91795</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9975,21 +9975,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9999,10 +9999,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464275</v>
+        <v>464201</v>
       </c>
       <c r="R91" t="n">
-        <v>6758081</v>
+        <v>6757851</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10071,32 +10071,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131805971</v>
+        <v>131806040</v>
       </c>
       <c r="B92" t="n">
-        <v>91795</v>
+        <v>79264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10106,10 +10106,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464201</v>
+        <v>464327</v>
       </c>
       <c r="R92" t="n">
-        <v>6757851</v>
+        <v>6758158</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10178,10 +10178,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131806051</v>
+        <v>131805977</v>
       </c>
       <c r="B93" t="n">
-        <v>57902</v>
+        <v>91832</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10189,39 +10189,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464172</v>
+        <v>464313</v>
       </c>
       <c r="R93" t="n">
-        <v>6757903</v>
+        <v>6757941</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10253,7 +10248,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10263,7 +10258,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10290,7 +10285,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131806048</v>
+        <v>131806051</v>
       </c>
       <c r="B94" t="n">
         <v>57902</v>
@@ -10321,7 +10316,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10330,10 +10325,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464290</v>
+        <v>464172</v>
       </c>
       <c r="R94" t="n">
-        <v>6758088</v>
+        <v>6757903</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10365,7 +10360,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10375,7 +10370,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10402,10 +10397,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131805977</v>
+        <v>131806048</v>
       </c>
       <c r="B95" t="n">
-        <v>91832</v>
+        <v>57902</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,34 +10408,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464313</v>
+        <v>464290</v>
       </c>
       <c r="R95" t="n">
-        <v>6757941</v>
+        <v>6758088</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10509,10 +10509,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806052</v>
+        <v>131806032</v>
       </c>
       <c r="B96" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10520,39 +10520,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464193</v>
+        <v>464341</v>
       </c>
       <c r="R96" t="n">
-        <v>6757936</v>
+        <v>6757956</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10584,7 +10579,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10594,7 +10589,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10621,7 +10616,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806032</v>
+        <v>131806030</v>
       </c>
       <c r="B97" t="n">
         <v>79264</v>
@@ -10656,10 +10651,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464341</v>
+        <v>464204</v>
       </c>
       <c r="R97" t="n">
-        <v>6757956</v>
+        <v>6758031</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10691,7 +10686,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10701,7 +10696,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10728,32 +10723,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131806030</v>
+        <v>131805972</v>
       </c>
       <c r="B98" t="n">
-        <v>79264</v>
+        <v>91795</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10763,10 +10758,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464204</v>
+        <v>464074</v>
       </c>
       <c r="R98" t="n">
-        <v>6758031</v>
+        <v>6758064</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10793,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10803,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10835,45 +10830,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131805972</v>
+        <v>131806052</v>
       </c>
       <c r="B99" t="n">
-        <v>91795</v>
+        <v>57902</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464074</v>
+        <v>464193</v>
       </c>
       <c r="R99" t="n">
-        <v>6758064</v>
+        <v>6757936</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11482,10 +11482,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806067</v>
+        <v>131806003</v>
       </c>
       <c r="B105" t="n">
-        <v>5178</v>
+        <v>80405</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11493,39 +11493,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464196</v>
+        <v>464137</v>
       </c>
       <c r="R105" t="n">
-        <v>6757964</v>
+        <v>6758186</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11557,7 +11552,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11567,7 +11562,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11578,6 +11573,21 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11594,10 +11604,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806003</v>
+        <v>131806067</v>
       </c>
       <c r="B106" t="n">
-        <v>80405</v>
+        <v>5178</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11605,34 +11615,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464137</v>
+        <v>464196</v>
       </c>
       <c r="R106" t="n">
-        <v>6758186</v>
+        <v>6757964</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11664,7 +11679,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11674,7 +11689,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11685,21 +11700,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131805990</v>
+        <v>131806061</v>
       </c>
       <c r="B114" t="n">
-        <v>91782</v>
+        <v>57902</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12505,34 +12505,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464391</v>
+        <v>464225</v>
       </c>
       <c r="R114" t="n">
-        <v>6758144</v>
+        <v>6758200</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12564,7 +12569,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12574,7 +12579,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12708,32 +12713,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131805987</v>
+        <v>131805990</v>
       </c>
       <c r="B116" t="n">
-        <v>80398</v>
+        <v>91782</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12743,10 +12748,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464138</v>
+        <v>464391</v>
       </c>
       <c r="R116" t="n">
-        <v>6758188</v>
+        <v>6758144</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12778,7 +12783,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12788,7 +12793,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12799,21 +12804,6 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -12830,10 +12820,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131806039</v>
+        <v>131806004</v>
       </c>
       <c r="B117" t="n">
-        <v>79264</v>
+        <v>81249</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12841,21 +12831,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12865,10 +12855,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464338</v>
+        <v>464261</v>
       </c>
       <c r="R117" t="n">
-        <v>6758168</v>
+        <v>6758029</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12900,7 +12890,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12910,7 +12900,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12937,7 +12927,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131806027</v>
+        <v>131806039</v>
       </c>
       <c r="B118" t="n">
         <v>79264</v>
@@ -12972,10 +12962,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464171</v>
+        <v>464338</v>
       </c>
       <c r="R118" t="n">
-        <v>6757887</v>
+        <v>6758168</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13007,7 +12997,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13017,7 +13007,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13044,7 +13034,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131806033</v>
+        <v>131806027</v>
       </c>
       <c r="B119" t="n">
         <v>79264</v>
@@ -13079,10 +13069,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464363</v>
+        <v>464171</v>
       </c>
       <c r="R119" t="n">
-        <v>6758150</v>
+        <v>6757887</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13114,7 +13104,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13124,7 +13114,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13151,32 +13141,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131806004</v>
+        <v>131805987</v>
       </c>
       <c r="B120" t="n">
-        <v>81249</v>
+        <v>80398</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1049</v>
+        <v>6462</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13186,10 +13176,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464261</v>
+        <v>464138</v>
       </c>
       <c r="R120" t="n">
-        <v>6758029</v>
+        <v>6758188</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13221,7 +13211,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13231,7 +13221,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13242,6 +13232,21 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
@@ -13258,10 +13263,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131806061</v>
+        <v>131806033</v>
       </c>
       <c r="B121" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13269,39 +13274,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464225</v>
+        <v>464363</v>
       </c>
       <c r="R121" t="n">
-        <v>6758200</v>
+        <v>6758150</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131605369</v>
+        <v>131592130</v>
       </c>
       <c r="B7" t="n">
         <v>79264</v>
@@ -1248,22 +1248,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464271</v>
+        <v>464070</v>
       </c>
       <c r="R7" t="n">
-        <v>6757950</v>
+        <v>6758175</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,18 +1292,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131604477</v>
+        <v>131589374</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1336,39 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464463</v>
+        <v>464029</v>
       </c>
       <c r="R8" t="n">
-        <v>6758106</v>
+        <v>6758112</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,11 +1387,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131592130</v>
+        <v>131587086</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,34 +1424,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464070</v>
+        <v>464056</v>
       </c>
       <c r="R9" t="n">
-        <v>6758175</v>
+        <v>6758091</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1515,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131589374</v>
+        <v>131605369</v>
       </c>
       <c r="B10" t="n">
         <v>79264</v>
@@ -1558,19 +1544,22 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464029</v>
+        <v>464271</v>
       </c>
       <c r="R10" t="n">
-        <v>6758112</v>
+        <v>6757950</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,12 +1591,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1626,7 +1621,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131587086</v>
+        <v>131604477</v>
       </c>
       <c r="B11" t="n">
         <v>57902</v>
@@ -1666,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464056</v>
+        <v>464463</v>
       </c>
       <c r="R11" t="n">
-        <v>6758091</v>
+        <v>6758106</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,6 +1697,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131604098</v>
+        <v>131594186</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,39 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464410</v>
+        <v>464035</v>
       </c>
       <c r="R17" t="n">
-        <v>6758165</v>
+        <v>6758187</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131594186</v>
+        <v>131600419</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>79883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2387,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464035</v>
+        <v>464251</v>
       </c>
       <c r="R18" t="n">
-        <v>6758187</v>
+        <v>6758281</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,7 +2422,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131600419</v>
+        <v>131604098</v>
       </c>
       <c r="B19" t="n">
-        <v>79883</v>
+        <v>57902</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,34 +2460,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464251</v>
+        <v>464410</v>
       </c>
       <c r="R19" t="n">
-        <v>6758281</v>
+        <v>6758165</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B20" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,42 +2567,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R20" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,6 +2627,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,37 +2669,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R21" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3362,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131591546</v>
+        <v>131604670</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,34 +3373,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464053</v>
+        <v>464483</v>
       </c>
       <c r="R28" t="n">
-        <v>6758144</v>
+        <v>6758032</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3433,6 +3438,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3459,10 +3469,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131597701</v>
+        <v>131603524</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3470,34 +3480,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464192</v>
+        <v>464384</v>
       </c>
       <c r="R29" t="n">
-        <v>6758156</v>
+        <v>6758179</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3530,6 +3545,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3556,48 +3576,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131594493</v>
+        <v>131600797</v>
       </c>
       <c r="B30" t="n">
-        <v>79264</v>
+        <v>99038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464034</v>
+        <v>464314</v>
       </c>
       <c r="R30" t="n">
-        <v>6758248</v>
+        <v>6758387</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,18 +3653,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3662,53 +3677,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131586714</v>
+        <v>131591546</v>
       </c>
       <c r="B31" t="n">
-        <v>57090</v>
+        <v>79264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464060</v>
+        <v>464053</v>
       </c>
       <c r="R31" t="n">
-        <v>6758044</v>
+        <v>6758144</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3764,10 +3774,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131604670</v>
+        <v>131597701</v>
       </c>
       <c r="B32" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3775,39 +3785,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464483</v>
+        <v>464192</v>
       </c>
       <c r="R32" t="n">
-        <v>6758032</v>
+        <v>6758156</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3840,11 +3845,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3871,10 +3871,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131603524</v>
+        <v>131594493</v>
       </c>
       <c r="B33" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3882,39 +3882,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464384</v>
+        <v>464034</v>
       </c>
       <c r="R33" t="n">
-        <v>6758179</v>
+        <v>6758248</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3951,7 +3949,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>2 bilder, bäck</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3960,6 +3958,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3978,37 +3977,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131600797</v>
+        <v>131586714</v>
       </c>
       <c r="B34" t="n">
-        <v>99038</v>
+        <v>57090</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>95</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4017,13 +4017,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464314</v>
+        <v>464060</v>
       </c>
       <c r="R34" t="n">
-        <v>6758387</v>
+        <v>6758044</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131603322</v>
+        <v>131586494</v>
       </c>
       <c r="B37" t="n">
         <v>79264</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464265</v>
+        <v>464066</v>
       </c>
       <c r="R37" t="n">
-        <v>6758140</v>
+        <v>6757982</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131586494</v>
+        <v>131586581</v>
       </c>
       <c r="B38" t="n">
         <v>79264</v>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464066</v>
+        <v>464051</v>
       </c>
       <c r="R38" t="n">
-        <v>6757982</v>
+        <v>6758034</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4477,7 +4477,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131586581</v>
+        <v>131603322</v>
       </c>
       <c r="B39" t="n">
         <v>79264</v>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464051</v>
+        <v>464265</v>
       </c>
       <c r="R39" t="n">
-        <v>6758034</v>
+        <v>6758140</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4870,10 +4870,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131603971</v>
+        <v>131600551</v>
       </c>
       <c r="B43" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4881,34 +4881,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464384</v>
+        <v>464263</v>
       </c>
       <c r="R43" t="n">
-        <v>6758179</v>
+        <v>6758298</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4941,11 +4946,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4972,7 +4972,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131600551</v>
+        <v>131603307</v>
       </c>
       <c r="B44" t="n">
         <v>57902</v>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464263</v>
+        <v>464265</v>
       </c>
       <c r="R44" t="n">
-        <v>6758298</v>
+        <v>6758140</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5048,6 +5048,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5074,10 +5079,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131603307</v>
+        <v>131600442</v>
       </c>
       <c r="B45" t="n">
-        <v>57902</v>
+        <v>79854</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5085,39 +5090,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464265</v>
+        <v>464251</v>
       </c>
       <c r="R45" t="n">
-        <v>6758140</v>
+        <v>6758281</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5150,11 +5150,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5181,10 +5176,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131600442</v>
+        <v>131603971</v>
       </c>
       <c r="B46" t="n">
-        <v>79854</v>
+        <v>79264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5192,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5216,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464251</v>
+        <v>464384</v>
       </c>
       <c r="R46" t="n">
-        <v>6758281</v>
+        <v>6758179</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5247,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,53 +5278,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131594252</v>
+        <v>131599244</v>
       </c>
       <c r="B47" t="n">
-        <v>57090</v>
+        <v>57899</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464049</v>
+        <v>464210</v>
       </c>
       <c r="R47" t="n">
-        <v>6758189</v>
+        <v>6758193</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5357,6 +5354,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5383,10 +5385,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131599244</v>
+        <v>131586790</v>
       </c>
       <c r="B48" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5394,39 +5396,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464210</v>
+        <v>464046</v>
       </c>
       <c r="R48" t="n">
-        <v>6758193</v>
+        <v>6758049</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5459,11 +5456,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5490,45 +5482,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131586790</v>
+        <v>131594252</v>
       </c>
       <c r="B49" t="n">
-        <v>79264</v>
+        <v>57090</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464046</v>
+        <v>464049</v>
       </c>
       <c r="R49" t="n">
-        <v>6758049</v>
+        <v>6758189</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131605450</v>
+        <v>131586702</v>
       </c>
       <c r="B50" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,40 +5598,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464189</v>
+        <v>464051</v>
       </c>
       <c r="R50" t="n">
-        <v>6757919</v>
+        <v>6758034</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5663,18 +5665,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5689,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131586702</v>
+        <v>131605450</v>
       </c>
       <c r="B51" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5704,42 +5700,40 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464051</v>
+        <v>464189</v>
       </c>
       <c r="R51" t="n">
-        <v>6758034</v>
+        <v>6757919</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5771,12 +5765,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131605468</v>
+        <v>131601417</v>
       </c>
       <c r="B52" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5806,45 +5806,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464189</v>
+        <v>464317</v>
       </c>
       <c r="R52" t="n">
-        <v>6757919</v>
+        <v>6758312</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5900,7 +5892,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131601417</v>
+        <v>131604599</v>
       </c>
       <c r="B53" t="n">
         <v>79264</v>
@@ -5935,13 +5927,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464317</v>
+        <v>464472</v>
       </c>
       <c r="R53" t="n">
-        <v>6758312</v>
+        <v>6758076</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5971,6 +5963,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5997,7 +5994,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131604599</v>
+        <v>131605027</v>
       </c>
       <c r="B54" t="n">
         <v>79264</v>
@@ -6032,10 +6029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464472</v>
+        <v>464394</v>
       </c>
       <c r="R54" t="n">
-        <v>6758076</v>
+        <v>6758039</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6072,7 +6069,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6099,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131605027</v>
+        <v>131605468</v>
       </c>
       <c r="B55" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,34 +6107,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464394</v>
+        <v>464189</v>
       </c>
       <c r="R55" t="n">
-        <v>6758039</v>
+        <v>6757919</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6170,11 +6175,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6298,45 +6298,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131596208</v>
+        <v>131587027</v>
       </c>
       <c r="B57" t="n">
-        <v>79264</v>
+        <v>57090</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464135</v>
+        <v>464056</v>
       </c>
       <c r="R57" t="n">
-        <v>6758234</v>
+        <v>6758091</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6369,6 +6374,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6395,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131595863</v>
+        <v>131586922</v>
       </c>
       <c r="B58" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6406,34 +6416,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464112</v>
+        <v>464054</v>
       </c>
       <c r="R58" t="n">
-        <v>6758222</v>
+        <v>6758066</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6492,38 +6507,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131587027</v>
+        <v>131604358</v>
       </c>
       <c r="B59" t="n">
-        <v>57090</v>
+        <v>57902</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6532,10 +6547,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464056</v>
+        <v>464439</v>
       </c>
       <c r="R59" t="n">
-        <v>6758091</v>
+        <v>6758140</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6572,7 +6587,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Spillning under tjädertall</t>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6599,7 +6614,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131586922</v>
+        <v>131601410</v>
       </c>
       <c r="B60" t="n">
         <v>57902</v>
@@ -6639,10 +6654,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464054</v>
+        <v>464317</v>
       </c>
       <c r="R60" t="n">
-        <v>6758066</v>
+        <v>6758312</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6675,6 +6690,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6701,10 +6721,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131604358</v>
+        <v>131596208</v>
       </c>
       <c r="B61" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6712,39 +6732,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464439</v>
+        <v>464135</v>
       </c>
       <c r="R61" t="n">
-        <v>6758140</v>
+        <v>6758234</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6777,11 +6792,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6808,10 +6818,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131601410</v>
+        <v>131595863</v>
       </c>
       <c r="B62" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6819,39 +6829,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464317</v>
+        <v>464112</v>
       </c>
       <c r="R62" t="n">
-        <v>6758312</v>
+        <v>6758222</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6884,11 +6889,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8767,10 +8767,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131806042</v>
+        <v>131805976</v>
       </c>
       <c r="B80" t="n">
-        <v>79264</v>
+        <v>91832</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8778,21 +8778,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464267</v>
+        <v>464319</v>
       </c>
       <c r="R80" t="n">
-        <v>6758179</v>
+        <v>6757939</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8874,32 +8874,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131806029</v>
+        <v>131805999</v>
       </c>
       <c r="B81" t="n">
-        <v>79264</v>
+        <v>97903</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464204</v>
+        <v>464140</v>
       </c>
       <c r="R81" t="n">
-        <v>6757960</v>
+        <v>6758185</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8981,7 +8981,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131806041</v>
+        <v>131806042</v>
       </c>
       <c r="B82" t="n">
         <v>79264</v>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464305</v>
+        <v>464267</v>
       </c>
       <c r="R82" t="n">
-        <v>6758161</v>
+        <v>6758179</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,10 +9088,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131805976</v>
+        <v>131806029</v>
       </c>
       <c r="B83" t="n">
-        <v>91832</v>
+        <v>79264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9099,21 +9099,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464319</v>
+        <v>464204</v>
       </c>
       <c r="R83" t="n">
-        <v>6757939</v>
+        <v>6757960</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9195,32 +9195,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131805999</v>
+        <v>131806041</v>
       </c>
       <c r="B84" t="n">
-        <v>97903</v>
+        <v>79264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464140</v>
+        <v>464305</v>
       </c>
       <c r="R84" t="n">
-        <v>6758185</v>
+        <v>6758161</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9302,10 +9302,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131805998</v>
+        <v>131806050</v>
       </c>
       <c r="B85" t="n">
-        <v>92131</v>
+        <v>57902</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9313,34 +9313,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464399</v>
+        <v>464143</v>
       </c>
       <c r="R85" t="n">
-        <v>6758179</v>
+        <v>6757875</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9372,7 +9377,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9382,7 +9387,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9409,7 +9414,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131806050</v>
+        <v>131806060</v>
       </c>
       <c r="B86" t="n">
         <v>57902</v>
@@ -9449,10 +9454,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464143</v>
+        <v>464263</v>
       </c>
       <c r="R86" t="n">
-        <v>6757875</v>
+        <v>6758180</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9484,7 +9489,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9494,7 +9499,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9521,7 +9526,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131806060</v>
+        <v>131806049</v>
       </c>
       <c r="B87" t="n">
         <v>57902</v>
@@ -9552,7 +9557,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9561,10 +9566,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464263</v>
+        <v>464099</v>
       </c>
       <c r="R87" t="n">
-        <v>6758180</v>
+        <v>6757847</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9596,7 +9601,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9606,7 +9611,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9633,10 +9638,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131806049</v>
+        <v>131805998</v>
       </c>
       <c r="B88" t="n">
-        <v>57902</v>
+        <v>92131</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9644,39 +9649,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464099</v>
+        <v>464399</v>
       </c>
       <c r="R88" t="n">
-        <v>6757847</v>
+        <v>6758179</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1222,7 +1222,7 @@
         <v>131592130</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>131589374</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>131587086</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131605369</v>
+        <v>131604477</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,40 +1526,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464271</v>
+        <v>464463</v>
       </c>
       <c r="R10" t="n">
-        <v>6757950</v>
+        <v>6758106</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,7 +1595,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,7 +1604,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1621,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131604477</v>
+        <v>131605369</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1632,42 +1633,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464463</v>
+        <v>464271</v>
       </c>
       <c r="R11" t="n">
-        <v>6758106</v>
+        <v>6757950</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1701,7 +1700,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,6 +1709,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>131587093</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131593794</v>
+        <v>131601638</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,34 +1836,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464022</v>
+        <v>464298</v>
       </c>
       <c r="R13" t="n">
-        <v>6758156</v>
+        <v>6758264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1905,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,10 +1932,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131595645</v>
+        <v>131593794</v>
       </c>
       <c r="B14" t="n">
-        <v>83244</v>
+        <v>79266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1938,37 +1943,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464112</v>
+        <v>464022</v>
       </c>
       <c r="R14" t="n">
-        <v>6758222</v>
+        <v>6758156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,7 +2007,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 st Miljöbilder bland annat på en bäck</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,7 +2016,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2033,10 +2034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131586783</v>
+        <v>131595645</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>83246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,31 +2045,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2076,10 +2072,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464041</v>
+        <v>464112</v>
       </c>
       <c r="R15" t="n">
-        <v>6758056</v>
+        <v>6758222</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,12 +2110,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5 st Miljöbilder bland annat på en bäck</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2138,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131601638</v>
+        <v>131586783</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,16 +2151,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2167,21 +2169,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464298</v>
+        <v>464041</v>
       </c>
       <c r="R16" t="n">
-        <v>6758264</v>
+        <v>6758056</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,11 +2219,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,7 +2248,7 @@
         <v>131594186</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131600419</v>
+        <v>131604098</v>
       </c>
       <c r="B18" t="n">
-        <v>79883</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2358,34 +2358,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464251</v>
+        <v>464410</v>
       </c>
       <c r="R18" t="n">
-        <v>6758281</v>
+        <v>6758165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2422,7 +2427,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2449,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131604098</v>
+        <v>131600419</v>
       </c>
       <c r="B19" t="n">
-        <v>57902</v>
+        <v>79885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,39 +2465,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464410</v>
+        <v>464251</v>
       </c>
       <c r="R19" t="n">
-        <v>6758165</v>
+        <v>6758281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,37 +2567,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R20" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2627,11 +2632,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B21" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,42 +2669,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R21" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2734,6 +2729,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2763,7 +2763,7 @@
         <v>131593946</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>131602481</v>
       </c>
       <c r="B23" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>131600576</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131604566</v>
+        <v>131586743</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,39 +3067,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464472</v>
+        <v>464052</v>
       </c>
       <c r="R25" t="n">
-        <v>6758091</v>
+        <v>6758047</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,11 +3127,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131586743</v>
+        <v>131604566</v>
       </c>
       <c r="B26" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,34 +3164,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464052</v>
+        <v>464472</v>
       </c>
       <c r="R26" t="n">
-        <v>6758047</v>
+        <v>6758091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,6 +3229,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3263,7 +3263,7 @@
         <v>131604893</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131604670</v>
+        <v>131591546</v>
       </c>
       <c r="B28" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3373,39 +3373,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464483</v>
+        <v>464053</v>
       </c>
       <c r="R28" t="n">
-        <v>6758032</v>
+        <v>6758144</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,11 +3433,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3469,10 +3459,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131603524</v>
+        <v>131597701</v>
       </c>
       <c r="B29" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3480,39 +3470,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464384</v>
+        <v>464192</v>
       </c>
       <c r="R29" t="n">
-        <v>6758179</v>
+        <v>6758156</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3545,11 +3530,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3576,49 +3556,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131600797</v>
+        <v>131594493</v>
       </c>
       <c r="B30" t="n">
-        <v>99038</v>
+        <v>79266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464314</v>
+        <v>464034</v>
       </c>
       <c r="R30" t="n">
-        <v>6758387</v>
+        <v>6758248</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,12 +3632,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2 bilder, bäck</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3677,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131591546</v>
+        <v>131603524</v>
       </c>
       <c r="B31" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3688,34 +3673,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464053</v>
+        <v>464384</v>
       </c>
       <c r="R31" t="n">
-        <v>6758144</v>
+        <v>6758179</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3748,6 +3738,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3774,10 +3769,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131597701</v>
+        <v>131604670</v>
       </c>
       <c r="B32" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3785,34 +3780,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464192</v>
+        <v>464483</v>
       </c>
       <c r="R32" t="n">
-        <v>6758156</v>
+        <v>6758032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3845,6 +3845,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3871,48 +3876,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131594493</v>
+        <v>131604756</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>57092</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464034</v>
+        <v>464541</v>
       </c>
       <c r="R33" t="n">
-        <v>6758248</v>
+        <v>6758017</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3947,18 +3954,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3980,7 +3981,7 @@
         <v>131586714</v>
       </c>
       <c r="B34" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4079,38 +4080,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131604756</v>
+        <v>131600797</v>
       </c>
       <c r="B35" t="n">
-        <v>57090</v>
+        <v>99044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>95</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464541</v>
+        <v>464314</v>
       </c>
       <c r="R35" t="n">
-        <v>6758017</v>
+        <v>6758387</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>131600974</v>
       </c>
       <c r="B36" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>131586494</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>131586581</v>
       </c>
       <c r="B38" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>131603322</v>
       </c>
       <c r="B39" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>131600594</v>
       </c>
       <c r="B40" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131599422</v>
       </c>
       <c r="B41" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131597848</v>
+        <v>131600551</v>
       </c>
       <c r="B42" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,34 +4784,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464205</v>
+        <v>464263</v>
       </c>
       <c r="R42" t="n">
-        <v>6758160</v>
+        <v>6758298</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,10 +4875,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131600551</v>
+        <v>131603307</v>
       </c>
       <c r="B43" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4910,10 +4915,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464263</v>
+        <v>464265</v>
       </c>
       <c r="R43" t="n">
-        <v>6758298</v>
+        <v>6758140</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4946,6 +4951,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4972,10 +4982,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131603307</v>
+        <v>131603971</v>
       </c>
       <c r="B44" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4983,39 +4993,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464265</v>
+        <v>464384</v>
       </c>
       <c r="R44" t="n">
-        <v>6758140</v>
+        <v>6758179</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5052,7 +5057,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>2 bilder, på tall</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5082,7 +5087,7 @@
         <v>131600442</v>
       </c>
       <c r="B45" t="n">
-        <v>79854</v>
+        <v>79856</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5176,10 +5181,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131603971</v>
+        <v>131597848</v>
       </c>
       <c r="B46" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5211,10 +5216,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464384</v>
+        <v>464205</v>
       </c>
       <c r="R46" t="n">
-        <v>6758179</v>
+        <v>6758160</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5247,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131599244</v>
+        <v>131586790</v>
       </c>
       <c r="B47" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,39 +5289,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464210</v>
+        <v>464046</v>
       </c>
       <c r="R47" t="n">
-        <v>6758193</v>
+        <v>6758049</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5354,11 +5349,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5385,10 +5375,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131586790</v>
+        <v>131599244</v>
       </c>
       <c r="B48" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5396,34 +5386,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464046</v>
+        <v>464210</v>
       </c>
       <c r="R48" t="n">
-        <v>6758049</v>
+        <v>6758193</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5456,6 +5451,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5485,7 +5485,7 @@
         <v>131594252</v>
       </c>
       <c r="B49" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131586702</v>
+        <v>131605450</v>
       </c>
       <c r="B50" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,42 +5598,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464051</v>
+        <v>464189</v>
       </c>
       <c r="R50" t="n">
-        <v>6758034</v>
+        <v>6757919</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5665,12 +5663,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131605450</v>
+        <v>131586702</v>
       </c>
       <c r="B51" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,40 +5704,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464189</v>
+        <v>464051</v>
       </c>
       <c r="R51" t="n">
-        <v>6757919</v>
+        <v>6758034</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5765,18 +5771,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131601417</v>
+        <v>131586572</v>
       </c>
       <c r="B52" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464317</v>
+        <v>464052</v>
       </c>
       <c r="R52" t="n">
-        <v>6758312</v>
+        <v>6758021</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5892,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131604599</v>
+        <v>131605468</v>
       </c>
       <c r="B53" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5903,34 +5903,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464472</v>
+        <v>464189</v>
       </c>
       <c r="R53" t="n">
-        <v>6758076</v>
+        <v>6757919</v>
       </c>
       <c r="S53" t="n">
         <v>50</v>
@@ -5963,11 +5971,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5994,10 +5997,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131605027</v>
+        <v>131601417</v>
       </c>
       <c r="B54" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6029,13 +6032,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464394</v>
+        <v>464317</v>
       </c>
       <c r="R54" t="n">
-        <v>6758039</v>
+        <v>6758312</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6065,11 +6068,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6096,10 +6094,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131605468</v>
+        <v>131604599</v>
       </c>
       <c r="B55" t="n">
-        <v>57899</v>
+        <v>79266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6107,42 +6105,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464189</v>
+        <v>464472</v>
       </c>
       <c r="R55" t="n">
-        <v>6757919</v>
+        <v>6758076</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6175,6 +6165,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6201,10 +6196,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131586572</v>
+        <v>131605027</v>
       </c>
       <c r="B56" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6236,13 +6231,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464052</v>
+        <v>464394</v>
       </c>
       <c r="R56" t="n">
-        <v>6758021</v>
+        <v>6758039</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6272,6 +6267,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6298,50 +6298,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131587027</v>
+        <v>131596208</v>
       </c>
       <c r="B57" t="n">
-        <v>57090</v>
+        <v>79266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464056</v>
+        <v>464135</v>
       </c>
       <c r="R57" t="n">
-        <v>6758091</v>
+        <v>6758234</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6374,11 +6369,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6405,10 +6395,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131586922</v>
+        <v>131595863</v>
       </c>
       <c r="B58" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,39 +6406,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464054</v>
+        <v>464112</v>
       </c>
       <c r="R58" t="n">
-        <v>6758066</v>
+        <v>6758222</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6507,10 +6492,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131604358</v>
+        <v>131601410</v>
       </c>
       <c r="B59" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6538,7 +6523,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6547,10 +6532,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464439</v>
+        <v>464317</v>
       </c>
       <c r="R59" t="n">
-        <v>6758140</v>
+        <v>6758312</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6587,7 +6572,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6614,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131601410</v>
+        <v>131604358</v>
       </c>
       <c r="B60" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6645,7 +6630,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6654,10 +6639,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464317</v>
+        <v>464439</v>
       </c>
       <c r="R60" t="n">
-        <v>6758312</v>
+        <v>6758140</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6694,7 +6679,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>1 bild, ringhack och garn</t>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6721,10 +6706,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131596208</v>
+        <v>131586922</v>
       </c>
       <c r="B61" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6732,34 +6717,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464135</v>
+        <v>464054</v>
       </c>
       <c r="R61" t="n">
-        <v>6758234</v>
+        <v>6758066</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6818,45 +6808,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131595863</v>
+        <v>131587027</v>
       </c>
       <c r="B62" t="n">
-        <v>79264</v>
+        <v>57092</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464112</v>
+        <v>464056</v>
       </c>
       <c r="R62" t="n">
-        <v>6758222</v>
+        <v>6758091</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6889,6 +6884,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6918,7 +6918,7 @@
         <v>131602531</v>
       </c>
       <c r="B63" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>131603229</v>
       </c>
       <c r="B64" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>131806044</v>
       </c>
       <c r="B65" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>131806025</v>
       </c>
       <c r="B66" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>131806001</v>
       </c>
       <c r="B67" t="n">
-        <v>92500</v>
+        <v>92506</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>131806043</v>
       </c>
       <c r="B68" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>131806066</v>
       </c>
       <c r="B69" t="n">
-        <v>78930</v>
+        <v>78932</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>131805997</v>
       </c>
       <c r="B70" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>131805980</v>
       </c>
       <c r="B71" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>131806056</v>
       </c>
       <c r="B72" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>131806028</v>
       </c>
       <c r="B74" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>131806059</v>
       </c>
       <c r="B75" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8319,32 +8319,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131806069</v>
+        <v>131805988</v>
       </c>
       <c r="B76" t="n">
-        <v>91785</v>
+        <v>80400</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4118</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tajgafiberskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fibricium subodoratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst. ex Bourdot &amp; Galzin) Spirin</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464424</v>
+        <v>464189</v>
       </c>
       <c r="R76" t="n">
-        <v>6758134</v>
+        <v>6758149</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8399,17 +8399,32 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8426,10 +8441,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131806068</v>
+        <v>131806038</v>
       </c>
       <c r="B77" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8437,39 +8452,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464196</v>
+        <v>464420</v>
       </c>
       <c r="R77" t="n">
-        <v>6757964</v>
+        <v>6758206</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8501,7 +8511,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8511,7 +8521,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8538,32 +8548,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131806038</v>
+        <v>131806069</v>
       </c>
       <c r="B78" t="n">
-        <v>79264</v>
+        <v>91791</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4118</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tajgafiberskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fibricium subodoratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst. ex Bourdot &amp; Galzin) Spirin</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8573,10 +8583,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464420</v>
+        <v>464424</v>
       </c>
       <c r="R78" t="n">
-        <v>6758206</v>
+        <v>6758134</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8608,7 +8618,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8618,14 +8628,14 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -8645,45 +8655,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131805988</v>
+        <v>131806068</v>
       </c>
       <c r="B79" t="n">
-        <v>80398</v>
+        <v>57904</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464189</v>
+        <v>464196</v>
       </c>
       <c r="R79" t="n">
-        <v>6758149</v>
+        <v>6757964</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8715,7 +8730,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8725,7 +8740,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8736,21 +8751,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -8767,10 +8767,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131805976</v>
+        <v>131806041</v>
       </c>
       <c r="B80" t="n">
-        <v>91832</v>
+        <v>79266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8778,21 +8778,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464319</v>
+        <v>464305</v>
       </c>
       <c r="R80" t="n">
-        <v>6757939</v>
+        <v>6758161</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8877,7 +8877,7 @@
         <v>131805999</v>
       </c>
       <c r="B81" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8981,10 +8981,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131806042</v>
+        <v>131805976</v>
       </c>
       <c r="B82" t="n">
-        <v>79264</v>
+        <v>91838</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8992,21 +8992,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464267</v>
+        <v>464319</v>
       </c>
       <c r="R82" t="n">
-        <v>6758179</v>
+        <v>6757939</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,10 +9088,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131806029</v>
+        <v>131806042</v>
       </c>
       <c r="B83" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464204</v>
+        <v>464267</v>
       </c>
       <c r="R83" t="n">
-        <v>6757960</v>
+        <v>6758179</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9195,10 +9195,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131806041</v>
+        <v>131806029</v>
       </c>
       <c r="B84" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464305</v>
+        <v>464204</v>
       </c>
       <c r="R84" t="n">
-        <v>6758161</v>
+        <v>6757960</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9302,10 +9302,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131806050</v>
+        <v>131805998</v>
       </c>
       <c r="B85" t="n">
-        <v>57902</v>
+        <v>92137</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9313,39 +9313,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464143</v>
+        <v>464399</v>
       </c>
       <c r="R85" t="n">
-        <v>6757875</v>
+        <v>6758179</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9377,7 +9372,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9387,7 +9382,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9417,7 +9412,7 @@
         <v>131806060</v>
       </c>
       <c r="B86" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9526,10 +9521,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131806049</v>
+        <v>131806050</v>
       </c>
       <c r="B87" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9557,7 +9552,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9566,10 +9561,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464099</v>
+        <v>464143</v>
       </c>
       <c r="R87" t="n">
-        <v>6757847</v>
+        <v>6757875</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9601,7 +9596,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9611,7 +9606,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9638,10 +9633,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131805998</v>
+        <v>131806049</v>
       </c>
       <c r="B88" t="n">
-        <v>92131</v>
+        <v>57904</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9649,34 +9644,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464399</v>
+        <v>464099</v>
       </c>
       <c r="R88" t="n">
-        <v>6758179</v>
+        <v>6757847</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9748,7 +9748,7 @@
         <v>131806057</v>
       </c>
       <c r="B89" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>131805982</v>
       </c>
       <c r="B90" t="n">
-        <v>92555</v>
+        <v>92561</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9964,32 +9964,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131805971</v>
+        <v>131806040</v>
       </c>
       <c r="B91" t="n">
-        <v>91795</v>
+        <v>79266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9999,10 +9999,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464201</v>
+        <v>464327</v>
       </c>
       <c r="R91" t="n">
-        <v>6757851</v>
+        <v>6758158</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10071,32 +10071,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131806040</v>
+        <v>131805971</v>
       </c>
       <c r="B92" t="n">
-        <v>79264</v>
+        <v>91801</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10106,10 +10106,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464327</v>
+        <v>464201</v>
       </c>
       <c r="R92" t="n">
-        <v>6758158</v>
+        <v>6757851</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10178,10 +10178,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131805977</v>
+        <v>131806051</v>
       </c>
       <c r="B93" t="n">
-        <v>91832</v>
+        <v>57904</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10189,34 +10189,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464313</v>
+        <v>464172</v>
       </c>
       <c r="R93" t="n">
-        <v>6757941</v>
+        <v>6757903</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10248,7 +10253,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10258,7 +10263,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10285,10 +10290,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131806051</v>
+        <v>131806048</v>
       </c>
       <c r="B94" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10316,7 +10321,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10325,10 +10330,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464172</v>
+        <v>464290</v>
       </c>
       <c r="R94" t="n">
-        <v>6757903</v>
+        <v>6758088</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10360,7 +10365,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10370,7 +10375,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10397,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806048</v>
+        <v>131805977</v>
       </c>
       <c r="B95" t="n">
-        <v>57902</v>
+        <v>91838</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10408,39 +10413,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464290</v>
+        <v>464313</v>
       </c>
       <c r="R95" t="n">
-        <v>6758088</v>
+        <v>6757941</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10509,10 +10509,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806032</v>
+        <v>131806052</v>
       </c>
       <c r="B96" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10520,34 +10520,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464341</v>
+        <v>464193</v>
       </c>
       <c r="R96" t="n">
-        <v>6757956</v>
+        <v>6757936</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10579,7 +10584,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10589,7 +10594,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10616,10 +10621,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806030</v>
+        <v>131806032</v>
       </c>
       <c r="B97" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10651,10 +10656,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464204</v>
+        <v>464341</v>
       </c>
       <c r="R97" t="n">
-        <v>6758031</v>
+        <v>6757956</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10686,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10696,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10723,32 +10728,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131805972</v>
+        <v>131806030</v>
       </c>
       <c r="B98" t="n">
-        <v>91795</v>
+        <v>79266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10758,10 +10763,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464074</v>
+        <v>464204</v>
       </c>
       <c r="R98" t="n">
-        <v>6758064</v>
+        <v>6758031</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10793,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10803,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10830,50 +10835,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131806052</v>
+        <v>131805972</v>
       </c>
       <c r="B99" t="n">
-        <v>57902</v>
+        <v>91801</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464193</v>
+        <v>464074</v>
       </c>
       <c r="R99" t="n">
-        <v>6757936</v>
+        <v>6758064</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10945,7 +10945,7 @@
         <v>131806002</v>
       </c>
       <c r="B100" t="n">
-        <v>79288</v>
+        <v>79290</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>131806000</v>
       </c>
       <c r="B101" t="n">
-        <v>57734</v>
+        <v>57736</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>131806026</v>
       </c>
       <c r="B102" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11268,32 +11268,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131805978</v>
+        <v>131806003</v>
       </c>
       <c r="B103" t="n">
-        <v>91832</v>
+        <v>80407</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11303,10 +11303,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464275</v>
+        <v>464137</v>
       </c>
       <c r="R103" t="n">
-        <v>6758069</v>
+        <v>6758186</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11359,6 +11359,21 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11375,10 +11390,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131806036</v>
+        <v>131805978</v>
       </c>
       <c r="B104" t="n">
-        <v>79264</v>
+        <v>91838</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11386,21 +11401,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11410,10 +11425,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464459</v>
+        <v>464275</v>
       </c>
       <c r="R104" t="n">
-        <v>6758165</v>
+        <v>6758069</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11445,7 +11460,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11455,7 +11470,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11482,10 +11497,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806003</v>
+        <v>131806067</v>
       </c>
       <c r="B105" t="n">
-        <v>80405</v>
+        <v>5178</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11493,34 +11508,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464137</v>
+        <v>464196</v>
       </c>
       <c r="R105" t="n">
-        <v>6758186</v>
+        <v>6757964</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11552,7 +11572,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11562,7 +11582,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11573,21 +11593,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11604,38 +11609,38 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806067</v>
+        <v>131806058</v>
       </c>
       <c r="B106" t="n">
-        <v>5178</v>
+        <v>57904</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11644,10 +11649,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464196</v>
+        <v>464435</v>
       </c>
       <c r="R106" t="n">
-        <v>6757964</v>
+        <v>6758156</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11679,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11689,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11716,10 +11721,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131806058</v>
+        <v>131806036</v>
       </c>
       <c r="B107" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11727,39 +11732,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464435</v>
+        <v>464459</v>
       </c>
       <c r="R107" t="n">
-        <v>6758156</v>
+        <v>6758165</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11831,7 +11831,7 @@
         <v>131805989</v>
       </c>
       <c r="B108" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>131806007</v>
       </c>
       <c r="B109" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>131806037</v>
       </c>
       <c r="B110" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12173,10 +12173,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131805979</v>
+        <v>131806034</v>
       </c>
       <c r="B111" t="n">
-        <v>91832</v>
+        <v>79266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12184,21 +12184,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464400</v>
+        <v>464383</v>
       </c>
       <c r="R111" t="n">
-        <v>6758180</v>
+        <v>6758151</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12280,10 +12280,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131806034</v>
+        <v>131806031</v>
       </c>
       <c r="B112" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464383</v>
+        <v>464219</v>
       </c>
       <c r="R112" t="n">
-        <v>6758151</v>
+        <v>6758055</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12387,10 +12387,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131806031</v>
+        <v>131805979</v>
       </c>
       <c r="B113" t="n">
-        <v>79264</v>
+        <v>91838</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464219</v>
+        <v>464400</v>
       </c>
       <c r="R113" t="n">
-        <v>6758055</v>
+        <v>6758180</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12497,7 +12497,7 @@
         <v>131806061</v>
       </c>
       <c r="B114" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12606,10 +12606,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131805970</v>
+        <v>131805987</v>
       </c>
       <c r="B115" t="n">
-        <v>91795</v>
+        <v>80400</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12617,21 +12617,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12641,10 +12641,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464109</v>
+        <v>464138</v>
       </c>
       <c r="R115" t="n">
-        <v>6757856</v>
+        <v>6758188</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12697,6 +12697,21 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -12713,10 +12728,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131805990</v>
+        <v>131806039</v>
       </c>
       <c r="B116" t="n">
-        <v>91782</v>
+        <v>79266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12724,21 +12739,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12748,10 +12763,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464391</v>
+        <v>464338</v>
       </c>
       <c r="R116" t="n">
-        <v>6758144</v>
+        <v>6758168</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12783,7 +12798,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12793,7 +12808,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12820,10 +12835,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131806004</v>
+        <v>131806027</v>
       </c>
       <c r="B117" t="n">
-        <v>81249</v>
+        <v>79266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12831,21 +12846,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12855,10 +12870,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464261</v>
+        <v>464171</v>
       </c>
       <c r="R117" t="n">
-        <v>6758029</v>
+        <v>6757887</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12890,7 +12905,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12900,7 +12915,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12927,32 +12942,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131806039</v>
+        <v>131805970</v>
       </c>
       <c r="B118" t="n">
-        <v>79264</v>
+        <v>91801</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12962,10 +12977,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464338</v>
+        <v>464109</v>
       </c>
       <c r="R118" t="n">
-        <v>6758168</v>
+        <v>6757856</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12997,7 +13012,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13007,7 +13022,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13034,10 +13049,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131806027</v>
+        <v>131806033</v>
       </c>
       <c r="B119" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13069,10 +13084,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464171</v>
+        <v>464363</v>
       </c>
       <c r="R119" t="n">
-        <v>6757887</v>
+        <v>6758150</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13104,7 +13119,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13114,7 +13129,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13141,32 +13156,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131805987</v>
+        <v>131806035</v>
       </c>
       <c r="B120" t="n">
-        <v>80398</v>
+        <v>79266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13176,10 +13191,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464138</v>
+        <v>464460</v>
       </c>
       <c r="R120" t="n">
-        <v>6758188</v>
+        <v>6758144</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13211,7 +13226,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13221,7 +13236,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13232,21 +13247,6 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
@@ -13263,10 +13263,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131806033</v>
+        <v>131805990</v>
       </c>
       <c r="B121" t="n">
-        <v>79264</v>
+        <v>91788</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13274,21 +13274,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13298,10 +13298,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464363</v>
+        <v>464391</v>
       </c>
       <c r="R121" t="n">
-        <v>6758150</v>
+        <v>6758144</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13370,10 +13370,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131806035</v>
+        <v>131806004</v>
       </c>
       <c r="B122" t="n">
-        <v>79264</v>
+        <v>81251</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13381,21 +13381,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13405,10 +13405,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464460</v>
+        <v>464261</v>
       </c>
       <c r="R122" t="n">
-        <v>6758144</v>
+        <v>6758029</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13440,7 +13440,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD122" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131592130</v>
+        <v>131604477</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,34 +1230,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464070</v>
+        <v>464463</v>
       </c>
       <c r="R7" t="n">
-        <v>6758175</v>
+        <v>6758106</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,6 +1295,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131589374</v>
+        <v>131605369</v>
       </c>
       <c r="B8" t="n">
         <v>79266</v>
@@ -1345,19 +1355,22 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464029</v>
+        <v>464271</v>
       </c>
       <c r="R8" t="n">
-        <v>6758112</v>
+        <v>6757950</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,12 +1402,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1413,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131587086</v>
+        <v>131592130</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1424,39 +1443,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464056</v>
+        <v>464070</v>
       </c>
       <c r="R9" t="n">
-        <v>6758091</v>
+        <v>6758175</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131604477</v>
+        <v>131589374</v>
       </c>
       <c r="B10" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,39 +1540,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464463</v>
+        <v>464029</v>
       </c>
       <c r="R10" t="n">
-        <v>6758106</v>
+        <v>6758112</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,11 +1600,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131605369</v>
+        <v>131587086</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,40 +1637,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464271</v>
+        <v>464056</v>
       </c>
       <c r="R11" t="n">
-        <v>6757950</v>
+        <v>6758091</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1698,18 +1704,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131594186</v>
+        <v>131604098</v>
       </c>
       <c r="B17" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,34 +2256,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464035</v>
+        <v>464410</v>
       </c>
       <c r="R17" t="n">
-        <v>6758187</v>
+        <v>6758165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2325,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131604098</v>
+        <v>131600419</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>79885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2358,39 +2363,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464410</v>
+        <v>464251</v>
       </c>
       <c r="R18" t="n">
-        <v>6758165</v>
+        <v>6758281</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131600419</v>
+        <v>131594186</v>
       </c>
       <c r="B19" t="n">
-        <v>79885</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464251</v>
+        <v>464035</v>
       </c>
       <c r="R19" t="n">
-        <v>6758281</v>
+        <v>6758187</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,42 +2567,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R20" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,6 +2627,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B21" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,37 +2669,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R21" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131586743</v>
+        <v>131604566</v>
       </c>
       <c r="B25" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,34 +3067,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464052</v>
+        <v>464472</v>
       </c>
       <c r="R25" t="n">
-        <v>6758047</v>
+        <v>6758091</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,6 +3132,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3153,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131604566</v>
+        <v>131586743</v>
       </c>
       <c r="B26" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3164,39 +3174,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464472</v>
+        <v>464052</v>
       </c>
       <c r="R26" t="n">
-        <v>6758091</v>
+        <v>6758047</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3229,11 +3234,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3362,45 +3362,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131591546</v>
+        <v>131600797</v>
       </c>
       <c r="B28" t="n">
-        <v>79266</v>
+        <v>99044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464053</v>
+        <v>464314</v>
       </c>
       <c r="R28" t="n">
-        <v>6758144</v>
+        <v>6758387</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3459,7 +3463,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131597701</v>
+        <v>131591546</v>
       </c>
       <c r="B29" t="n">
         <v>79266</v>
@@ -3494,10 +3498,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464192</v>
+        <v>464053</v>
       </c>
       <c r="R29" t="n">
-        <v>6758156</v>
+        <v>6758144</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,7 +3560,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131594493</v>
+        <v>131597701</v>
       </c>
       <c r="B30" t="n">
         <v>79266</v>
@@ -3585,19 +3589,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464034</v>
+        <v>464192</v>
       </c>
       <c r="R30" t="n">
-        <v>6758248</v>
+        <v>6758156</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,18 +3633,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3662,10 +3657,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131603524</v>
+        <v>131594493</v>
       </c>
       <c r="B31" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,39 +3668,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464384</v>
+        <v>464034</v>
       </c>
       <c r="R31" t="n">
-        <v>6758179</v>
+        <v>6758248</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3742,7 +3735,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>2 bilder, bäck</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3751,6 +3744,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3769,38 +3763,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131604670</v>
+        <v>131604756</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>57092</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3809,10 +3803,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464483</v>
+        <v>464541</v>
       </c>
       <c r="R32" t="n">
-        <v>6758032</v>
+        <v>6758017</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3845,11 +3839,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3876,7 +3865,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131604756</v>
+        <v>131586714</v>
       </c>
       <c r="B33" t="n">
         <v>57092</v>
@@ -3916,13 +3905,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464541</v>
+        <v>464060</v>
       </c>
       <c r="R33" t="n">
-        <v>6758017</v>
+        <v>6758044</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3978,38 +3967,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131586714</v>
+        <v>131603524</v>
       </c>
       <c r="B34" t="n">
-        <v>57092</v>
+        <v>57904</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4018,13 +4007,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464060</v>
+        <v>464384</v>
       </c>
       <c r="R34" t="n">
-        <v>6758044</v>
+        <v>6758179</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4054,6 +4043,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4080,37 +4074,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131600797</v>
+        <v>131604670</v>
       </c>
       <c r="B35" t="n">
-        <v>99044</v>
+        <v>57904</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>95</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464314</v>
+        <v>464483</v>
       </c>
       <c r="R35" t="n">
-        <v>6758387</v>
+        <v>6758032</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131600551</v>
+        <v>131597848</v>
       </c>
       <c r="B42" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,39 +4784,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464263</v>
+        <v>464205</v>
       </c>
       <c r="R42" t="n">
-        <v>6758298</v>
+        <v>6758160</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4875,10 +4870,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131603307</v>
+        <v>131600442</v>
       </c>
       <c r="B43" t="n">
-        <v>57904</v>
+        <v>79856</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4886,39 +4881,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464265</v>
+        <v>464251</v>
       </c>
       <c r="R43" t="n">
-        <v>6758140</v>
+        <v>6758281</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,11 +4941,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4982,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131603971</v>
+        <v>131600551</v>
       </c>
       <c r="B44" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4993,34 +4978,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464384</v>
+        <v>464263</v>
       </c>
       <c r="R44" t="n">
-        <v>6758179</v>
+        <v>6758298</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,11 +5043,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5084,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131600442</v>
+        <v>131603307</v>
       </c>
       <c r="B45" t="n">
-        <v>79856</v>
+        <v>57904</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5095,34 +5080,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464251</v>
+        <v>464265</v>
       </c>
       <c r="R45" t="n">
-        <v>6758281</v>
+        <v>6758140</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,6 +5145,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5181,7 +5176,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131597848</v>
+        <v>131603971</v>
       </c>
       <c r="B46" t="n">
         <v>79266</v>
@@ -5216,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464205</v>
+        <v>464384</v>
       </c>
       <c r="R46" t="n">
-        <v>6758160</v>
+        <v>6758179</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5247,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131586790</v>
+        <v>131599244</v>
       </c>
       <c r="B47" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,34 +5289,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464046</v>
+        <v>464210</v>
       </c>
       <c r="R47" t="n">
-        <v>6758049</v>
+        <v>6758193</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5349,6 +5354,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5375,50 +5385,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131599244</v>
+        <v>131594252</v>
       </c>
       <c r="B48" t="n">
-        <v>57901</v>
+        <v>57092</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464210</v>
+        <v>464049</v>
       </c>
       <c r="R48" t="n">
-        <v>6758193</v>
+        <v>6758189</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,11 +5464,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5482,53 +5490,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131594252</v>
+        <v>131586790</v>
       </c>
       <c r="B49" t="n">
-        <v>57092</v>
+        <v>79266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464049</v>
+        <v>464046</v>
       </c>
       <c r="R49" t="n">
-        <v>6758189</v>
+        <v>6758049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7662,45 +7662,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131805997</v>
+        <v>131806056</v>
       </c>
       <c r="B70" t="n">
-        <v>92298</v>
+        <v>57904</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464284</v>
+        <v>464295</v>
       </c>
       <c r="R70" t="n">
-        <v>6758164</v>
+        <v>6757996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7732,7 +7737,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7742,7 +7747,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7769,45 +7774,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131805980</v>
+        <v>131805986</v>
       </c>
       <c r="B71" t="n">
-        <v>91838</v>
+        <v>4774</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464132</v>
+        <v>464254</v>
       </c>
       <c r="R71" t="n">
-        <v>6757988</v>
+        <v>6758196</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7839,7 +7849,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7849,7 +7859,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7876,50 +7886,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131806056</v>
+        <v>131805997</v>
       </c>
       <c r="B72" t="n">
-        <v>57904</v>
+        <v>92298</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464295</v>
+        <v>464284</v>
       </c>
       <c r="R72" t="n">
-        <v>6757996</v>
+        <v>6758164</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7951,7 +7956,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7961,7 +7966,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,50 +7993,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131805986</v>
+        <v>131805980</v>
       </c>
       <c r="B73" t="n">
-        <v>4774</v>
+        <v>91838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464254</v>
+        <v>464132</v>
       </c>
       <c r="R73" t="n">
-        <v>6758196</v>
+        <v>6757988</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10509,10 +10509,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806052</v>
+        <v>131806032</v>
       </c>
       <c r="B96" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10520,39 +10520,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464193</v>
+        <v>464341</v>
       </c>
       <c r="R96" t="n">
-        <v>6757936</v>
+        <v>6757956</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10584,7 +10579,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10594,7 +10589,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10621,7 +10616,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806032</v>
+        <v>131806030</v>
       </c>
       <c r="B97" t="n">
         <v>79266</v>
@@ -10656,10 +10651,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464341</v>
+        <v>464204</v>
       </c>
       <c r="R97" t="n">
-        <v>6757956</v>
+        <v>6758031</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10691,7 +10686,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10701,7 +10696,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10728,32 +10723,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131806030</v>
+        <v>131805972</v>
       </c>
       <c r="B98" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10763,10 +10758,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464204</v>
+        <v>464074</v>
       </c>
       <c r="R98" t="n">
-        <v>6758031</v>
+        <v>6758064</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10793,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10803,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10835,45 +10830,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131805972</v>
+        <v>131806052</v>
       </c>
       <c r="B99" t="n">
-        <v>91801</v>
+        <v>57904</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464074</v>
+        <v>464193</v>
       </c>
       <c r="R99" t="n">
-        <v>6758064</v>
+        <v>6757936</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131604566</v>
+        <v>131586743</v>
       </c>
       <c r="B25" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,39 +3067,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464472</v>
+        <v>464052</v>
       </c>
       <c r="R25" t="n">
-        <v>6758091</v>
+        <v>6758047</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,11 +3127,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131586743</v>
+        <v>131604566</v>
       </c>
       <c r="B26" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,34 +3164,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464052</v>
+        <v>464472</v>
       </c>
       <c r="R26" t="n">
-        <v>6758047</v>
+        <v>6758091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,6 +3229,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3362,49 +3362,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131600797</v>
+        <v>131591546</v>
       </c>
       <c r="B28" t="n">
-        <v>99044</v>
+        <v>79266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464314</v>
+        <v>464053</v>
       </c>
       <c r="R28" t="n">
-        <v>6758387</v>
+        <v>6758144</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,7 +3459,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131591546</v>
+        <v>131597701</v>
       </c>
       <c r="B29" t="n">
         <v>79266</v>
@@ -3498,10 +3494,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464053</v>
+        <v>464192</v>
       </c>
       <c r="R29" t="n">
-        <v>6758144</v>
+        <v>6758156</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3560,7 +3556,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131597701</v>
+        <v>131594493</v>
       </c>
       <c r="B30" t="n">
         <v>79266</v>
@@ -3589,16 +3585,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464192</v>
+        <v>464034</v>
       </c>
       <c r="R30" t="n">
-        <v>6758156</v>
+        <v>6758248</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,12 +3632,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2 bilder, bäck</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3657,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131594493</v>
+        <v>131603524</v>
       </c>
       <c r="B31" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3668,37 +3673,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464034</v>
+        <v>464384</v>
       </c>
       <c r="R31" t="n">
-        <v>6758248</v>
+        <v>6758179</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,7 +3742,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2 bilder, bäck</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3744,7 +3751,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3763,38 +3769,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131604756</v>
+        <v>131604670</v>
       </c>
       <c r="B32" t="n">
-        <v>57092</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3803,10 +3809,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464541</v>
+        <v>464483</v>
       </c>
       <c r="R32" t="n">
-        <v>6758017</v>
+        <v>6758032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,6 +3845,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,7 +3876,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131586714</v>
+        <v>131604756</v>
       </c>
       <c r="B33" t="n">
         <v>57092</v>
@@ -3905,13 +3916,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464060</v>
+        <v>464541</v>
       </c>
       <c r="R33" t="n">
-        <v>6758044</v>
+        <v>6758017</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3967,38 +3978,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131603524</v>
+        <v>131586714</v>
       </c>
       <c r="B34" t="n">
-        <v>57904</v>
+        <v>57092</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4007,13 +4018,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464384</v>
+        <v>464060</v>
       </c>
       <c r="R34" t="n">
-        <v>6758179</v>
+        <v>6758044</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4043,11 +4054,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4074,38 +4080,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131604670</v>
+        <v>131600797</v>
       </c>
       <c r="B35" t="n">
-        <v>57904</v>
+        <v>99044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>95</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4114,10 +4119,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464483</v>
+        <v>464314</v>
       </c>
       <c r="R35" t="n">
-        <v>6758032</v>
+        <v>6758387</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4150,11 +4155,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131597848</v>
+        <v>131600551</v>
       </c>
       <c r="B42" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,34 +4784,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464205</v>
+        <v>464263</v>
       </c>
       <c r="R42" t="n">
-        <v>6758160</v>
+        <v>6758298</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,10 +4875,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131600442</v>
+        <v>131603307</v>
       </c>
       <c r="B43" t="n">
-        <v>79856</v>
+        <v>57904</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4881,34 +4886,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464251</v>
+        <v>464265</v>
       </c>
       <c r="R43" t="n">
-        <v>6758281</v>
+        <v>6758140</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4941,6 +4951,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4967,10 +4982,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131600551</v>
+        <v>131603971</v>
       </c>
       <c r="B44" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4978,39 +4993,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464263</v>
+        <v>464384</v>
       </c>
       <c r="R44" t="n">
-        <v>6758298</v>
+        <v>6758179</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5043,6 +5053,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5084,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131603307</v>
+        <v>131600442</v>
       </c>
       <c r="B45" t="n">
-        <v>57904</v>
+        <v>79856</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5080,39 +5095,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464265</v>
+        <v>464251</v>
       </c>
       <c r="R45" t="n">
-        <v>6758140</v>
+        <v>6758281</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5145,11 +5155,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5176,7 +5181,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131603971</v>
+        <v>131597848</v>
       </c>
       <c r="B46" t="n">
         <v>79266</v>
@@ -5211,10 +5216,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464384</v>
+        <v>464205</v>
       </c>
       <c r="R46" t="n">
-        <v>6758179</v>
+        <v>6758160</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5247,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131599244</v>
+        <v>131586790</v>
       </c>
       <c r="B47" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,39 +5289,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464210</v>
+        <v>464046</v>
       </c>
       <c r="R47" t="n">
-        <v>6758193</v>
+        <v>6758049</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5354,11 +5349,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5385,53 +5375,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131594252</v>
+        <v>131599244</v>
       </c>
       <c r="B48" t="n">
-        <v>57092</v>
+        <v>57901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464049</v>
+        <v>464210</v>
       </c>
       <c r="R48" t="n">
-        <v>6758189</v>
+        <v>6758193</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5464,6 +5451,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5490,45 +5482,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131586790</v>
+        <v>131594252</v>
       </c>
       <c r="B49" t="n">
-        <v>79266</v>
+        <v>57092</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464046</v>
+        <v>464049</v>
       </c>
       <c r="R49" t="n">
-        <v>6758049</v>
+        <v>6758189</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7662,50 +7662,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131806056</v>
+        <v>131805997</v>
       </c>
       <c r="B70" t="n">
-        <v>57904</v>
+        <v>92298</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464295</v>
+        <v>464284</v>
       </c>
       <c r="R70" t="n">
-        <v>6757996</v>
+        <v>6758164</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7737,7 +7732,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7747,7 +7742,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7774,50 +7769,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131805986</v>
+        <v>131805980</v>
       </c>
       <c r="B71" t="n">
-        <v>4774</v>
+        <v>91838</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464254</v>
+        <v>464132</v>
       </c>
       <c r="R71" t="n">
-        <v>6758196</v>
+        <v>6757988</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7849,7 +7839,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7859,7 +7849,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,45 +7876,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131805997</v>
+        <v>131806056</v>
       </c>
       <c r="B72" t="n">
-        <v>92298</v>
+        <v>57904</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464284</v>
+        <v>464295</v>
       </c>
       <c r="R72" t="n">
-        <v>6758164</v>
+        <v>6757996</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7956,7 +7951,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7966,7 +7961,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7993,45 +7988,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131805980</v>
+        <v>131805986</v>
       </c>
       <c r="B73" t="n">
-        <v>91838</v>
+        <v>4774</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464132</v>
+        <v>464254</v>
       </c>
       <c r="R73" t="n">
-        <v>6757988</v>
+        <v>6758196</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8874,32 +8874,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131805999</v>
+        <v>131806042</v>
       </c>
       <c r="B81" t="n">
-        <v>97909</v>
+        <v>79266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464140</v>
+        <v>464267</v>
       </c>
       <c r="R81" t="n">
-        <v>6758185</v>
+        <v>6758179</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8981,10 +8981,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131805976</v>
+        <v>131806029</v>
       </c>
       <c r="B82" t="n">
-        <v>91838</v>
+        <v>79266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8992,21 +8992,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464319</v>
+        <v>464204</v>
       </c>
       <c r="R82" t="n">
-        <v>6757939</v>
+        <v>6757960</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,10 +9088,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131806042</v>
+        <v>131805976</v>
       </c>
       <c r="B83" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9099,21 +9099,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464267</v>
+        <v>464319</v>
       </c>
       <c r="R83" t="n">
-        <v>6758179</v>
+        <v>6757939</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9195,32 +9195,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131806029</v>
+        <v>131805999</v>
       </c>
       <c r="B84" t="n">
-        <v>79266</v>
+        <v>97909</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464204</v>
+        <v>464140</v>
       </c>
       <c r="R84" t="n">
-        <v>6757960</v>
+        <v>6758185</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10178,10 +10178,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131806051</v>
+        <v>131805977</v>
       </c>
       <c r="B93" t="n">
-        <v>57904</v>
+        <v>91838</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10189,39 +10189,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464172</v>
+        <v>464313</v>
       </c>
       <c r="R93" t="n">
-        <v>6757903</v>
+        <v>6757941</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10253,7 +10248,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10263,7 +10258,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10290,7 +10285,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131806048</v>
+        <v>131806051</v>
       </c>
       <c r="B94" t="n">
         <v>57904</v>
@@ -10321,7 +10316,7 @@
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10330,10 +10325,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464290</v>
+        <v>464172</v>
       </c>
       <c r="R94" t="n">
-        <v>6758088</v>
+        <v>6757903</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10365,7 +10360,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10375,7 +10370,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10402,10 +10397,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131805977</v>
+        <v>131806048</v>
       </c>
       <c r="B95" t="n">
-        <v>91838</v>
+        <v>57904</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,34 +10408,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464313</v>
+        <v>464290</v>
       </c>
       <c r="R95" t="n">
-        <v>6757941</v>
+        <v>6758088</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10509,10 +10509,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806032</v>
+        <v>131806052</v>
       </c>
       <c r="B96" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10520,34 +10520,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464341</v>
+        <v>464193</v>
       </c>
       <c r="R96" t="n">
-        <v>6757956</v>
+        <v>6757936</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10579,7 +10584,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10589,7 +10594,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10616,7 +10621,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806030</v>
+        <v>131806032</v>
       </c>
       <c r="B97" t="n">
         <v>79266</v>
@@ -10651,10 +10656,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464204</v>
+        <v>464341</v>
       </c>
       <c r="R97" t="n">
-        <v>6758031</v>
+        <v>6757956</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10686,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10696,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10723,32 +10728,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131805972</v>
+        <v>131806030</v>
       </c>
       <c r="B98" t="n">
-        <v>91801</v>
+        <v>79266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10758,10 +10763,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464074</v>
+        <v>464204</v>
       </c>
       <c r="R98" t="n">
-        <v>6758064</v>
+        <v>6758031</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10793,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10803,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10830,50 +10835,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131806052</v>
+        <v>131805972</v>
       </c>
       <c r="B99" t="n">
-        <v>57904</v>
+        <v>91801</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464193</v>
+        <v>464074</v>
       </c>
       <c r="R99" t="n">
-        <v>6757936</v>
+        <v>6758064</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131806061</v>
+        <v>131806039</v>
       </c>
       <c r="B114" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12505,39 +12505,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464225</v>
+        <v>464338</v>
       </c>
       <c r="R114" t="n">
-        <v>6758200</v>
+        <v>6758168</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12569,7 +12564,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12579,7 +12574,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12606,32 +12601,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131805987</v>
+        <v>131806027</v>
       </c>
       <c r="B115" t="n">
-        <v>80400</v>
+        <v>79266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12641,10 +12636,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464138</v>
+        <v>464171</v>
       </c>
       <c r="R115" t="n">
-        <v>6758188</v>
+        <v>6757887</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12676,7 +12671,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12686,7 +12681,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12697,21 +12692,6 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -12728,32 +12708,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131806039</v>
+        <v>131805970</v>
       </c>
       <c r="B116" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12763,10 +12743,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464338</v>
+        <v>464109</v>
       </c>
       <c r="R116" t="n">
-        <v>6758168</v>
+        <v>6757856</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12798,7 +12778,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12808,7 +12788,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12835,7 +12815,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131806027</v>
+        <v>131806033</v>
       </c>
       <c r="B117" t="n">
         <v>79266</v>
@@ -12870,10 +12850,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464171</v>
+        <v>464363</v>
       </c>
       <c r="R117" t="n">
-        <v>6757887</v>
+        <v>6758150</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12905,7 +12885,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12915,7 +12895,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12942,32 +12922,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131805970</v>
+        <v>131806035</v>
       </c>
       <c r="B118" t="n">
-        <v>91801</v>
+        <v>79266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12977,10 +12957,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464109</v>
+        <v>464460</v>
       </c>
       <c r="R118" t="n">
-        <v>6757856</v>
+        <v>6758144</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13012,7 +12992,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13022,7 +13002,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13049,32 +13029,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131806033</v>
+        <v>131805987</v>
       </c>
       <c r="B119" t="n">
-        <v>79266</v>
+        <v>80400</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13084,10 +13064,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464363</v>
+        <v>464138</v>
       </c>
       <c r="R119" t="n">
-        <v>6758150</v>
+        <v>6758188</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13119,7 +13099,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13129,7 +13109,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13140,6 +13120,21 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -13156,10 +13151,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131806035</v>
+        <v>131805990</v>
       </c>
       <c r="B120" t="n">
-        <v>79266</v>
+        <v>91788</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13167,21 +13162,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13191,7 +13186,7 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464460</v>
+        <v>464391</v>
       </c>
       <c r="R120" t="n">
         <v>6758144</v>
@@ -13226,7 +13221,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13236,7 +13231,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13263,10 +13258,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131805990</v>
+        <v>131806004</v>
       </c>
       <c r="B121" t="n">
-        <v>91788</v>
+        <v>81251</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13274,21 +13269,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>112</v>
+        <v>1049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13298,10 +13293,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464391</v>
+        <v>464261</v>
       </c>
       <c r="R121" t="n">
-        <v>6758144</v>
+        <v>6758029</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13333,7 +13328,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13343,7 +13338,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13370,10 +13365,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131806004</v>
+        <v>131806061</v>
       </c>
       <c r="B122" t="n">
-        <v>81251</v>
+        <v>57904</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13381,34 +13376,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464261</v>
+        <v>464225</v>
       </c>
       <c r="R122" t="n">
-        <v>6758029</v>
+        <v>6758200</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13440,7 +13440,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD122" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,37 +2567,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R20" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2627,11 +2632,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,42 +2669,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R21" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2734,6 +2729,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -5278,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131586790</v>
+        <v>131599244</v>
       </c>
       <c r="B47" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,34 +5289,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464046</v>
+        <v>464210</v>
       </c>
       <c r="R47" t="n">
-        <v>6758049</v>
+        <v>6758193</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5349,6 +5354,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5375,50 +5385,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131599244</v>
+        <v>131594252</v>
       </c>
       <c r="B48" t="n">
-        <v>57901</v>
+        <v>57092</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464210</v>
+        <v>464049</v>
       </c>
       <c r="R48" t="n">
-        <v>6758193</v>
+        <v>6758189</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,11 +5464,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5482,53 +5490,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131594252</v>
+        <v>131586790</v>
       </c>
       <c r="B49" t="n">
-        <v>57092</v>
+        <v>79266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464049</v>
+        <v>464046</v>
       </c>
       <c r="R49" t="n">
-        <v>6758189</v>
+        <v>6758049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7127,32 +7127,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131806044</v>
+        <v>131806001</v>
       </c>
       <c r="B65" t="n">
-        <v>79266</v>
+        <v>92506</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106596</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464091</v>
+        <v>464428</v>
       </c>
       <c r="R65" t="n">
-        <v>6758171</v>
+        <v>6758134</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7234,7 +7234,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131806025</v>
+        <v>131806044</v>
       </c>
       <c r="B66" t="n">
         <v>79266</v>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464116</v>
+        <v>464091</v>
       </c>
       <c r="R66" t="n">
-        <v>6757815</v>
+        <v>6758171</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7341,32 +7341,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131806001</v>
+        <v>131806025</v>
       </c>
       <c r="B67" t="n">
-        <v>92506</v>
+        <v>79266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106596</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordlig parasitporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464428</v>
+        <v>464116</v>
       </c>
       <c r="R67" t="n">
-        <v>6758134</v>
+        <v>6757815</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8548,45 +8548,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131806069</v>
+        <v>131806068</v>
       </c>
       <c r="B78" t="n">
-        <v>91791</v>
+        <v>57904</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4118</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tajgafiberskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fibricium subodoratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst. ex Bourdot &amp; Galzin) Spirin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464424</v>
+        <v>464196</v>
       </c>
       <c r="R78" t="n">
-        <v>6758134</v>
+        <v>6757964</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8618,7 +8623,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8628,14 +8633,14 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -8655,10 +8660,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131806068</v>
+        <v>131806041</v>
       </c>
       <c r="B79" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8666,39 +8671,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464196</v>
+        <v>464305</v>
       </c>
       <c r="R79" t="n">
-        <v>6757964</v>
+        <v>6758161</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8767,7 +8767,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131806041</v>
+        <v>131806042</v>
       </c>
       <c r="B80" t="n">
         <v>79266</v>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464305</v>
+        <v>464267</v>
       </c>
       <c r="R80" t="n">
-        <v>6758161</v>
+        <v>6758179</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8874,7 +8874,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131806042</v>
+        <v>131806029</v>
       </c>
       <c r="B81" t="n">
         <v>79266</v>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464267</v>
+        <v>464204</v>
       </c>
       <c r="R81" t="n">
-        <v>6758179</v>
+        <v>6757960</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8981,10 +8981,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131806029</v>
+        <v>131805976</v>
       </c>
       <c r="B82" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8992,21 +8992,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464204</v>
+        <v>464319</v>
       </c>
       <c r="R82" t="n">
-        <v>6757960</v>
+        <v>6757939</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,32 +9088,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131805976</v>
+        <v>131805999</v>
       </c>
       <c r="B83" t="n">
-        <v>91838</v>
+        <v>97909</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464319</v>
+        <v>464140</v>
       </c>
       <c r="R83" t="n">
-        <v>6757939</v>
+        <v>6758185</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9195,32 +9195,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131805999</v>
+        <v>131805998</v>
       </c>
       <c r="B84" t="n">
-        <v>97909</v>
+        <v>92137</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9230,10 +9230,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464140</v>
+        <v>464399</v>
       </c>
       <c r="R84" t="n">
-        <v>6758185</v>
+        <v>6758179</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9302,10 +9302,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131805998</v>
+        <v>131806060</v>
       </c>
       <c r="B85" t="n">
-        <v>92137</v>
+        <v>57904</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9313,34 +9313,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464399</v>
+        <v>464263</v>
       </c>
       <c r="R85" t="n">
-        <v>6758179</v>
+        <v>6758180</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9372,7 +9377,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9382,7 +9387,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9409,7 +9414,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131806060</v>
+        <v>131806050</v>
       </c>
       <c r="B86" t="n">
         <v>57904</v>
@@ -9449,10 +9454,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464263</v>
+        <v>464143</v>
       </c>
       <c r="R86" t="n">
-        <v>6758180</v>
+        <v>6757875</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9484,7 +9489,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9494,7 +9499,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9521,7 +9526,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131806050</v>
+        <v>131806049</v>
       </c>
       <c r="B87" t="n">
         <v>57904</v>
@@ -9552,7 +9557,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9561,10 +9566,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464143</v>
+        <v>464099</v>
       </c>
       <c r="R87" t="n">
-        <v>6757875</v>
+        <v>6757847</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9596,7 +9601,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9606,7 +9611,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9633,7 +9638,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131806049</v>
+        <v>131806057</v>
       </c>
       <c r="B88" t="n">
         <v>57904</v>
@@ -9664,7 +9669,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9673,10 +9678,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464099</v>
+        <v>464303</v>
       </c>
       <c r="R88" t="n">
-        <v>6757847</v>
+        <v>6758002</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9708,7 +9713,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9718,7 +9723,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9745,50 +9750,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131806057</v>
+        <v>131805982</v>
       </c>
       <c r="B89" t="n">
-        <v>57904</v>
+        <v>92561</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464303</v>
+        <v>464275</v>
       </c>
       <c r="R89" t="n">
-        <v>6758002</v>
+        <v>6758081</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9857,32 +9857,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131805982</v>
+        <v>131806040</v>
       </c>
       <c r="B90" t="n">
-        <v>92561</v>
+        <v>79266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464275</v>
+        <v>464327</v>
       </c>
       <c r="R90" t="n">
-        <v>6758081</v>
+        <v>6758158</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9964,32 +9964,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131806040</v>
+        <v>131805971</v>
       </c>
       <c r="B91" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9999,10 +9999,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464327</v>
+        <v>464201</v>
       </c>
       <c r="R91" t="n">
-        <v>6758158</v>
+        <v>6757851</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10071,45 +10071,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131805971</v>
+        <v>131806051</v>
       </c>
       <c r="B92" t="n">
-        <v>91801</v>
+        <v>57904</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464201</v>
+        <v>464172</v>
       </c>
       <c r="R92" t="n">
-        <v>6757851</v>
+        <v>6757903</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10141,7 +10146,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10151,7 +10156,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10178,10 +10183,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131805977</v>
+        <v>131806048</v>
       </c>
       <c r="B93" t="n">
-        <v>91838</v>
+        <v>57904</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10189,34 +10194,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464313</v>
+        <v>464290</v>
       </c>
       <c r="R93" t="n">
-        <v>6757941</v>
+        <v>6758088</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10248,7 +10258,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10258,7 +10268,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10285,10 +10295,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131806051</v>
+        <v>131805977</v>
       </c>
       <c r="B94" t="n">
-        <v>57904</v>
+        <v>91838</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10296,39 +10306,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464172</v>
+        <v>464313</v>
       </c>
       <c r="R94" t="n">
-        <v>6757903</v>
+        <v>6757941</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10360,7 +10365,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10370,7 +10375,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10397,7 +10402,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806048</v>
+        <v>131806052</v>
       </c>
       <c r="B95" t="n">
         <v>57904</v>
@@ -10428,7 +10433,7 @@
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10437,10 +10442,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464290</v>
+        <v>464193</v>
       </c>
       <c r="R95" t="n">
-        <v>6758088</v>
+        <v>6757936</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,7 +10477,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10482,7 +10487,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10509,10 +10514,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806052</v>
+        <v>131806032</v>
       </c>
       <c r="B96" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10520,39 +10525,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464193</v>
+        <v>464341</v>
       </c>
       <c r="R96" t="n">
-        <v>6757936</v>
+        <v>6757956</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10621,7 +10621,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806032</v>
+        <v>131806030</v>
       </c>
       <c r="B97" t="n">
         <v>79266</v>
@@ -10656,10 +10656,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464341</v>
+        <v>464204</v>
       </c>
       <c r="R97" t="n">
-        <v>6757956</v>
+        <v>6758031</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10728,32 +10728,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131806030</v>
+        <v>131805972</v>
       </c>
       <c r="B98" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464204</v>
+        <v>464074</v>
       </c>
       <c r="R98" t="n">
-        <v>6758031</v>
+        <v>6758064</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10835,10 +10835,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131805972</v>
+        <v>131806002</v>
       </c>
       <c r="B99" t="n">
-        <v>91801</v>
+        <v>79290</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10846,21 +10846,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10870,10 +10870,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464074</v>
+        <v>464113</v>
       </c>
       <c r="R99" t="n">
-        <v>6758064</v>
+        <v>6757861</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10942,10 +10942,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131806002</v>
+        <v>131806000</v>
       </c>
       <c r="B100" t="n">
-        <v>79290</v>
+        <v>57736</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10953,34 +10953,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6434</v>
+        <v>102622</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464113</v>
+        <v>464154</v>
       </c>
       <c r="R100" t="n">
-        <v>6757861</v>
+        <v>6758193</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11012,7 +11017,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11022,7 +11027,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11049,50 +11054,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131806000</v>
+        <v>131806026</v>
       </c>
       <c r="B101" t="n">
-        <v>57736</v>
+        <v>79266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>102622</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>464154</v>
+        <v>464158</v>
       </c>
       <c r="R101" t="n">
-        <v>6758193</v>
+        <v>6757887</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11161,32 +11161,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131806026</v>
+        <v>131806003</v>
       </c>
       <c r="B102" t="n">
-        <v>79266</v>
+        <v>80407</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464158</v>
+        <v>464137</v>
       </c>
       <c r="R102" t="n">
-        <v>6757887</v>
+        <v>6758186</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11252,6 +11252,21 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11268,32 +11283,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131806003</v>
+        <v>131805978</v>
       </c>
       <c r="B103" t="n">
-        <v>80407</v>
+        <v>91838</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11303,10 +11318,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464137</v>
+        <v>464275</v>
       </c>
       <c r="R103" t="n">
-        <v>6758186</v>
+        <v>6758069</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11338,7 +11353,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11348,7 +11363,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11359,21 +11374,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11390,45 +11390,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131805978</v>
+        <v>131806067</v>
       </c>
       <c r="B104" t="n">
-        <v>91838</v>
+        <v>5178</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464275</v>
+        <v>464196</v>
       </c>
       <c r="R104" t="n">
-        <v>6758069</v>
+        <v>6757964</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11460,7 +11465,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11470,7 +11475,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11497,38 +11502,38 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806067</v>
+        <v>131806058</v>
       </c>
       <c r="B105" t="n">
-        <v>5178</v>
+        <v>57904</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11537,10 +11542,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464196</v>
+        <v>464435</v>
       </c>
       <c r="R105" t="n">
-        <v>6757964</v>
+        <v>6758156</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11572,7 +11577,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11582,7 +11587,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11609,10 +11614,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806058</v>
+        <v>131806036</v>
       </c>
       <c r="B106" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11620,39 +11625,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464435</v>
+        <v>464459</v>
       </c>
       <c r="R106" t="n">
-        <v>6758156</v>
+        <v>6758165</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11721,32 +11721,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131806036</v>
+        <v>131805989</v>
       </c>
       <c r="B107" t="n">
-        <v>79266</v>
+        <v>80400</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11756,10 +11756,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464459</v>
+        <v>464196</v>
       </c>
       <c r="R107" t="n">
-        <v>6758165</v>
+        <v>6758006</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11812,6 +11812,21 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11828,45 +11843,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131805989</v>
+        <v>131806007</v>
       </c>
       <c r="B108" t="n">
-        <v>80400</v>
+        <v>99044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464196</v>
+        <v>464255</v>
       </c>
       <c r="R108" t="n">
-        <v>6758006</v>
+        <v>6758034</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11898,7 +11922,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11908,7 +11932,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11919,21 +11943,6 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -11950,54 +11959,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>131806007</v>
+        <v>131806037</v>
       </c>
       <c r="B109" t="n">
-        <v>99044</v>
+        <v>79266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>464255</v>
+        <v>464449</v>
       </c>
       <c r="R109" t="n">
-        <v>6758034</v>
+        <v>6758165</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12066,7 +12066,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131806037</v>
+        <v>131806034</v>
       </c>
       <c r="B110" t="n">
         <v>79266</v>
@@ -12101,10 +12101,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464449</v>
+        <v>464383</v>
       </c>
       <c r="R110" t="n">
-        <v>6758165</v>
+        <v>6758151</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12173,7 +12173,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131806034</v>
+        <v>131806031</v>
       </c>
       <c r="B111" t="n">
         <v>79266</v>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464383</v>
+        <v>464219</v>
       </c>
       <c r="R111" t="n">
-        <v>6758151</v>
+        <v>6758055</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12280,10 +12280,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131806031</v>
+        <v>131805979</v>
       </c>
       <c r="B112" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12291,21 +12291,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464219</v>
+        <v>464400</v>
       </c>
       <c r="R112" t="n">
-        <v>6758055</v>
+        <v>6758180</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12387,10 +12387,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131805979</v>
+        <v>131806061</v>
       </c>
       <c r="B113" t="n">
-        <v>91838</v>
+        <v>57904</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12398,34 +12398,39 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464400</v>
+        <v>464225</v>
       </c>
       <c r="R113" t="n">
-        <v>6758180</v>
+        <v>6758200</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12457,7 +12462,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12467,7 +12472,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12494,32 +12499,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131806039</v>
+        <v>131805987</v>
       </c>
       <c r="B114" t="n">
-        <v>79266</v>
+        <v>80400</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12529,10 +12534,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464338</v>
+        <v>464138</v>
       </c>
       <c r="R114" t="n">
-        <v>6758168</v>
+        <v>6758188</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12564,7 +12569,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12574,7 +12579,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12585,6 +12590,21 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -12601,7 +12621,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131806027</v>
+        <v>131806039</v>
       </c>
       <c r="B115" t="n">
         <v>79266</v>
@@ -12636,10 +12656,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464171</v>
+        <v>464338</v>
       </c>
       <c r="R115" t="n">
-        <v>6757887</v>
+        <v>6758168</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12671,7 +12691,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12681,7 +12701,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12708,32 +12728,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131805970</v>
+        <v>131806027</v>
       </c>
       <c r="B116" t="n">
-        <v>91801</v>
+        <v>79266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12743,10 +12763,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464109</v>
+        <v>464171</v>
       </c>
       <c r="R116" t="n">
-        <v>6757856</v>
+        <v>6757887</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12778,7 +12798,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12788,7 +12808,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12815,32 +12835,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131806033</v>
+        <v>131805970</v>
       </c>
       <c r="B117" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12850,10 +12870,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464363</v>
+        <v>464109</v>
       </c>
       <c r="R117" t="n">
-        <v>6758150</v>
+        <v>6757856</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12885,7 +12905,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12895,7 +12915,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12922,7 +12942,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131806035</v>
+        <v>131806033</v>
       </c>
       <c r="B118" t="n">
         <v>79266</v>
@@ -12957,10 +12977,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464460</v>
+        <v>464363</v>
       </c>
       <c r="R118" t="n">
-        <v>6758144</v>
+        <v>6758150</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12992,7 +13012,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13002,7 +13022,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13029,32 +13049,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131805987</v>
+        <v>131806035</v>
       </c>
       <c r="B119" t="n">
-        <v>80400</v>
+        <v>79266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13064,10 +13084,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464138</v>
+        <v>464460</v>
       </c>
       <c r="R119" t="n">
-        <v>6758188</v>
+        <v>6758144</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13099,7 +13119,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13109,7 +13129,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13120,21 +13140,6 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -13365,50 +13370,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>131806061</v>
+        <v>131806069</v>
       </c>
       <c r="B122" t="n">
-        <v>57904</v>
+        <v>91793</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>4118</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tajgafiberskinn</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fibricium subodoratum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst. ex Bourdot &amp; Galzin) Spirin</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>464225</v>
+        <v>464424</v>
       </c>
       <c r="R122" t="n">
-        <v>6758200</v>
+        <v>6758134</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13440,7 +13443,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13450,7 +13453,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rätt mikrokaraktär i form av kristalltäckta cystider.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13458,6 +13466,11 @@
       </c>
       <c r="AE122" t="b">
         <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG122" t="b">
         <v>0</v>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131604098</v>
+        <v>131594186</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,39 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464410</v>
+        <v>464035</v>
       </c>
       <c r="R17" t="n">
-        <v>6758165</v>
+        <v>6758187</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131600419</v>
+        <v>131604098</v>
       </c>
       <c r="B18" t="n">
-        <v>79885</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,34 +2358,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464251</v>
+        <v>464410</v>
       </c>
       <c r="R18" t="n">
-        <v>6758281</v>
+        <v>6758165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594186</v>
+        <v>131600419</v>
       </c>
       <c r="B19" t="n">
-        <v>79266</v>
+        <v>79885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464035</v>
+        <v>464251</v>
       </c>
       <c r="R19" t="n">
-        <v>6758187</v>
+        <v>6758281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,42 +2567,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R20" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,6 +2627,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B21" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,37 +2669,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R21" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131600551</v>
+        <v>131597848</v>
       </c>
       <c r="B42" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,39 +4784,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464263</v>
+        <v>464205</v>
       </c>
       <c r="R42" t="n">
-        <v>6758298</v>
+        <v>6758160</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4875,10 +4870,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131603307</v>
+        <v>131600442</v>
       </c>
       <c r="B43" t="n">
-        <v>57904</v>
+        <v>79856</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4886,39 +4881,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464265</v>
+        <v>464251</v>
       </c>
       <c r="R43" t="n">
-        <v>6758140</v>
+        <v>6758281</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,11 +4941,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4982,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131603971</v>
+        <v>131600551</v>
       </c>
       <c r="B44" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4993,34 +4978,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464384</v>
+        <v>464263</v>
       </c>
       <c r="R44" t="n">
-        <v>6758179</v>
+        <v>6758298</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,11 +5043,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5084,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131600442</v>
+        <v>131603307</v>
       </c>
       <c r="B45" t="n">
-        <v>79856</v>
+        <v>57904</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5095,34 +5080,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464251</v>
+        <v>464265</v>
       </c>
       <c r="R45" t="n">
-        <v>6758281</v>
+        <v>6758140</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,6 +5145,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5181,7 +5176,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131597848</v>
+        <v>131603971</v>
       </c>
       <c r="B46" t="n">
         <v>79266</v>
@@ -5216,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464205</v>
+        <v>464384</v>
       </c>
       <c r="R46" t="n">
-        <v>6758160</v>
+        <v>6758179</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5247,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131599244</v>
+        <v>131586790</v>
       </c>
       <c r="B47" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,39 +5289,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464210</v>
+        <v>464046</v>
       </c>
       <c r="R47" t="n">
-        <v>6758193</v>
+        <v>6758049</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5354,11 +5349,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5385,53 +5375,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131594252</v>
+        <v>131599244</v>
       </c>
       <c r="B48" t="n">
-        <v>57092</v>
+        <v>57901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464049</v>
+        <v>464210</v>
       </c>
       <c r="R48" t="n">
-        <v>6758189</v>
+        <v>6758193</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5464,6 +5451,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5490,45 +5482,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131586790</v>
+        <v>131594252</v>
       </c>
       <c r="B49" t="n">
-        <v>79266</v>
+        <v>57092</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464046</v>
+        <v>464049</v>
       </c>
       <c r="R49" t="n">
-        <v>6758049</v>
+        <v>6758189</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131605450</v>
+        <v>131586702</v>
       </c>
       <c r="B50" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,40 +5598,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464189</v>
+        <v>464051</v>
       </c>
       <c r="R50" t="n">
-        <v>6757919</v>
+        <v>6758034</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5663,18 +5665,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5689,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131586702</v>
+        <v>131605450</v>
       </c>
       <c r="B51" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5704,42 +5700,40 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464051</v>
+        <v>464189</v>
       </c>
       <c r="R51" t="n">
-        <v>6758034</v>
+        <v>6757919</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5771,12 +5765,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -8767,32 +8767,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131806042</v>
+        <v>131805999</v>
       </c>
       <c r="B80" t="n">
-        <v>79266</v>
+        <v>97909</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464267</v>
+        <v>464140</v>
       </c>
       <c r="R80" t="n">
-        <v>6758179</v>
+        <v>6758185</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8874,10 +8874,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131806029</v>
+        <v>131805976</v>
       </c>
       <c r="B81" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8885,21 +8885,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464204</v>
+        <v>464319</v>
       </c>
       <c r="R81" t="n">
-        <v>6757960</v>
+        <v>6757939</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8981,10 +8981,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131805976</v>
+        <v>131806042</v>
       </c>
       <c r="B82" t="n">
-        <v>91838</v>
+        <v>79266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8992,21 +8992,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464319</v>
+        <v>464267</v>
       </c>
       <c r="R82" t="n">
-        <v>6757939</v>
+        <v>6758179</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,32 +9088,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131805999</v>
+        <v>131806029</v>
       </c>
       <c r="B83" t="n">
-        <v>97909</v>
+        <v>79266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464140</v>
+        <v>464204</v>
       </c>
       <c r="R83" t="n">
-        <v>6758185</v>
+        <v>6757960</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10071,10 +10071,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131806051</v>
+        <v>131805977</v>
       </c>
       <c r="B92" t="n">
-        <v>57904</v>
+        <v>91838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10082,39 +10082,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464172</v>
+        <v>464313</v>
       </c>
       <c r="R92" t="n">
-        <v>6757903</v>
+        <v>6757941</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10146,7 +10141,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10156,7 +10151,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10183,7 +10178,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131806048</v>
+        <v>131806051</v>
       </c>
       <c r="B93" t="n">
         <v>57904</v>
@@ -10214,7 +10209,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10223,10 +10218,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464290</v>
+        <v>464172</v>
       </c>
       <c r="R93" t="n">
-        <v>6758088</v>
+        <v>6757903</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10258,7 +10253,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10268,7 +10263,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10295,10 +10290,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131805977</v>
+        <v>131806048</v>
       </c>
       <c r="B94" t="n">
-        <v>91838</v>
+        <v>57904</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10306,34 +10301,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464313</v>
+        <v>464290</v>
       </c>
       <c r="R94" t="n">
-        <v>6757941</v>
+        <v>6758088</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11161,32 +11161,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131806003</v>
+        <v>131805978</v>
       </c>
       <c r="B102" t="n">
-        <v>80407</v>
+        <v>91838</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464137</v>
+        <v>464275</v>
       </c>
       <c r="R102" t="n">
-        <v>6758186</v>
+        <v>6758069</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11252,21 +11252,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11283,32 +11268,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131805978</v>
+        <v>131806003</v>
       </c>
       <c r="B103" t="n">
-        <v>91838</v>
+        <v>80407</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11318,10 +11303,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464275</v>
+        <v>464137</v>
       </c>
       <c r="R103" t="n">
-        <v>6758069</v>
+        <v>6758186</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11353,7 +11338,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11363,7 +11348,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11374,6 +11359,21 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11390,50 +11390,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131806067</v>
+        <v>131806036</v>
       </c>
       <c r="B104" t="n">
-        <v>5178</v>
+        <v>79266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464196</v>
+        <v>464459</v>
       </c>
       <c r="R104" t="n">
-        <v>6757964</v>
+        <v>6758165</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11465,7 +11460,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11475,7 +11470,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11502,38 +11497,38 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806058</v>
+        <v>131806067</v>
       </c>
       <c r="B105" t="n">
-        <v>57904</v>
+        <v>5178</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11542,10 +11537,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464435</v>
+        <v>464196</v>
       </c>
       <c r="R105" t="n">
-        <v>6758156</v>
+        <v>6757964</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11577,7 +11572,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11587,7 +11582,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11614,10 +11609,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806036</v>
+        <v>131806058</v>
       </c>
       <c r="B106" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11625,34 +11620,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464459</v>
+        <v>464435</v>
       </c>
       <c r="R106" t="n">
-        <v>6758165</v>
+        <v>6758156</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12387,10 +12387,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131806061</v>
+        <v>131805990</v>
       </c>
       <c r="B113" t="n">
-        <v>57904</v>
+        <v>91788</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12398,39 +12398,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464225</v>
+        <v>464391</v>
       </c>
       <c r="R113" t="n">
-        <v>6758200</v>
+        <v>6758144</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12462,7 +12457,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12472,7 +12467,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12499,32 +12494,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131805987</v>
+        <v>131806004</v>
       </c>
       <c r="B114" t="n">
-        <v>80400</v>
+        <v>81251</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>1049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12534,10 +12529,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464138</v>
+        <v>464261</v>
       </c>
       <c r="R114" t="n">
-        <v>6758188</v>
+        <v>6758029</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12569,7 +12564,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12579,7 +12574,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12590,21 +12585,6 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -12621,10 +12601,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131806039</v>
+        <v>131806061</v>
       </c>
       <c r="B115" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12632,34 +12612,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464338</v>
+        <v>464225</v>
       </c>
       <c r="R115" t="n">
-        <v>6758168</v>
+        <v>6758200</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12691,7 +12676,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12701,7 +12686,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12728,32 +12713,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131806027</v>
+        <v>131805987</v>
       </c>
       <c r="B116" t="n">
-        <v>79266</v>
+        <v>80400</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12763,10 +12748,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464171</v>
+        <v>464138</v>
       </c>
       <c r="R116" t="n">
-        <v>6757887</v>
+        <v>6758188</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12798,7 +12783,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12808,7 +12793,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12819,6 +12804,21 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -12835,32 +12835,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131805970</v>
+        <v>131806039</v>
       </c>
       <c r="B117" t="n">
-        <v>91801</v>
+        <v>79266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12870,10 +12870,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464109</v>
+        <v>464338</v>
       </c>
       <c r="R117" t="n">
-        <v>6757856</v>
+        <v>6758168</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12905,7 +12905,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12942,7 +12942,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131806033</v>
+        <v>131806027</v>
       </c>
       <c r="B118" t="n">
         <v>79266</v>
@@ -12977,10 +12977,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464363</v>
+        <v>464171</v>
       </c>
       <c r="R118" t="n">
-        <v>6758150</v>
+        <v>6757887</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13012,7 +13012,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13049,32 +13049,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131806035</v>
+        <v>131805970</v>
       </c>
       <c r="B119" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13084,10 +13084,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464460</v>
+        <v>464109</v>
       </c>
       <c r="R119" t="n">
-        <v>6758144</v>
+        <v>6757856</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13156,10 +13156,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131805990</v>
+        <v>131806033</v>
       </c>
       <c r="B120" t="n">
-        <v>91788</v>
+        <v>79266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13167,21 +13167,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13191,10 +13191,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464391</v>
+        <v>464363</v>
       </c>
       <c r="R120" t="n">
-        <v>6758144</v>
+        <v>6758150</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13263,10 +13263,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131806004</v>
+        <v>131806035</v>
       </c>
       <c r="B121" t="n">
-        <v>81251</v>
+        <v>79266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13274,21 +13274,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13298,10 +13298,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464261</v>
+        <v>464460</v>
       </c>
       <c r="R121" t="n">
-        <v>6758029</v>
+        <v>6758144</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131604477</v>
+        <v>131587086</v>
       </c>
       <c r="B7" t="n">
         <v>57904</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464463</v>
+        <v>464056</v>
       </c>
       <c r="R7" t="n">
-        <v>6758106</v>
+        <v>6758091</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,11 +1295,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131605369</v>
+        <v>131592130</v>
       </c>
       <c r="B8" t="n">
         <v>79266</v>
@@ -1355,22 +1350,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464271</v>
+        <v>464070</v>
       </c>
       <c r="R8" t="n">
-        <v>6757950</v>
+        <v>6758175</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,18 +1394,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1432,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131592130</v>
+        <v>131589374</v>
       </c>
       <c r="B9" t="n">
         <v>79266</v>
@@ -1467,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464070</v>
+        <v>464029</v>
       </c>
       <c r="R9" t="n">
-        <v>6758175</v>
+        <v>6758112</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131589374</v>
+        <v>131604477</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,34 +1526,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464029</v>
+        <v>464463</v>
       </c>
       <c r="R10" t="n">
-        <v>6758112</v>
+        <v>6758106</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,6 +1591,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131587086</v>
+        <v>131605369</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,42 +1633,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464056</v>
+        <v>464271</v>
       </c>
       <c r="R11" t="n">
-        <v>6758091</v>
+        <v>6757950</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,12 +1698,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131594186</v>
+        <v>131604098</v>
       </c>
       <c r="B17" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,34 +2256,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464035</v>
+        <v>464410</v>
       </c>
       <c r="R17" t="n">
-        <v>6758187</v>
+        <v>6758165</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2325,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131604098</v>
+        <v>131600419</v>
       </c>
       <c r="B18" t="n">
-        <v>57904</v>
+        <v>79885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2358,39 +2363,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464410</v>
+        <v>464251</v>
       </c>
       <c r="R18" t="n">
-        <v>6758165</v>
+        <v>6758281</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131600419</v>
+        <v>131594186</v>
       </c>
       <c r="B19" t="n">
-        <v>79885</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464251</v>
+        <v>464035</v>
       </c>
       <c r="R19" t="n">
-        <v>6758281</v>
+        <v>6758187</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,37 +2567,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R20" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2627,11 +2632,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,42 +2669,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R21" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2734,6 +2729,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131586743</v>
+        <v>131604566</v>
       </c>
       <c r="B25" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,34 +3067,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464052</v>
+        <v>464472</v>
       </c>
       <c r="R25" t="n">
-        <v>6758047</v>
+        <v>6758091</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,6 +3132,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3153,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131604566</v>
+        <v>131586743</v>
       </c>
       <c r="B26" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3164,39 +3174,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464472</v>
+        <v>464052</v>
       </c>
       <c r="R26" t="n">
-        <v>6758091</v>
+        <v>6758047</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3229,11 +3234,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131597848</v>
+        <v>131600551</v>
       </c>
       <c r="B42" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,34 +4784,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464205</v>
+        <v>464263</v>
       </c>
       <c r="R42" t="n">
-        <v>6758160</v>
+        <v>6758298</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,10 +4875,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131600442</v>
+        <v>131603307</v>
       </c>
       <c r="B43" t="n">
-        <v>79856</v>
+        <v>57904</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4881,34 +4886,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464251</v>
+        <v>464265</v>
       </c>
       <c r="R43" t="n">
-        <v>6758281</v>
+        <v>6758140</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4941,6 +4951,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4967,10 +4982,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131600551</v>
+        <v>131603971</v>
       </c>
       <c r="B44" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4978,39 +4993,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464263</v>
+        <v>464384</v>
       </c>
       <c r="R44" t="n">
-        <v>6758298</v>
+        <v>6758179</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5043,6 +5053,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5084,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131603307</v>
+        <v>131600442</v>
       </c>
       <c r="B45" t="n">
-        <v>57904</v>
+        <v>79856</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5080,39 +5095,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464265</v>
+        <v>464251</v>
       </c>
       <c r="R45" t="n">
-        <v>6758140</v>
+        <v>6758281</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5145,11 +5155,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5176,7 +5181,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131603971</v>
+        <v>131597848</v>
       </c>
       <c r="B46" t="n">
         <v>79266</v>
@@ -5211,10 +5216,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464384</v>
+        <v>464205</v>
       </c>
       <c r="R46" t="n">
-        <v>6758179</v>
+        <v>6758160</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5247,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131586702</v>
+        <v>131605450</v>
       </c>
       <c r="B50" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,42 +5598,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464051</v>
+        <v>464189</v>
       </c>
       <c r="R50" t="n">
-        <v>6758034</v>
+        <v>6757919</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5665,12 +5663,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131605450</v>
+        <v>131586702</v>
       </c>
       <c r="B51" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,40 +5704,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464189</v>
+        <v>464051</v>
       </c>
       <c r="R51" t="n">
-        <v>6757919</v>
+        <v>6758034</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5765,18 +5771,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7127,32 +7127,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131806001</v>
+        <v>131806044</v>
       </c>
       <c r="B65" t="n">
-        <v>92506</v>
+        <v>79266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106596</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordlig parasitporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464428</v>
+        <v>464091</v>
       </c>
       <c r="R65" t="n">
-        <v>6758134</v>
+        <v>6758171</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7234,7 +7234,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131806044</v>
+        <v>131806025</v>
       </c>
       <c r="B66" t="n">
         <v>79266</v>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464091</v>
+        <v>464116</v>
       </c>
       <c r="R66" t="n">
-        <v>6758171</v>
+        <v>6757815</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7341,32 +7341,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131806025</v>
+        <v>131806001</v>
       </c>
       <c r="B67" t="n">
-        <v>79266</v>
+        <v>92506</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106596</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464116</v>
+        <v>464428</v>
       </c>
       <c r="R67" t="n">
-        <v>6757815</v>
+        <v>6758134</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131587086</v>
+        <v>131604477</v>
       </c>
       <c r="B7" t="n">
         <v>57904</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464056</v>
+        <v>464463</v>
       </c>
       <c r="R7" t="n">
-        <v>6758091</v>
+        <v>6758106</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,6 +1295,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131592130</v>
+        <v>131605369</v>
       </c>
       <c r="B8" t="n">
         <v>79266</v>
@@ -1350,19 +1355,22 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464070</v>
+        <v>464271</v>
       </c>
       <c r="R8" t="n">
-        <v>6758175</v>
+        <v>6757950</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,12 +1402,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1418,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131589374</v>
+        <v>131592130</v>
       </c>
       <c r="B9" t="n">
         <v>79266</v>
@@ -1453,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464029</v>
+        <v>464070</v>
       </c>
       <c r="R9" t="n">
-        <v>6758112</v>
+        <v>6758175</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131604477</v>
+        <v>131589374</v>
       </c>
       <c r="B10" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,39 +1540,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464463</v>
+        <v>464029</v>
       </c>
       <c r="R10" t="n">
-        <v>6758106</v>
+        <v>6758112</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,11 +1600,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131605369</v>
+        <v>131587086</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,40 +1637,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464271</v>
+        <v>464056</v>
       </c>
       <c r="R11" t="n">
-        <v>6757950</v>
+        <v>6758091</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1698,18 +1704,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,42 +2567,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R20" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2632,6 +2627,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B21" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,37 +2669,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R21" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2729,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131600551</v>
+        <v>131597848</v>
       </c>
       <c r="B42" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,39 +4784,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464263</v>
+        <v>464205</v>
       </c>
       <c r="R42" t="n">
-        <v>6758298</v>
+        <v>6758160</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4875,10 +4870,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131603307</v>
+        <v>131600442</v>
       </c>
       <c r="B43" t="n">
-        <v>57904</v>
+        <v>79856</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4886,39 +4881,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464265</v>
+        <v>464251</v>
       </c>
       <c r="R43" t="n">
-        <v>6758140</v>
+        <v>6758281</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,11 +4941,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4982,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131603971</v>
+        <v>131600551</v>
       </c>
       <c r="B44" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4993,34 +4978,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464384</v>
+        <v>464263</v>
       </c>
       <c r="R44" t="n">
-        <v>6758179</v>
+        <v>6758298</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,11 +5043,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5084,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131600442</v>
+        <v>131603307</v>
       </c>
       <c r="B45" t="n">
-        <v>79856</v>
+        <v>57904</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5095,34 +5080,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464251</v>
+        <v>464265</v>
       </c>
       <c r="R45" t="n">
-        <v>6758281</v>
+        <v>6758140</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5155,6 +5145,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5181,7 +5176,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131597848</v>
+        <v>131603971</v>
       </c>
       <c r="B46" t="n">
         <v>79266</v>
@@ -5216,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464205</v>
+        <v>464384</v>
       </c>
       <c r="R46" t="n">
-        <v>6758160</v>
+        <v>6758179</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5247,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5278,10 +5278,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131586790</v>
+        <v>131599244</v>
       </c>
       <c r="B47" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5289,34 +5289,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464046</v>
+        <v>464210</v>
       </c>
       <c r="R47" t="n">
-        <v>6758049</v>
+        <v>6758193</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5349,6 +5354,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5375,50 +5385,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131599244</v>
+        <v>131594252</v>
       </c>
       <c r="B48" t="n">
-        <v>57901</v>
+        <v>57092</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464210</v>
+        <v>464049</v>
       </c>
       <c r="R48" t="n">
-        <v>6758193</v>
+        <v>6758189</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5451,11 +5464,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5482,53 +5490,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131594252</v>
+        <v>131586790</v>
       </c>
       <c r="B49" t="n">
-        <v>57092</v>
+        <v>79266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464049</v>
+        <v>464046</v>
       </c>
       <c r="R49" t="n">
-        <v>6758189</v>
+        <v>6758049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7662,45 +7662,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131805997</v>
+        <v>131806056</v>
       </c>
       <c r="B70" t="n">
-        <v>92298</v>
+        <v>57904</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464284</v>
+        <v>464295</v>
       </c>
       <c r="R70" t="n">
-        <v>6758164</v>
+        <v>6757996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7732,7 +7737,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7742,7 +7747,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7769,45 +7774,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131805980</v>
+        <v>131805986</v>
       </c>
       <c r="B71" t="n">
-        <v>91838</v>
+        <v>4774</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464132</v>
+        <v>464254</v>
       </c>
       <c r="R71" t="n">
-        <v>6757988</v>
+        <v>6758196</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7839,7 +7849,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7849,7 +7859,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7876,50 +7886,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131806056</v>
+        <v>131805997</v>
       </c>
       <c r="B72" t="n">
-        <v>57904</v>
+        <v>92298</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464295</v>
+        <v>464284</v>
       </c>
       <c r="R72" t="n">
-        <v>6757996</v>
+        <v>6758164</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7951,7 +7956,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7961,7 +7966,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,50 +7993,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131805986</v>
+        <v>131805980</v>
       </c>
       <c r="B73" t="n">
-        <v>4774</v>
+        <v>91838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464254</v>
+        <v>464132</v>
       </c>
       <c r="R73" t="n">
-        <v>6758196</v>
+        <v>6757988</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8767,32 +8767,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131805999</v>
+        <v>131806042</v>
       </c>
       <c r="B80" t="n">
-        <v>97909</v>
+        <v>79266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464140</v>
+        <v>464267</v>
       </c>
       <c r="R80" t="n">
-        <v>6758185</v>
+        <v>6758179</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8874,10 +8874,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131805976</v>
+        <v>131806029</v>
       </c>
       <c r="B81" t="n">
-        <v>91838</v>
+        <v>79266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8885,21 +8885,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464319</v>
+        <v>464204</v>
       </c>
       <c r="R81" t="n">
-        <v>6757939</v>
+        <v>6757960</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8981,10 +8981,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131806042</v>
+        <v>131805976</v>
       </c>
       <c r="B82" t="n">
-        <v>79266</v>
+        <v>91838</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8992,21 +8992,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464267</v>
+        <v>464319</v>
       </c>
       <c r="R82" t="n">
-        <v>6758179</v>
+        <v>6757939</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,32 +9088,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131806029</v>
+        <v>131805999</v>
       </c>
       <c r="B83" t="n">
-        <v>79266</v>
+        <v>97909</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464204</v>
+        <v>464140</v>
       </c>
       <c r="R83" t="n">
-        <v>6757960</v>
+        <v>6758185</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10071,10 +10071,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131805977</v>
+        <v>131806051</v>
       </c>
       <c r="B92" t="n">
-        <v>91838</v>
+        <v>57904</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10082,34 +10082,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464313</v>
+        <v>464172</v>
       </c>
       <c r="R92" t="n">
-        <v>6757941</v>
+        <v>6757903</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10141,7 +10146,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10151,7 +10156,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10178,7 +10183,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131806051</v>
+        <v>131806048</v>
       </c>
       <c r="B93" t="n">
         <v>57904</v>
@@ -10209,7 +10214,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10218,10 +10223,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464172</v>
+        <v>464290</v>
       </c>
       <c r="R93" t="n">
-        <v>6757903</v>
+        <v>6758088</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10253,7 +10258,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10263,7 +10268,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10290,10 +10295,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131806048</v>
+        <v>131805977</v>
       </c>
       <c r="B94" t="n">
-        <v>57904</v>
+        <v>91838</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10301,39 +10306,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464290</v>
+        <v>464313</v>
       </c>
       <c r="R94" t="n">
-        <v>6758088</v>
+        <v>6757941</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10402,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806052</v>
+        <v>131806032</v>
       </c>
       <c r="B95" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,39 +10413,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464193</v>
+        <v>464341</v>
       </c>
       <c r="R95" t="n">
-        <v>6757936</v>
+        <v>6757956</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10477,7 +10472,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10487,7 +10482,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10514,7 +10509,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806032</v>
+        <v>131806030</v>
       </c>
       <c r="B96" t="n">
         <v>79266</v>
@@ -10549,10 +10544,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464341</v>
+        <v>464204</v>
       </c>
       <c r="R96" t="n">
-        <v>6757956</v>
+        <v>6758031</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10584,7 +10579,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10594,7 +10589,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10621,32 +10616,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806030</v>
+        <v>131805972</v>
       </c>
       <c r="B97" t="n">
-        <v>79266</v>
+        <v>91801</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10656,10 +10651,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464204</v>
+        <v>464074</v>
       </c>
       <c r="R97" t="n">
-        <v>6758031</v>
+        <v>6758064</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10691,7 +10686,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10701,7 +10696,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10728,45 +10723,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131805972</v>
+        <v>131806052</v>
       </c>
       <c r="B98" t="n">
-        <v>91801</v>
+        <v>57904</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464074</v>
+        <v>464193</v>
       </c>
       <c r="R98" t="n">
-        <v>6758064</v>
+        <v>6757936</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11161,32 +11161,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131805978</v>
+        <v>131806003</v>
       </c>
       <c r="B102" t="n">
-        <v>91838</v>
+        <v>80407</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464275</v>
+        <v>464137</v>
       </c>
       <c r="R102" t="n">
-        <v>6758069</v>
+        <v>6758186</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11252,6 +11252,21 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11268,32 +11283,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131806003</v>
+        <v>131805978</v>
       </c>
       <c r="B103" t="n">
-        <v>80407</v>
+        <v>91838</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11303,10 +11318,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464137</v>
+        <v>464275</v>
       </c>
       <c r="R103" t="n">
-        <v>6758186</v>
+        <v>6758069</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11338,7 +11353,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11348,7 +11363,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11359,21 +11374,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11390,45 +11390,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131806036</v>
+        <v>131806067</v>
       </c>
       <c r="B104" t="n">
-        <v>79266</v>
+        <v>5178</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464459</v>
+        <v>464196</v>
       </c>
       <c r="R104" t="n">
-        <v>6758165</v>
+        <v>6757964</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11460,7 +11465,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11470,7 +11475,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11497,38 +11502,38 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806067</v>
+        <v>131806058</v>
       </c>
       <c r="B105" t="n">
-        <v>5178</v>
+        <v>57904</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11537,10 +11542,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464196</v>
+        <v>464435</v>
       </c>
       <c r="R105" t="n">
-        <v>6757964</v>
+        <v>6758156</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11572,7 +11577,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11582,7 +11587,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11609,10 +11614,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806058</v>
+        <v>131806036</v>
       </c>
       <c r="B106" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11620,39 +11625,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464435</v>
+        <v>464459</v>
       </c>
       <c r="R106" t="n">
-        <v>6758156</v>
+        <v>6758165</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12387,10 +12387,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131805990</v>
+        <v>131806039</v>
       </c>
       <c r="B113" t="n">
-        <v>91788</v>
+        <v>79266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464391</v>
+        <v>464338</v>
       </c>
       <c r="R113" t="n">
-        <v>6758144</v>
+        <v>6758168</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131806004</v>
+        <v>131806027</v>
       </c>
       <c r="B114" t="n">
-        <v>81251</v>
+        <v>79266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464261</v>
+        <v>464171</v>
       </c>
       <c r="R114" t="n">
-        <v>6758029</v>
+        <v>6757887</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12601,50 +12601,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131806061</v>
+        <v>131805970</v>
       </c>
       <c r="B115" t="n">
-        <v>57904</v>
+        <v>91801</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464225</v>
+        <v>464109</v>
       </c>
       <c r="R115" t="n">
-        <v>6758200</v>
+        <v>6757856</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12676,7 +12671,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12686,7 +12681,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12713,32 +12708,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131805987</v>
+        <v>131806033</v>
       </c>
       <c r="B116" t="n">
-        <v>80400</v>
+        <v>79266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12748,10 +12743,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464138</v>
+        <v>464363</v>
       </c>
       <c r="R116" t="n">
-        <v>6758188</v>
+        <v>6758150</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12783,7 +12778,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12793,7 +12788,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12804,21 +12799,6 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -12835,7 +12815,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131806039</v>
+        <v>131806035</v>
       </c>
       <c r="B117" t="n">
         <v>79266</v>
@@ -12870,10 +12850,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464338</v>
+        <v>464460</v>
       </c>
       <c r="R117" t="n">
-        <v>6758168</v>
+        <v>6758144</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12905,7 +12885,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12915,7 +12895,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12942,32 +12922,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131806027</v>
+        <v>131805987</v>
       </c>
       <c r="B118" t="n">
-        <v>79266</v>
+        <v>80400</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12977,10 +12957,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464171</v>
+        <v>464138</v>
       </c>
       <c r="R118" t="n">
-        <v>6757887</v>
+        <v>6758188</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13012,7 +12992,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13022,7 +13002,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13033,6 +13013,21 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13049,32 +13044,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131805970</v>
+        <v>131805990</v>
       </c>
       <c r="B119" t="n">
-        <v>91801</v>
+        <v>91788</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13084,10 +13079,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464109</v>
+        <v>464391</v>
       </c>
       <c r="R119" t="n">
-        <v>6757856</v>
+        <v>6758144</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13119,7 +13114,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13129,7 +13124,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13156,10 +13151,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131806033</v>
+        <v>131806004</v>
       </c>
       <c r="B120" t="n">
-        <v>79266</v>
+        <v>81251</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13167,21 +13162,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13191,10 +13186,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464363</v>
+        <v>464261</v>
       </c>
       <c r="R120" t="n">
-        <v>6758150</v>
+        <v>6758029</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13226,7 +13221,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13236,7 +13231,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13263,10 +13258,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131806035</v>
+        <v>131806061</v>
       </c>
       <c r="B121" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13274,34 +13269,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464460</v>
+        <v>464225</v>
       </c>
       <c r="R121" t="n">
-        <v>6758144</v>
+        <v>6758200</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131604477</v>
+        <v>131592130</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,39 +1230,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464463</v>
+        <v>464070</v>
       </c>
       <c r="R7" t="n">
-        <v>6758106</v>
+        <v>6758175</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,11 +1290,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131605369</v>
+        <v>131589374</v>
       </c>
       <c r="B8" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,22 +1345,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464271</v>
+        <v>464029</v>
       </c>
       <c r="R8" t="n">
-        <v>6757950</v>
+        <v>6758112</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,18 +1389,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1432,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131592130</v>
+        <v>131587086</v>
       </c>
       <c r="B9" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,34 +1424,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464070</v>
+        <v>464056</v>
       </c>
       <c r="R9" t="n">
-        <v>6758175</v>
+        <v>6758091</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131589374</v>
+        <v>131604477</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,34 +1526,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464029</v>
+        <v>464463</v>
       </c>
       <c r="R10" t="n">
-        <v>6758112</v>
+        <v>6758106</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,6 +1591,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131587086</v>
+        <v>131605369</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,42 +1633,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464056</v>
+        <v>464271</v>
       </c>
       <c r="R11" t="n">
-        <v>6758091</v>
+        <v>6757950</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1704,12 +1698,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>131587093</v>
       </c>
       <c r="B12" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>131601638</v>
       </c>
       <c r="B13" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>131593794</v>
       </c>
       <c r="B14" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>131595645</v>
       </c>
       <c r="B15" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>131586783</v>
       </c>
       <c r="B16" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131604098</v>
+        <v>131600419</v>
       </c>
       <c r="B17" t="n">
-        <v>57904</v>
+        <v>79888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,39 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464410</v>
+        <v>464251</v>
       </c>
       <c r="R17" t="n">
-        <v>6758165</v>
+        <v>6758281</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131600419</v>
+        <v>131604098</v>
       </c>
       <c r="B18" t="n">
-        <v>79885</v>
+        <v>57907</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,34 +2358,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464251</v>
+        <v>464410</v>
       </c>
       <c r="R18" t="n">
-        <v>6758281</v>
+        <v>6758165</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2457,7 +2457,7 @@
         <v>131594186</v>
       </c>
       <c r="B19" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>131601488</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>131591075</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>131593946</v>
       </c>
       <c r="B22" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>131602481</v>
       </c>
       <c r="B23" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>131600576</v>
       </c>
       <c r="B24" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131604566</v>
+        <v>131586743</v>
       </c>
       <c r="B25" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3067,39 +3067,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464472</v>
+        <v>464052</v>
       </c>
       <c r="R25" t="n">
-        <v>6758091</v>
+        <v>6758047</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,11 +3127,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,10 +3153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131586743</v>
+        <v>131604566</v>
       </c>
       <c r="B26" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,34 +3164,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464052</v>
+        <v>464472</v>
       </c>
       <c r="R26" t="n">
-        <v>6758047</v>
+        <v>6758091</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,6 +3229,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 bild, tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3263,7 +3263,7 @@
         <v>131604893</v>
       </c>
       <c r="B27" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3362,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131591546</v>
+        <v>131597701</v>
       </c>
       <c r="B28" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464053</v>
+        <v>464192</v>
       </c>
       <c r="R28" t="n">
-        <v>6758144</v>
+        <v>6758156</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3459,48 +3459,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131597701</v>
+        <v>131586714</v>
       </c>
       <c r="B29" t="n">
-        <v>79266</v>
+        <v>57095</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464192</v>
+        <v>464060</v>
       </c>
       <c r="R29" t="n">
-        <v>6758156</v>
+        <v>6758044</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3556,48 +3561,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131594493</v>
+        <v>131604756</v>
       </c>
       <c r="B30" t="n">
-        <v>79266</v>
+        <v>57095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464034</v>
+        <v>464541</v>
       </c>
       <c r="R30" t="n">
-        <v>6758248</v>
+        <v>6758017</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,18 +3639,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3662,10 +3663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131603524</v>
+        <v>131604670</v>
       </c>
       <c r="B31" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3702,10 +3703,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464384</v>
+        <v>464483</v>
       </c>
       <c r="R31" t="n">
-        <v>6758179</v>
+        <v>6758032</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3742,7 +3743,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 bild, gran</t>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3769,10 +3770,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131604670</v>
+        <v>131603524</v>
       </c>
       <c r="B32" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3809,10 +3810,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464483</v>
+        <v>464384</v>
       </c>
       <c r="R32" t="n">
-        <v>6758032</v>
+        <v>6758179</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3849,7 +3850,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt med ringhack</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3876,50 +3877,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131604756</v>
+        <v>131591546</v>
       </c>
       <c r="B33" t="n">
-        <v>57092</v>
+        <v>79269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464541</v>
+        <v>464053</v>
       </c>
       <c r="R33" t="n">
-        <v>6758017</v>
+        <v>6758144</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,53 +3974,51 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131586714</v>
+        <v>131594493</v>
       </c>
       <c r="B34" t="n">
-        <v>57092</v>
+        <v>79269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464060</v>
+        <v>464034</v>
       </c>
       <c r="R34" t="n">
-        <v>6758044</v>
+        <v>6758248</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4056,12 +4050,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2 bilder, bäck</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>131600797</v>
       </c>
       <c r="B35" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>131600974</v>
       </c>
       <c r="B36" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131586494</v>
+        <v>131603322</v>
       </c>
       <c r="B37" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464066</v>
+        <v>464265</v>
       </c>
       <c r="R37" t="n">
-        <v>6757982</v>
+        <v>6758140</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131586581</v>
+        <v>131600594</v>
       </c>
       <c r="B38" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464051</v>
+        <v>464296</v>
       </c>
       <c r="R38" t="n">
-        <v>6758034</v>
+        <v>6758304</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,6 +4451,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4477,10 +4482,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131603322</v>
+        <v>131586494</v>
       </c>
       <c r="B39" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4512,10 +4517,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464265</v>
+        <v>464066</v>
       </c>
       <c r="R39" t="n">
-        <v>6758140</v>
+        <v>6757982</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4574,10 +4579,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131600594</v>
+        <v>131586581</v>
       </c>
       <c r="B40" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4609,10 +4614,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464296</v>
+        <v>464051</v>
       </c>
       <c r="R40" t="n">
-        <v>6758304</v>
+        <v>6758034</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4645,11 +4650,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4679,7 +4679,7 @@
         <v>131599422</v>
       </c>
       <c r="B41" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131597848</v>
+        <v>131600551</v>
       </c>
       <c r="B42" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,34 +4784,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464205</v>
+        <v>464263</v>
       </c>
       <c r="R42" t="n">
-        <v>6758160</v>
+        <v>6758298</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4870,10 +4875,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131600442</v>
+        <v>131603307</v>
       </c>
       <c r="B43" t="n">
-        <v>79856</v>
+        <v>57907</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4881,34 +4886,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464251</v>
+        <v>464265</v>
       </c>
       <c r="R43" t="n">
-        <v>6758281</v>
+        <v>6758140</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4941,6 +4951,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4967,10 +4982,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131600551</v>
+        <v>131603971</v>
       </c>
       <c r="B44" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4978,39 +4993,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464263</v>
+        <v>464384</v>
       </c>
       <c r="R44" t="n">
-        <v>6758298</v>
+        <v>6758179</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5043,6 +5053,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5084,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131603307</v>
+        <v>131597848</v>
       </c>
       <c r="B45" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5080,39 +5095,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464265</v>
+        <v>464205</v>
       </c>
       <c r="R45" t="n">
-        <v>6758140</v>
+        <v>6758160</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5145,11 +5155,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5176,10 +5181,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131603971</v>
+        <v>131600442</v>
       </c>
       <c r="B46" t="n">
-        <v>79266</v>
+        <v>79859</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5187,21 +5192,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5211,10 +5216,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464384</v>
+        <v>464251</v>
       </c>
       <c r="R46" t="n">
-        <v>6758179</v>
+        <v>6758281</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5247,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5281,7 +5281,7 @@
         <v>131599244</v>
       </c>
       <c r="B47" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>131594252</v>
       </c>
       <c r="B48" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>131586790</v>
       </c>
       <c r="B49" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131605450</v>
+        <v>131586702</v>
       </c>
       <c r="B50" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,40 +5598,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464189</v>
+        <v>464051</v>
       </c>
       <c r="R50" t="n">
-        <v>6757919</v>
+        <v>6758034</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5663,18 +5665,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5689,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131586702</v>
+        <v>131605450</v>
       </c>
       <c r="B51" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5704,42 +5700,40 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464051</v>
+        <v>464189</v>
       </c>
       <c r="R51" t="n">
-        <v>6758034</v>
+        <v>6757919</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5771,12 +5765,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131586572</v>
+        <v>131605468</v>
       </c>
       <c r="B52" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5806,37 +5806,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464052</v>
+        <v>464189</v>
       </c>
       <c r="R52" t="n">
-        <v>6758021</v>
+        <v>6757919</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5892,10 +5900,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131605468</v>
+        <v>131586572</v>
       </c>
       <c r="B53" t="n">
-        <v>57901</v>
+        <v>79269</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5903,45 +5911,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464189</v>
+        <v>464052</v>
       </c>
       <c r="R53" t="n">
-        <v>6757919</v>
+        <v>6758021</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>131601417</v>
       </c>
       <c r="B54" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>131604599</v>
       </c>
       <c r="B55" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>131605027</v>
       </c>
       <c r="B56" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6298,10 +6298,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131596208</v>
+        <v>131604358</v>
       </c>
       <c r="B57" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6309,34 +6309,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464135</v>
+        <v>464439</v>
       </c>
       <c r="R57" t="n">
-        <v>6758234</v>
+        <v>6758140</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6369,6 +6374,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6395,10 +6405,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131595863</v>
+        <v>131601410</v>
       </c>
       <c r="B58" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6406,34 +6416,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464112</v>
+        <v>464317</v>
       </c>
       <c r="R58" t="n">
-        <v>6758222</v>
+        <v>6758312</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6466,6 +6481,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6492,38 +6512,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131601410</v>
+        <v>131587027</v>
       </c>
       <c r="B59" t="n">
-        <v>57904</v>
+        <v>57095</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6532,10 +6552,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464317</v>
+        <v>464056</v>
       </c>
       <c r="R59" t="n">
-        <v>6758312</v>
+        <v>6758091</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6572,7 +6592,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>1 bild, ringhack och garn</t>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6599,10 +6619,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131604358</v>
+        <v>131596208</v>
       </c>
       <c r="B60" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6610,39 +6630,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464439</v>
+        <v>464135</v>
       </c>
       <c r="R60" t="n">
-        <v>6758140</v>
+        <v>6758234</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6675,11 +6690,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6706,10 +6716,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131586922</v>
+        <v>131595863</v>
       </c>
       <c r="B61" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6717,39 +6727,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464054</v>
+        <v>464112</v>
       </c>
       <c r="R61" t="n">
-        <v>6758066</v>
+        <v>6758222</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6808,38 +6813,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131587027</v>
+        <v>131586922</v>
       </c>
       <c r="B62" t="n">
-        <v>57092</v>
+        <v>57907</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6848,10 +6853,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464056</v>
+        <v>464054</v>
       </c>
       <c r="R62" t="n">
-        <v>6758091</v>
+        <v>6758066</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6884,11 +6889,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6918,7 +6918,7 @@
         <v>131602531</v>
       </c>
       <c r="B63" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>131603229</v>
       </c>
       <c r="B64" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>131806044</v>
       </c>
       <c r="B65" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>131806025</v>
       </c>
       <c r="B66" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>131806001</v>
       </c>
       <c r="B67" t="n">
-        <v>92506</v>
+        <v>92509</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7448,10 +7448,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131806043</v>
+        <v>131806066</v>
       </c>
       <c r="B68" t="n">
-        <v>79266</v>
+        <v>78935</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7459,21 +7459,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464078</v>
+        <v>464255</v>
       </c>
       <c r="R68" t="n">
-        <v>6758160</v>
+        <v>6758034</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7555,10 +7555,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131806066</v>
+        <v>131806043</v>
       </c>
       <c r="B69" t="n">
-        <v>78932</v>
+        <v>79269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7566,21 +7566,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464255</v>
+        <v>464078</v>
       </c>
       <c r="R69" t="n">
-        <v>6758034</v>
+        <v>6758160</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7662,50 +7662,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131806056</v>
+        <v>131805997</v>
       </c>
       <c r="B70" t="n">
-        <v>57904</v>
+        <v>92301</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464295</v>
+        <v>464284</v>
       </c>
       <c r="R70" t="n">
-        <v>6757996</v>
+        <v>6758164</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7737,7 +7732,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7747,7 +7742,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7774,50 +7769,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131805986</v>
+        <v>131805980</v>
       </c>
       <c r="B71" t="n">
-        <v>4774</v>
+        <v>91841</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464254</v>
+        <v>464132</v>
       </c>
       <c r="R71" t="n">
-        <v>6758196</v>
+        <v>6757988</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7849,7 +7839,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7859,7 +7849,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,45 +7876,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131805997</v>
+        <v>131806056</v>
       </c>
       <c r="B72" t="n">
-        <v>92298</v>
+        <v>57907</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464284</v>
+        <v>464295</v>
       </c>
       <c r="R72" t="n">
-        <v>6758164</v>
+        <v>6757996</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7956,7 +7951,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7966,7 +7961,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7993,45 +7988,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131805980</v>
+        <v>131805986</v>
       </c>
       <c r="B73" t="n">
-        <v>91838</v>
+        <v>4775</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464132</v>
+        <v>464254</v>
       </c>
       <c r="R73" t="n">
-        <v>6757988</v>
+        <v>6758196</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8100,10 +8100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131806028</v>
+        <v>131806059</v>
       </c>
       <c r="B74" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,34 +8111,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464181</v>
+        <v>464438</v>
       </c>
       <c r="R74" t="n">
-        <v>6757897</v>
+        <v>6758173</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8170,7 +8175,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8180,7 +8185,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8207,10 +8212,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131806059</v>
+        <v>131806028</v>
       </c>
       <c r="B75" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8218,39 +8223,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464438</v>
+        <v>464181</v>
       </c>
       <c r="R75" t="n">
-        <v>6758173</v>
+        <v>6757897</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8319,32 +8319,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131805988</v>
+        <v>131806038</v>
       </c>
       <c r="B76" t="n">
-        <v>80400</v>
+        <v>79269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464189</v>
+        <v>464420</v>
       </c>
       <c r="R76" t="n">
-        <v>6758149</v>
+        <v>6758206</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8410,21 +8410,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8441,32 +8426,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131806038</v>
+        <v>131805988</v>
       </c>
       <c r="B77" t="n">
-        <v>79266</v>
+        <v>80403</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8476,10 +8461,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464420</v>
+        <v>464189</v>
       </c>
       <c r="R77" t="n">
-        <v>6758206</v>
+        <v>6758149</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8511,7 +8496,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8521,7 +8506,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8532,6 +8517,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8551,7 +8551,7 @@
         <v>131806068</v>
       </c>
       <c r="B78" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8660,10 +8660,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131806041</v>
+        <v>131806042</v>
       </c>
       <c r="B79" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464305</v>
+        <v>464267</v>
       </c>
       <c r="R79" t="n">
-        <v>6758161</v>
+        <v>6758179</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8767,10 +8767,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131806042</v>
+        <v>131806029</v>
       </c>
       <c r="B80" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464267</v>
+        <v>464204</v>
       </c>
       <c r="R80" t="n">
-        <v>6758179</v>
+        <v>6757960</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8874,10 +8874,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131806029</v>
+        <v>131806041</v>
       </c>
       <c r="B81" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464204</v>
+        <v>464305</v>
       </c>
       <c r="R81" t="n">
-        <v>6757960</v>
+        <v>6758161</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8984,7 +8984,7 @@
         <v>131805976</v>
       </c>
       <c r="B82" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>131805999</v>
       </c>
       <c r="B83" t="n">
-        <v>97909</v>
+        <v>97912</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>131805998</v>
       </c>
       <c r="B84" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9302,10 +9302,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131806060</v>
+        <v>131806050</v>
       </c>
       <c r="B85" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9342,10 +9342,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464263</v>
+        <v>464143</v>
       </c>
       <c r="R85" t="n">
-        <v>6758180</v>
+        <v>6757875</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9414,10 +9414,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131806050</v>
+        <v>131806049</v>
       </c>
       <c r="B86" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464143</v>
+        <v>464099</v>
       </c>
       <c r="R86" t="n">
-        <v>6757875</v>
+        <v>6757847</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9526,10 +9526,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131806049</v>
+        <v>131806060</v>
       </c>
       <c r="B87" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464099</v>
+        <v>464263</v>
       </c>
       <c r="R87" t="n">
-        <v>6757847</v>
+        <v>6758180</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9641,7 +9641,7 @@
         <v>131806057</v>
       </c>
       <c r="B88" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>131805982</v>
       </c>
       <c r="B89" t="n">
-        <v>92561</v>
+        <v>92564</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>131806040</v>
       </c>
       <c r="B90" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>131805971</v>
       </c>
       <c r="B91" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>131806051</v>
       </c>
       <c r="B92" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>131806048</v>
       </c>
       <c r="B93" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>131805977</v>
       </c>
       <c r="B94" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10402,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806032</v>
+        <v>131806052</v>
       </c>
       <c r="B95" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,34 +10413,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464341</v>
+        <v>464193</v>
       </c>
       <c r="R95" t="n">
-        <v>6757956</v>
+        <v>6757936</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,7 +10477,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10482,7 +10487,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10509,10 +10514,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806030</v>
+        <v>131806032</v>
       </c>
       <c r="B96" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10544,10 +10549,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464204</v>
+        <v>464341</v>
       </c>
       <c r="R96" t="n">
-        <v>6758031</v>
+        <v>6757956</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10579,7 +10584,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10589,7 +10594,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10616,32 +10621,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131805972</v>
+        <v>131806030</v>
       </c>
       <c r="B97" t="n">
-        <v>91801</v>
+        <v>79269</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10651,10 +10656,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464074</v>
+        <v>464204</v>
       </c>
       <c r="R97" t="n">
-        <v>6758064</v>
+        <v>6758031</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10686,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10696,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10723,50 +10728,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131806052</v>
+        <v>131805972</v>
       </c>
       <c r="B98" t="n">
-        <v>57904</v>
+        <v>91804</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464193</v>
+        <v>464074</v>
       </c>
       <c r="R98" t="n">
-        <v>6757936</v>
+        <v>6758064</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10838,7 +10838,7 @@
         <v>131806002</v>
       </c>
       <c r="B99" t="n">
-        <v>79290</v>
+        <v>79293</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>131806000</v>
       </c>
       <c r="B100" t="n">
-        <v>57736</v>
+        <v>57739</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>131806026</v>
       </c>
       <c r="B101" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11161,32 +11161,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131806003</v>
+        <v>131806036</v>
       </c>
       <c r="B102" t="n">
-        <v>80407</v>
+        <v>79269</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464137</v>
+        <v>464459</v>
       </c>
       <c r="R102" t="n">
-        <v>6758186</v>
+        <v>6758165</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11252,21 +11252,6 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -11283,32 +11268,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131805978</v>
+        <v>131806003</v>
       </c>
       <c r="B103" t="n">
-        <v>91838</v>
+        <v>80410</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11318,10 +11303,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464275</v>
+        <v>464137</v>
       </c>
       <c r="R103" t="n">
-        <v>6758069</v>
+        <v>6758186</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11353,7 +11338,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11363,7 +11348,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11374,6 +11359,21 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11390,50 +11390,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131806067</v>
+        <v>131805978</v>
       </c>
       <c r="B104" t="n">
-        <v>5178</v>
+        <v>91841</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464196</v>
+        <v>464275</v>
       </c>
       <c r="R104" t="n">
-        <v>6757964</v>
+        <v>6758069</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11465,7 +11460,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11475,7 +11470,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11502,38 +11497,38 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806058</v>
+        <v>131806067</v>
       </c>
       <c r="B105" t="n">
-        <v>57904</v>
+        <v>5179</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11542,10 +11537,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464435</v>
+        <v>464196</v>
       </c>
       <c r="R105" t="n">
-        <v>6758156</v>
+        <v>6757964</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11577,7 +11572,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11587,7 +11582,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11614,10 +11609,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806036</v>
+        <v>131806058</v>
       </c>
       <c r="B106" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11625,34 +11620,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464459</v>
+        <v>464435</v>
       </c>
       <c r="R106" t="n">
-        <v>6758165</v>
+        <v>6758156</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11721,45 +11721,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131805989</v>
+        <v>131806007</v>
       </c>
       <c r="B107" t="n">
-        <v>80400</v>
+        <v>99047</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464196</v>
+        <v>464255</v>
       </c>
       <c r="R107" t="n">
-        <v>6758006</v>
+        <v>6758034</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11791,7 +11800,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11801,7 +11810,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11812,21 +11821,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11843,54 +11837,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131806007</v>
+        <v>131805989</v>
       </c>
       <c r="B108" t="n">
-        <v>99044</v>
+        <v>80403</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464255</v>
+        <v>464196</v>
       </c>
       <c r="R108" t="n">
-        <v>6758034</v>
+        <v>6758006</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11922,7 +11907,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11932,7 +11917,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11943,6 +11928,21 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -11962,7 +11962,7 @@
         <v>131806037</v>
       </c>
       <c r="B109" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12066,10 +12066,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131806034</v>
+        <v>131806031</v>
       </c>
       <c r="B110" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12101,10 +12101,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464383</v>
+        <v>464219</v>
       </c>
       <c r="R110" t="n">
-        <v>6758151</v>
+        <v>6758055</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12173,10 +12173,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131806031</v>
+        <v>131805979</v>
       </c>
       <c r="B111" t="n">
-        <v>79266</v>
+        <v>91841</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12184,21 +12184,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464219</v>
+        <v>464400</v>
       </c>
       <c r="R111" t="n">
-        <v>6758055</v>
+        <v>6758180</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12280,10 +12280,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131805979</v>
+        <v>131806034</v>
       </c>
       <c r="B112" t="n">
-        <v>91838</v>
+        <v>79269</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12291,21 +12291,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464400</v>
+        <v>464383</v>
       </c>
       <c r="R112" t="n">
-        <v>6758180</v>
+        <v>6758151</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12390,7 +12390,7 @@
         <v>131806039</v>
       </c>
       <c r="B113" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>131806027</v>
       </c>
       <c r="B114" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>131805970</v>
       </c>
       <c r="B115" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12708,32 +12708,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131806033</v>
+        <v>131805987</v>
       </c>
       <c r="B116" t="n">
-        <v>79266</v>
+        <v>80403</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464363</v>
+        <v>464138</v>
       </c>
       <c r="R116" t="n">
-        <v>6758150</v>
+        <v>6758188</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12799,6 +12799,21 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -12815,10 +12830,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131806035</v>
+        <v>131806033</v>
       </c>
       <c r="B117" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12850,10 +12865,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464460</v>
+        <v>464363</v>
       </c>
       <c r="R117" t="n">
-        <v>6758144</v>
+        <v>6758150</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12885,7 +12900,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12895,7 +12910,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12922,32 +12937,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131805987</v>
+        <v>131806035</v>
       </c>
       <c r="B118" t="n">
-        <v>80400</v>
+        <v>79269</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12957,10 +12972,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464138</v>
+        <v>464460</v>
       </c>
       <c r="R118" t="n">
-        <v>6758188</v>
+        <v>6758144</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12992,7 +13007,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13002,7 +13017,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13013,21 +13028,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13047,7 +13047,7 @@
         <v>131805990</v>
       </c>
       <c r="B119" t="n">
-        <v>91788</v>
+        <v>91791</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>131806004</v>
       </c>
       <c r="B120" t="n">
-        <v>81251</v>
+        <v>81254</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>131806061</v>
       </c>
       <c r="B121" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>131806069</v>
       </c>
       <c r="B122" t="n">
-        <v>91793</v>
+        <v>91794</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1222,7 +1222,7 @@
         <v>131592130</v>
       </c>
       <c r="B7" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>131589374</v>
       </c>
       <c r="B8" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>131587086</v>
       </c>
       <c r="B9" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131604477</v>
+        <v>131605369</v>
       </c>
       <c r="B10" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,42 +1526,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464463</v>
+        <v>464271</v>
       </c>
       <c r="R10" t="n">
-        <v>6758106</v>
+        <v>6757950</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1595,7 +1593,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1604,6 +1602,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1622,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131605369</v>
+        <v>131604477</v>
       </c>
       <c r="B11" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,40 +1632,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464271</v>
+        <v>464463</v>
       </c>
       <c r="R11" t="n">
-        <v>6757950</v>
+        <v>6758106</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1700,7 +1701,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+          <t>2 bilder , tall samt miljöbild där garn hänger till höger</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,7 +1710,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>131587093</v>
       </c>
       <c r="B12" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131601638</v>
+        <v>131593794</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>79274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,39 +1836,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464298</v>
+        <v>464022</v>
       </c>
       <c r="R13" t="n">
-        <v>6758264</v>
+        <v>6758156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1900,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1 bild gran</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131593794</v>
+        <v>131595645</v>
       </c>
       <c r="B14" t="n">
-        <v>79269</v>
+        <v>83254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,34 +1938,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464022</v>
+        <v>464112</v>
       </c>
       <c r="R14" t="n">
-        <v>6758156</v>
+        <v>6758222</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,7 +2005,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>5 st Miljöbilder bland annat på en bäck</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,6 +2014,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2034,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131595645</v>
+        <v>131586783</v>
       </c>
       <c r="B15" t="n">
-        <v>83249</v>
+        <v>57912</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,26 +2044,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2072,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464112</v>
+        <v>464041</v>
       </c>
       <c r="R15" t="n">
-        <v>6758222</v>
+        <v>6758056</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2110,18 +2114,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>5 st Miljöbilder bland annat på en bäck</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2140,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131586783</v>
+        <v>131601638</v>
       </c>
       <c r="B16" t="n">
-        <v>57907</v>
+        <v>57909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,16 +2149,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2169,24 +2167,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464041</v>
+        <v>464298</v>
       </c>
       <c r="R16" t="n">
-        <v>6758056</v>
+        <v>6758264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,6 +2214,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131600419</v>
+        <v>131594186</v>
       </c>
       <c r="B17" t="n">
-        <v>79888</v>
+        <v>79274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464251</v>
+        <v>464035</v>
       </c>
       <c r="R17" t="n">
-        <v>6758281</v>
+        <v>6758187</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2350,7 +2350,7 @@
         <v>131604098</v>
       </c>
       <c r="B18" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594186</v>
+        <v>131600419</v>
       </c>
       <c r="B19" t="n">
-        <v>79269</v>
+        <v>79893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464035</v>
+        <v>464251</v>
       </c>
       <c r="R19" t="n">
-        <v>6758187</v>
+        <v>6758281</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131601488</v>
+        <v>131591075</v>
       </c>
       <c r="B20" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2567,37 +2567,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464297</v>
+        <v>464053</v>
       </c>
       <c r="R20" t="n">
-        <v>6758284</v>
+        <v>6758144</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2627,11 +2632,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131591075</v>
+        <v>131601488</v>
       </c>
       <c r="B21" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,42 +2669,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464053</v>
+        <v>464297</v>
       </c>
       <c r="R21" t="n">
-        <v>6758144</v>
+        <v>6758284</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2734,6 +2729,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2763,7 +2763,7 @@
         <v>131593946</v>
       </c>
       <c r="B22" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>131602481</v>
       </c>
       <c r="B23" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>131600576</v>
       </c>
       <c r="B24" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131586743</v>
+        <v>131604893</v>
       </c>
       <c r="B25" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464052</v>
+        <v>464457</v>
       </c>
       <c r="R25" t="n">
-        <v>6758047</v>
+        <v>6758015</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3127,6 +3127,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3156,7 +3161,7 @@
         <v>131604566</v>
       </c>
       <c r="B26" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3260,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131604893</v>
+        <v>131586743</v>
       </c>
       <c r="B27" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3295,13 +3300,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464457</v>
+        <v>464052</v>
       </c>
       <c r="R27" t="n">
-        <v>6758015</v>
+        <v>6758047</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3331,11 +3336,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3362,10 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131597701</v>
+        <v>131591546</v>
       </c>
       <c r="B28" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464192</v>
+        <v>464053</v>
       </c>
       <c r="R28" t="n">
-        <v>6758156</v>
+        <v>6758144</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3459,53 +3459,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131586714</v>
+        <v>131597701</v>
       </c>
       <c r="B29" t="n">
-        <v>57095</v>
+        <v>79274</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464060</v>
+        <v>464192</v>
       </c>
       <c r="R29" t="n">
-        <v>6758044</v>
+        <v>6758156</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3561,50 +3556,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131604756</v>
+        <v>131594493</v>
       </c>
       <c r="B30" t="n">
-        <v>57095</v>
+        <v>79274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464541</v>
+        <v>464034</v>
       </c>
       <c r="R30" t="n">
-        <v>6758017</v>
+        <v>6758248</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3639,12 +3632,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2 bilder, bäck</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3663,38 +3662,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131604670</v>
+        <v>131586714</v>
       </c>
       <c r="B31" t="n">
-        <v>57907</v>
+        <v>57100</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3703,13 +3702,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464483</v>
+        <v>464060</v>
       </c>
       <c r="R31" t="n">
-        <v>6758032</v>
+        <v>6758044</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3739,11 +3738,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3770,38 +3764,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131603524</v>
+        <v>131600797</v>
       </c>
       <c r="B32" t="n">
-        <v>57907</v>
+        <v>99052</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>95</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3810,10 +3803,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464384</v>
+        <v>464314</v>
       </c>
       <c r="R32" t="n">
-        <v>6758179</v>
+        <v>6758387</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3846,11 +3839,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3877,45 +3865,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131591546</v>
+        <v>131604756</v>
       </c>
       <c r="B33" t="n">
-        <v>79269</v>
+        <v>57100</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464053</v>
+        <v>464541</v>
       </c>
       <c r="R33" t="n">
-        <v>6758144</v>
+        <v>6758017</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3974,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131594493</v>
+        <v>131603524</v>
       </c>
       <c r="B34" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3985,37 +3978,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464034</v>
+        <v>464384</v>
       </c>
       <c r="R34" t="n">
-        <v>6758248</v>
+        <v>6758179</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4052,7 +4047,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>2 bilder, bäck</t>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4061,7 +4056,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4080,37 +4074,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131600797</v>
+        <v>131604670</v>
       </c>
       <c r="B35" t="n">
-        <v>99047</v>
+        <v>57912</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>95</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4119,10 +4114,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464314</v>
+        <v>464483</v>
       </c>
       <c r="R35" t="n">
-        <v>6758387</v>
+        <v>6758032</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,6 +4150,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4184,7 +4184,7 @@
         <v>131600974</v>
       </c>
       <c r="B36" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131603322</v>
+        <v>131586494</v>
       </c>
       <c r="B37" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464265</v>
+        <v>464066</v>
       </c>
       <c r="R37" t="n">
-        <v>6758140</v>
+        <v>6757982</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131600594</v>
+        <v>131586581</v>
       </c>
       <c r="B38" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464296</v>
+        <v>464051</v>
       </c>
       <c r="R38" t="n">
-        <v>6758304</v>
+        <v>6758034</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,11 +4451,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4482,10 +4477,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131586494</v>
+        <v>131603322</v>
       </c>
       <c r="B39" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4517,10 +4512,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464066</v>
+        <v>464265</v>
       </c>
       <c r="R39" t="n">
-        <v>6757982</v>
+        <v>6758140</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4579,10 +4574,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131586581</v>
+        <v>131600594</v>
       </c>
       <c r="B40" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4614,10 +4609,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464051</v>
+        <v>464296</v>
       </c>
       <c r="R40" t="n">
-        <v>6758034</v>
+        <v>6758304</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4650,6 +4645,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4679,7 +4679,7 @@
         <v>131599422</v>
       </c>
       <c r="B41" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>131600551</v>
       </c>
       <c r="B42" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>131603307</v>
       </c>
       <c r="B43" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4982,10 +4982,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131603971</v>
+        <v>131600442</v>
       </c>
       <c r="B44" t="n">
-        <v>79269</v>
+        <v>79864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4993,21 +4993,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464384</v>
+        <v>464251</v>
       </c>
       <c r="R44" t="n">
-        <v>6758179</v>
+        <v>6758281</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,11 +5053,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5087,7 +5082,7 @@
         <v>131597848</v>
       </c>
       <c r="B45" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5181,10 +5176,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131600442</v>
+        <v>131603971</v>
       </c>
       <c r="B46" t="n">
-        <v>79859</v>
+        <v>79274</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5192,21 +5187,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5216,10 +5211,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464251</v>
+        <v>464384</v>
       </c>
       <c r="R46" t="n">
-        <v>6758281</v>
+        <v>6758179</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5252,6 +5247,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5281,7 +5281,7 @@
         <v>131599244</v>
       </c>
       <c r="B47" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5385,53 +5385,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131594252</v>
+        <v>131586790</v>
       </c>
       <c r="B48" t="n">
-        <v>57095</v>
+        <v>79274</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464049</v>
+        <v>464046</v>
       </c>
       <c r="R48" t="n">
-        <v>6758189</v>
+        <v>6758049</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5490,45 +5482,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131586790</v>
+        <v>131594252</v>
       </c>
       <c r="B49" t="n">
-        <v>79269</v>
+        <v>57100</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464046</v>
+        <v>464049</v>
       </c>
       <c r="R49" t="n">
-        <v>6758049</v>
+        <v>6758189</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5590,7 +5590,7 @@
         <v>131586702</v>
       </c>
       <c r="B50" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>131605450</v>
       </c>
       <c r="B51" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131605468</v>
+        <v>131586572</v>
       </c>
       <c r="B52" t="n">
-        <v>57904</v>
+        <v>79274</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5806,45 +5806,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464189</v>
+        <v>464052</v>
       </c>
       <c r="R52" t="n">
-        <v>6757919</v>
+        <v>6758021</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5900,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131586572</v>
+        <v>131601417</v>
       </c>
       <c r="B53" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5935,10 +5927,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464052</v>
+        <v>464317</v>
       </c>
       <c r="R53" t="n">
-        <v>6758021</v>
+        <v>6758312</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5997,10 +5989,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131601417</v>
+        <v>131604599</v>
       </c>
       <c r="B54" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6032,13 +6024,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464317</v>
+        <v>464472</v>
       </c>
       <c r="R54" t="n">
-        <v>6758312</v>
+        <v>6758076</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6068,6 +6060,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6094,10 +6091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131604599</v>
+        <v>131605027</v>
       </c>
       <c r="B55" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6129,10 +6126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464472</v>
+        <v>464394</v>
       </c>
       <c r="R55" t="n">
-        <v>6758076</v>
+        <v>6758039</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6169,7 +6166,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6196,10 +6193,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131605027</v>
+        <v>131605468</v>
       </c>
       <c r="B56" t="n">
-        <v>79269</v>
+        <v>57909</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6207,34 +6204,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464394</v>
+        <v>464189</v>
       </c>
       <c r="R56" t="n">
-        <v>6758039</v>
+        <v>6757919</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6267,11 +6272,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6298,38 +6298,38 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131604358</v>
+        <v>131587027</v>
       </c>
       <c r="B57" t="n">
-        <v>57907</v>
+        <v>57100</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464439</v>
+        <v>464056</v>
       </c>
       <c r="R57" t="n">
-        <v>6758140</v>
+        <v>6758091</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6408,7 +6408,7 @@
         <v>131601410</v>
       </c>
       <c r="B58" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6512,38 +6512,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131587027</v>
+        <v>131604358</v>
       </c>
       <c r="B59" t="n">
-        <v>57095</v>
+        <v>57912</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6552,10 +6552,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464056</v>
+        <v>464439</v>
       </c>
       <c r="R59" t="n">
-        <v>6758091</v>
+        <v>6758140</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Spillning under tjädertall</t>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6622,7 +6622,7 @@
         <v>131596208</v>
       </c>
       <c r="B60" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>131595863</v>
       </c>
       <c r="B61" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>131586922</v>
       </c>
       <c r="B62" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>131602531</v>
       </c>
       <c r="B63" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>131603229</v>
       </c>
       <c r="B64" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>131806044</v>
       </c>
       <c r="B65" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>131806025</v>
       </c>
       <c r="B66" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>131806001</v>
       </c>
       <c r="B67" t="n">
-        <v>92509</v>
+        <v>92514</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7448,10 +7448,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131806066</v>
+        <v>131806043</v>
       </c>
       <c r="B68" t="n">
-        <v>78935</v>
+        <v>79274</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7459,21 +7459,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464255</v>
+        <v>464078</v>
       </c>
       <c r="R68" t="n">
-        <v>6758034</v>
+        <v>6758160</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7555,10 +7555,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131806043</v>
+        <v>131806066</v>
       </c>
       <c r="B69" t="n">
-        <v>79269</v>
+        <v>78940</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7566,21 +7566,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464078</v>
+        <v>464255</v>
       </c>
       <c r="R69" t="n">
-        <v>6758160</v>
+        <v>6758034</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7665,7 +7665,7 @@
         <v>131805997</v>
       </c>
       <c r="B70" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>131805980</v>
       </c>
       <c r="B71" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7876,38 +7876,38 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131806056</v>
+        <v>131805986</v>
       </c>
       <c r="B72" t="n">
-        <v>57907</v>
+        <v>4775</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7916,10 +7916,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464295</v>
+        <v>464254</v>
       </c>
       <c r="R72" t="n">
-        <v>6757996</v>
+        <v>6758196</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,38 +7988,38 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131805986</v>
+        <v>131806056</v>
       </c>
       <c r="B73" t="n">
-        <v>4775</v>
+        <v>57912</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464254</v>
+        <v>464295</v>
       </c>
       <c r="R73" t="n">
-        <v>6758196</v>
+        <v>6757996</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8100,10 +8100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131806059</v>
+        <v>131806028</v>
       </c>
       <c r="B74" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,39 +8111,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464438</v>
+        <v>464181</v>
       </c>
       <c r="R74" t="n">
-        <v>6758173</v>
+        <v>6757897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8175,7 +8170,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8185,7 +8180,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8212,10 +8207,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131806028</v>
+        <v>131806059</v>
       </c>
       <c r="B75" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8223,34 +8218,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464181</v>
+        <v>464438</v>
       </c>
       <c r="R75" t="n">
-        <v>6757897</v>
+        <v>6758173</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8322,7 +8322,7 @@
         <v>131806038</v>
       </c>
       <c r="B76" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>131805988</v>
       </c>
       <c r="B77" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>131806068</v>
       </c>
       <c r="B78" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>131806042</v>
       </c>
       <c r="B79" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>131806029</v>
       </c>
       <c r="B80" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>131806041</v>
       </c>
       <c r="B81" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>131805976</v>
       </c>
       <c r="B82" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>131805999</v>
       </c>
       <c r="B83" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>131805998</v>
       </c>
       <c r="B84" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9302,10 +9302,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131806050</v>
+        <v>131806060</v>
       </c>
       <c r="B85" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9342,10 +9342,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464143</v>
+        <v>464263</v>
       </c>
       <c r="R85" t="n">
-        <v>6757875</v>
+        <v>6758180</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9414,10 +9414,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131806049</v>
+        <v>131806050</v>
       </c>
       <c r="B86" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464099</v>
+        <v>464143</v>
       </c>
       <c r="R86" t="n">
-        <v>6757847</v>
+        <v>6757875</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9526,10 +9526,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131806060</v>
+        <v>131806049</v>
       </c>
       <c r="B87" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464263</v>
+        <v>464099</v>
       </c>
       <c r="R87" t="n">
-        <v>6758180</v>
+        <v>6757847</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9641,7 +9641,7 @@
         <v>131806057</v>
       </c>
       <c r="B88" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>131805982</v>
       </c>
       <c r="B89" t="n">
-        <v>92564</v>
+        <v>92569</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>131806040</v>
       </c>
       <c r="B90" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>131805971</v>
       </c>
       <c r="B91" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10071,10 +10071,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131806051</v>
+        <v>131805977</v>
       </c>
       <c r="B92" t="n">
-        <v>57907</v>
+        <v>91846</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10082,39 +10082,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464172</v>
+        <v>464313</v>
       </c>
       <c r="R92" t="n">
-        <v>6757903</v>
+        <v>6757941</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10146,7 +10141,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10156,7 +10151,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10183,10 +10178,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131806048</v>
+        <v>131806051</v>
       </c>
       <c r="B93" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10214,7 +10209,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10223,10 +10218,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464290</v>
+        <v>464172</v>
       </c>
       <c r="R93" t="n">
-        <v>6758088</v>
+        <v>6757903</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10258,7 +10253,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10268,7 +10263,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10295,10 +10290,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131805977</v>
+        <v>131806048</v>
       </c>
       <c r="B94" t="n">
-        <v>91841</v>
+        <v>57912</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10306,34 +10301,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464313</v>
+        <v>464290</v>
       </c>
       <c r="R94" t="n">
-        <v>6757941</v>
+        <v>6758088</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10402,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806052</v>
+        <v>131806032</v>
       </c>
       <c r="B95" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,39 +10413,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464193</v>
+        <v>464341</v>
       </c>
       <c r="R95" t="n">
-        <v>6757936</v>
+        <v>6757956</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10477,7 +10472,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10487,7 +10482,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10514,32 +10509,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806032</v>
+        <v>131805972</v>
       </c>
       <c r="B96" t="n">
-        <v>79269</v>
+        <v>91809</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10549,10 +10544,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464341</v>
+        <v>464074</v>
       </c>
       <c r="R96" t="n">
-        <v>6757956</v>
+        <v>6758064</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10584,7 +10579,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10594,7 +10589,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10621,10 +10616,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806030</v>
+        <v>131806052</v>
       </c>
       <c r="B97" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10632,34 +10627,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464204</v>
+        <v>464193</v>
       </c>
       <c r="R97" t="n">
-        <v>6758031</v>
+        <v>6757936</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10728,32 +10728,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131805972</v>
+        <v>131806030</v>
       </c>
       <c r="B98" t="n">
-        <v>91804</v>
+        <v>79274</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464074</v>
+        <v>464204</v>
       </c>
       <c r="R98" t="n">
-        <v>6758064</v>
+        <v>6758031</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10838,7 +10838,7 @@
         <v>131806002</v>
       </c>
       <c r="B99" t="n">
-        <v>79293</v>
+        <v>79298</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>131806000</v>
       </c>
       <c r="B100" t="n">
-        <v>57739</v>
+        <v>57744</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>131806026</v>
       </c>
       <c r="B101" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11161,45 +11161,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131806036</v>
+        <v>131806067</v>
       </c>
       <c r="B102" t="n">
-        <v>79269</v>
+        <v>5179</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464459</v>
+        <v>464196</v>
       </c>
       <c r="R102" t="n">
-        <v>6758165</v>
+        <v>6757964</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11231,7 +11236,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11241,7 +11246,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11268,45 +11273,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131806003</v>
+        <v>131806058</v>
       </c>
       <c r="B103" t="n">
-        <v>80410</v>
+        <v>57912</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464137</v>
+        <v>464435</v>
       </c>
       <c r="R103" t="n">
-        <v>6758186</v>
+        <v>6758156</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11338,7 +11348,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11348,7 +11358,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11359,21 +11369,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11393,7 +11388,7 @@
         <v>131805978</v>
       </c>
       <c r="B104" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11497,10 +11492,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806067</v>
+        <v>131806003</v>
       </c>
       <c r="B105" t="n">
-        <v>5179</v>
+        <v>80415</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11508,39 +11503,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464196</v>
+        <v>464137</v>
       </c>
       <c r="R105" t="n">
-        <v>6757964</v>
+        <v>6758186</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11572,7 +11562,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11582,7 +11572,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11593,6 +11583,21 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11609,10 +11614,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806058</v>
+        <v>131806036</v>
       </c>
       <c r="B106" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11620,39 +11625,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464435</v>
+        <v>464459</v>
       </c>
       <c r="R106" t="n">
-        <v>6758156</v>
+        <v>6758165</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11724,7 +11724,7 @@
         <v>131806007</v>
       </c>
       <c r="B107" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>131805989</v>
       </c>
       <c r="B108" t="n">
-        <v>80403</v>
+        <v>80408</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>131806037</v>
       </c>
       <c r="B109" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12066,10 +12066,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131806031</v>
+        <v>131806034</v>
       </c>
       <c r="B110" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12101,10 +12101,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464219</v>
+        <v>464383</v>
       </c>
       <c r="R110" t="n">
-        <v>6758055</v>
+        <v>6758151</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12173,10 +12173,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131805979</v>
+        <v>131806031</v>
       </c>
       <c r="B111" t="n">
-        <v>91841</v>
+        <v>79274</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12184,21 +12184,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464400</v>
+        <v>464219</v>
       </c>
       <c r="R111" t="n">
-        <v>6758180</v>
+        <v>6758055</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12280,10 +12280,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131806034</v>
+        <v>131805979</v>
       </c>
       <c r="B112" t="n">
-        <v>79269</v>
+        <v>91846</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12291,21 +12291,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464383</v>
+        <v>464400</v>
       </c>
       <c r="R112" t="n">
-        <v>6758151</v>
+        <v>6758180</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12387,10 +12387,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131806039</v>
+        <v>131805990</v>
       </c>
       <c r="B113" t="n">
-        <v>79269</v>
+        <v>91796</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464338</v>
+        <v>464391</v>
       </c>
       <c r="R113" t="n">
-        <v>6758168</v>
+        <v>6758144</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131806027</v>
+        <v>131806004</v>
       </c>
       <c r="B114" t="n">
-        <v>79269</v>
+        <v>81259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464171</v>
+        <v>464261</v>
       </c>
       <c r="R114" t="n">
-        <v>6757887</v>
+        <v>6758029</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12601,32 +12601,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131805970</v>
+        <v>131806039</v>
       </c>
       <c r="B115" t="n">
-        <v>91804</v>
+        <v>79274</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464109</v>
+        <v>464338</v>
       </c>
       <c r="R115" t="n">
-        <v>6757856</v>
+        <v>6758168</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12708,32 +12708,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131805987</v>
+        <v>131806027</v>
       </c>
       <c r="B116" t="n">
-        <v>80403</v>
+        <v>79274</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464138</v>
+        <v>464171</v>
       </c>
       <c r="R116" t="n">
-        <v>6758188</v>
+        <v>6757887</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12799,21 +12799,6 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -12830,32 +12815,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131806033</v>
+        <v>131805970</v>
       </c>
       <c r="B117" t="n">
-        <v>79269</v>
+        <v>91809</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12865,10 +12850,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464363</v>
+        <v>464109</v>
       </c>
       <c r="R117" t="n">
-        <v>6758150</v>
+        <v>6757856</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12900,7 +12885,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12910,7 +12895,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12937,32 +12922,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131806035</v>
+        <v>131805987</v>
       </c>
       <c r="B118" t="n">
-        <v>79269</v>
+        <v>80408</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12972,10 +12957,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464460</v>
+        <v>464138</v>
       </c>
       <c r="R118" t="n">
-        <v>6758144</v>
+        <v>6758188</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13007,7 +12992,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13017,7 +13002,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13028,6 +13013,21 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13044,10 +13044,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131805990</v>
+        <v>131806033</v>
       </c>
       <c r="B119" t="n">
-        <v>91791</v>
+        <v>79274</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13055,21 +13055,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13079,10 +13079,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464391</v>
+        <v>464363</v>
       </c>
       <c r="R119" t="n">
-        <v>6758144</v>
+        <v>6758150</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13151,10 +13151,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131806004</v>
+        <v>131806035</v>
       </c>
       <c r="B120" t="n">
-        <v>81254</v>
+        <v>79274</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13162,21 +13162,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464261</v>
+        <v>464460</v>
       </c>
       <c r="R120" t="n">
-        <v>6758029</v>
+        <v>6758144</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13221,7 +13221,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13261,7 +13261,7 @@
         <v>131806061</v>
       </c>
       <c r="B121" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>131806069</v>
       </c>
       <c r="B122" t="n">
-        <v>91794</v>
+        <v>91799</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131594186</v>
+        <v>131600419</v>
       </c>
       <c r="B17" t="n">
-        <v>79274</v>
+        <v>79893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464035</v>
+        <v>464251</v>
       </c>
       <c r="R17" t="n">
-        <v>6758187</v>
+        <v>6758281</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,10 +2454,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131600419</v>
+        <v>131594186</v>
       </c>
       <c r="B19" t="n">
-        <v>79893</v>
+        <v>79274</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464251</v>
+        <v>464035</v>
       </c>
       <c r="R19" t="n">
-        <v>6758281</v>
+        <v>6758187</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3362,48 +3362,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131591546</v>
+        <v>131586714</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>57100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464053</v>
+        <v>464060</v>
       </c>
       <c r="R28" t="n">
-        <v>6758144</v>
+        <v>6758044</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3459,45 +3464,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131597701</v>
+        <v>131600797</v>
       </c>
       <c r="B29" t="n">
-        <v>79274</v>
+        <v>99052</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464192</v>
+        <v>464314</v>
       </c>
       <c r="R29" t="n">
-        <v>6758156</v>
+        <v>6758387</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,48 +3565,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131594493</v>
+        <v>131604756</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>57100</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464034</v>
+        <v>464541</v>
       </c>
       <c r="R30" t="n">
-        <v>6758248</v>
+        <v>6758017</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3632,18 +3643,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3662,38 +3667,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131586714</v>
+        <v>131603524</v>
       </c>
       <c r="B31" t="n">
-        <v>57100</v>
+        <v>57912</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3702,13 +3707,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464060</v>
+        <v>464384</v>
       </c>
       <c r="R31" t="n">
-        <v>6758044</v>
+        <v>6758179</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3738,6 +3743,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3764,37 +3774,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131600797</v>
+        <v>131604670</v>
       </c>
       <c r="B32" t="n">
-        <v>99052</v>
+        <v>57912</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>95</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3803,10 +3814,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464314</v>
+        <v>464483</v>
       </c>
       <c r="R32" t="n">
-        <v>6758387</v>
+        <v>6758032</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,6 +3850,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,50 +3881,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131604756</v>
+        <v>131591546</v>
       </c>
       <c r="B33" t="n">
-        <v>57100</v>
+        <v>79274</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464541</v>
+        <v>464053</v>
       </c>
       <c r="R33" t="n">
-        <v>6758017</v>
+        <v>6758144</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,10 +3978,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131603524</v>
+        <v>131597701</v>
       </c>
       <c r="B34" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3978,39 +3989,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464384</v>
+        <v>464192</v>
       </c>
       <c r="R34" t="n">
-        <v>6758179</v>
+        <v>6758156</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,11 +4049,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4074,10 +4075,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131604670</v>
+        <v>131594493</v>
       </c>
       <c r="B35" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4085,39 +4086,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464483</v>
+        <v>464034</v>
       </c>
       <c r="R35" t="n">
-        <v>6758032</v>
+        <v>6758248</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4154,7 +4153,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt med ringhack</t>
+          <t>2 bilder, bäck</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4163,6 +4162,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131600551</v>
+        <v>131600442</v>
       </c>
       <c r="B42" t="n">
-        <v>57912</v>
+        <v>79864</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,39 +4784,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464263</v>
+        <v>464251</v>
       </c>
       <c r="R42" t="n">
-        <v>6758298</v>
+        <v>6758281</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4875,10 +4870,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131603307</v>
+        <v>131597848</v>
       </c>
       <c r="B43" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4886,39 +4881,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464265</v>
+        <v>464205</v>
       </c>
       <c r="R43" t="n">
-        <v>6758140</v>
+        <v>6758160</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,11 +4941,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4982,10 +4967,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131600442</v>
+        <v>131603971</v>
       </c>
       <c r="B44" t="n">
-        <v>79864</v>
+        <v>79274</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4993,21 +4978,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5017,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464251</v>
+        <v>464384</v>
       </c>
       <c r="R44" t="n">
-        <v>6758281</v>
+        <v>6758179</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5053,6 +5038,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5079,10 +5069,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131597848</v>
+        <v>131600551</v>
       </c>
       <c r="B45" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5090,34 +5080,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464205</v>
+        <v>464263</v>
       </c>
       <c r="R45" t="n">
-        <v>6758160</v>
+        <v>6758298</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5176,10 +5171,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131603971</v>
+        <v>131603307</v>
       </c>
       <c r="B46" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5187,34 +5182,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464384</v>
+        <v>464265</v>
       </c>
       <c r="R46" t="n">
-        <v>6758179</v>
+        <v>6758140</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5385,45 +5385,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131586790</v>
+        <v>131594252</v>
       </c>
       <c r="B48" t="n">
-        <v>79274</v>
+        <v>57100</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464046</v>
+        <v>464049</v>
       </c>
       <c r="R48" t="n">
-        <v>6758049</v>
+        <v>6758189</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5482,53 +5490,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131594252</v>
+        <v>131586790</v>
       </c>
       <c r="B49" t="n">
-        <v>57100</v>
+        <v>79274</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464049</v>
+        <v>464046</v>
       </c>
       <c r="R49" t="n">
-        <v>6758189</v>
+        <v>6758049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6298,38 +6298,38 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131587027</v>
+        <v>131601410</v>
       </c>
       <c r="B57" t="n">
-        <v>57100</v>
+        <v>57912</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464056</v>
+        <v>464317</v>
       </c>
       <c r="R57" t="n">
-        <v>6758091</v>
+        <v>6758312</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Spillning under tjädertall</t>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6405,7 +6405,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131601410</v>
+        <v>131604358</v>
       </c>
       <c r="B58" t="n">
         <v>57912</v>
@@ -6436,7 +6436,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464317</v>
+        <v>464439</v>
       </c>
       <c r="R58" t="n">
-        <v>6758312</v>
+        <v>6758140</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>1 bild, ringhack och garn</t>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6512,10 +6512,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131604358</v>
+        <v>131596208</v>
       </c>
       <c r="B59" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6523,39 +6523,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464439</v>
+        <v>464135</v>
       </c>
       <c r="R59" t="n">
-        <v>6758140</v>
+        <v>6758234</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6588,11 +6583,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6619,7 +6609,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131596208</v>
+        <v>131595863</v>
       </c>
       <c r="B60" t="n">
         <v>79274</v>
@@ -6654,10 +6644,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464135</v>
+        <v>464112</v>
       </c>
       <c r="R60" t="n">
-        <v>6758234</v>
+        <v>6758222</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6716,10 +6706,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131595863</v>
+        <v>131586922</v>
       </c>
       <c r="B61" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6727,34 +6717,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464112</v>
+        <v>464054</v>
       </c>
       <c r="R61" t="n">
-        <v>6758222</v>
+        <v>6758066</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6813,38 +6808,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131586922</v>
+        <v>131587027</v>
       </c>
       <c r="B62" t="n">
-        <v>57912</v>
+        <v>57100</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6853,10 +6848,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464054</v>
+        <v>464056</v>
       </c>
       <c r="R62" t="n">
-        <v>6758066</v>
+        <v>6758091</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6889,6 +6884,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8100,10 +8100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131806028</v>
+        <v>131806059</v>
       </c>
       <c r="B74" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,34 +8111,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464181</v>
+        <v>464438</v>
       </c>
       <c r="R74" t="n">
-        <v>6757897</v>
+        <v>6758173</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8170,7 +8175,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8180,7 +8185,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8207,10 +8212,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131806059</v>
+        <v>131806028</v>
       </c>
       <c r="B75" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8218,39 +8223,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464438</v>
+        <v>464181</v>
       </c>
       <c r="R75" t="n">
-        <v>6758173</v>
+        <v>6757897</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8660,10 +8660,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131806042</v>
+        <v>131805976</v>
       </c>
       <c r="B79" t="n">
-        <v>79274</v>
+        <v>91846</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8671,21 +8671,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464267</v>
+        <v>464319</v>
       </c>
       <c r="R79" t="n">
-        <v>6758179</v>
+        <v>6757939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8767,7 +8767,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131806029</v>
+        <v>131806042</v>
       </c>
       <c r="B80" t="n">
         <v>79274</v>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464204</v>
+        <v>464267</v>
       </c>
       <c r="R80" t="n">
-        <v>6757960</v>
+        <v>6758179</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8874,7 +8874,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131806041</v>
+        <v>131806029</v>
       </c>
       <c r="B81" t="n">
         <v>79274</v>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464305</v>
+        <v>464204</v>
       </c>
       <c r="R81" t="n">
-        <v>6758161</v>
+        <v>6757960</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8981,10 +8981,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131805976</v>
+        <v>131806041</v>
       </c>
       <c r="B82" t="n">
-        <v>91846</v>
+        <v>79274</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8992,21 +8992,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464319</v>
+        <v>464305</v>
       </c>
       <c r="R82" t="n">
-        <v>6757939</v>
+        <v>6758161</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10402,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806032</v>
+        <v>131806052</v>
       </c>
       <c r="B95" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,34 +10413,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464341</v>
+        <v>464193</v>
       </c>
       <c r="R95" t="n">
-        <v>6757956</v>
+        <v>6757936</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,7 +10477,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10482,7 +10487,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10509,32 +10514,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131805972</v>
+        <v>131806032</v>
       </c>
       <c r="B96" t="n">
-        <v>91809</v>
+        <v>79274</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10544,10 +10549,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464074</v>
+        <v>464341</v>
       </c>
       <c r="R96" t="n">
-        <v>6758064</v>
+        <v>6757956</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10579,7 +10584,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10589,7 +10594,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10616,10 +10621,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806052</v>
+        <v>131806030</v>
       </c>
       <c r="B97" t="n">
-        <v>57912</v>
+        <v>79274</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10627,39 +10632,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464193</v>
+        <v>464204</v>
       </c>
       <c r="R97" t="n">
-        <v>6757936</v>
+        <v>6758031</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10728,32 +10728,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131806030</v>
+        <v>131805972</v>
       </c>
       <c r="B98" t="n">
-        <v>79274</v>
+        <v>91809</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464204</v>
+        <v>464074</v>
       </c>
       <c r="R98" t="n">
-        <v>6758031</v>
+        <v>6758064</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10835,10 +10835,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131806002</v>
+        <v>131806000</v>
       </c>
       <c r="B99" t="n">
-        <v>79298</v>
+        <v>57744</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10846,34 +10846,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6434</v>
+        <v>102622</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464113</v>
+        <v>464154</v>
       </c>
       <c r="R99" t="n">
-        <v>6757861</v>
+        <v>6758193</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10905,7 +10910,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10915,7 +10920,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10942,10 +10947,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131806000</v>
+        <v>131806002</v>
       </c>
       <c r="B100" t="n">
-        <v>57744</v>
+        <v>79298</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10953,39 +10958,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102622</v>
+        <v>6434</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464154</v>
+        <v>464113</v>
       </c>
       <c r="R100" t="n">
-        <v>6758193</v>
+        <v>6757861</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11161,50 +11161,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131806067</v>
+        <v>131805978</v>
       </c>
       <c r="B102" t="n">
-        <v>5179</v>
+        <v>91846</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464196</v>
+        <v>464275</v>
       </c>
       <c r="R102" t="n">
-        <v>6757964</v>
+        <v>6758069</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11236,7 +11231,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11246,7 +11241,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11273,50 +11268,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131806058</v>
+        <v>131806003</v>
       </c>
       <c r="B103" t="n">
-        <v>57912</v>
+        <v>80415</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464435</v>
+        <v>464137</v>
       </c>
       <c r="R103" t="n">
-        <v>6758156</v>
+        <v>6758186</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11348,7 +11338,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11358,7 +11348,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11369,6 +11359,21 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11385,10 +11390,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131805978</v>
+        <v>131806036</v>
       </c>
       <c r="B104" t="n">
-        <v>91846</v>
+        <v>79274</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11396,21 +11401,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11420,10 +11425,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464275</v>
+        <v>464459</v>
       </c>
       <c r="R104" t="n">
-        <v>6758069</v>
+        <v>6758165</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11455,7 +11460,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11465,7 +11470,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11492,10 +11497,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806003</v>
+        <v>131806067</v>
       </c>
       <c r="B105" t="n">
-        <v>80415</v>
+        <v>5179</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11503,34 +11508,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464137</v>
+        <v>464196</v>
       </c>
       <c r="R105" t="n">
-        <v>6758186</v>
+        <v>6757964</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11562,7 +11572,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11572,7 +11582,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11583,21 +11593,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11614,10 +11609,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806036</v>
+        <v>131806058</v>
       </c>
       <c r="B106" t="n">
-        <v>79274</v>
+        <v>57912</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11625,34 +11620,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464459</v>
+        <v>464435</v>
       </c>
       <c r="R106" t="n">
-        <v>6758165</v>
+        <v>6758156</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12066,10 +12066,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>131806034</v>
+        <v>131805979</v>
       </c>
       <c r="B110" t="n">
-        <v>79274</v>
+        <v>91846</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12077,21 +12077,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12101,10 +12101,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>464383</v>
+        <v>464400</v>
       </c>
       <c r="R110" t="n">
-        <v>6758151</v>
+        <v>6758180</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12173,7 +12173,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>131806031</v>
+        <v>131806034</v>
       </c>
       <c r="B111" t="n">
         <v>79274</v>
@@ -12208,10 +12208,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>464219</v>
+        <v>464383</v>
       </c>
       <c r="R111" t="n">
-        <v>6758055</v>
+        <v>6758151</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12280,10 +12280,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>131805979</v>
+        <v>131806031</v>
       </c>
       <c r="B112" t="n">
-        <v>91846</v>
+        <v>79274</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12291,21 +12291,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>464400</v>
+        <v>464219</v>
       </c>
       <c r="R112" t="n">
-        <v>6758180</v>
+        <v>6758055</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD112" t="b">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -1222,7 +1222,7 @@
         <v>131592130</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>131589374</v>
       </c>
       <c r="B8" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>131587086</v>
       </c>
       <c r="B9" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>131605369</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131604477</v>
       </c>
       <c r="B11" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131587093</v>
       </c>
       <c r="B12" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131593794</v>
+        <v>131586783</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,34 +1836,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464022</v>
+        <v>464041</v>
       </c>
       <c r="R13" t="n">
-        <v>6758156</v>
+        <v>6758056</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,11 +1904,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,10 +1930,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131595645</v>
+        <v>131601638</v>
       </c>
       <c r="B14" t="n">
-        <v>83254</v>
+        <v>57911</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1938,37 +1941,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464112</v>
+        <v>464298</v>
       </c>
       <c r="R14" t="n">
-        <v>6758222</v>
+        <v>6758264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,7 +2010,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>5 st Miljöbilder bland annat på en bäck</t>
+          <t>1 bild gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,7 +2019,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2033,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131586783</v>
+        <v>131593794</v>
       </c>
       <c r="B15" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,42 +2048,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464041</v>
+        <v>464022</v>
       </c>
       <c r="R15" t="n">
-        <v>6758056</v>
+        <v>6758156</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,6 +2108,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131601638</v>
+        <v>131595645</v>
       </c>
       <c r="B16" t="n">
-        <v>57909</v>
+        <v>83256</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,39 +2150,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464298</v>
+        <v>464112</v>
       </c>
       <c r="R16" t="n">
-        <v>6758264</v>
+        <v>6758222</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,7 +2217,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1 bild gran</t>
+          <t>5 st Miljöbilder bland annat på en bäck</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2227,6 +2226,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2245,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131600419</v>
+        <v>131594186</v>
       </c>
       <c r="B17" t="n">
-        <v>79893</v>
+        <v>79276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464251</v>
+        <v>464035</v>
       </c>
       <c r="R17" t="n">
-        <v>6758281</v>
+        <v>6758187</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1 bild, stubbe</t>
+          <t>Rikligt med garnlav. Miljöbild på källa</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2347,10 +2347,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131604098</v>
+        <v>131600419</v>
       </c>
       <c r="B18" t="n">
-        <v>57912</v>
+        <v>79895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2358,39 +2358,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464410</v>
+        <v>464251</v>
       </c>
       <c r="R18" t="n">
-        <v>6758165</v>
+        <v>6758281</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,7 +2422,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>4 bilder, tall</t>
+          <t>1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,10 +2449,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594186</v>
+        <v>131604098</v>
       </c>
       <c r="B19" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,34 +2460,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464035</v>
+        <v>464410</v>
       </c>
       <c r="R19" t="n">
-        <v>6758187</v>
+        <v>6758165</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav. Miljöbild på källa</t>
+          <t>4 bilder, tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2559,7 +2559,7 @@
         <v>131591075</v>
       </c>
       <c r="B20" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>131601488</v>
       </c>
       <c r="B21" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>131593946</v>
       </c>
       <c r="B22" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>131602481</v>
       </c>
       <c r="B23" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>131600576</v>
       </c>
       <c r="B24" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,10 +3056,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131604893</v>
+        <v>131586743</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464457</v>
+        <v>464052</v>
       </c>
       <c r="R25" t="n">
-        <v>6758015</v>
+        <v>6758047</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3127,11 +3127,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3161,7 +3156,7 @@
         <v>131604566</v>
       </c>
       <c r="B26" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3265,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131586743</v>
+        <v>131604893</v>
       </c>
       <c r="B27" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,13 +3295,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464052</v>
+        <v>464457</v>
       </c>
       <c r="R27" t="n">
-        <v>6758047</v>
+        <v>6758015</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3336,6 +3331,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 bild, låga och stubbe i förgrunden. Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3362,53 +3362,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131586714</v>
+        <v>131591546</v>
       </c>
       <c r="B28" t="n">
-        <v>57100</v>
+        <v>79276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464060</v>
+        <v>464053</v>
       </c>
       <c r="R28" t="n">
-        <v>6758044</v>
+        <v>6758144</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3464,49 +3459,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131600797</v>
+        <v>131597701</v>
       </c>
       <c r="B29" t="n">
-        <v>99052</v>
+        <v>79276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464314</v>
+        <v>464192</v>
       </c>
       <c r="R29" t="n">
-        <v>6758387</v>
+        <v>6758156</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3565,50 +3556,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131604756</v>
+        <v>131594493</v>
       </c>
       <c r="B30" t="n">
-        <v>57100</v>
+        <v>79276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464541</v>
+        <v>464034</v>
       </c>
       <c r="R30" t="n">
-        <v>6758017</v>
+        <v>6758248</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3643,12 +3632,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2 bilder, bäck</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3667,38 +3662,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131603524</v>
+        <v>131586714</v>
       </c>
       <c r="B31" t="n">
-        <v>57912</v>
+        <v>57102</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3707,13 +3702,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464384</v>
+        <v>464060</v>
       </c>
       <c r="R31" t="n">
-        <v>6758179</v>
+        <v>6758044</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3743,11 +3738,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3774,38 +3764,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131604670</v>
+        <v>131600797</v>
       </c>
       <c r="B32" t="n">
-        <v>57912</v>
+        <v>99054</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>95</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3814,10 +3803,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464483</v>
+        <v>464314</v>
       </c>
       <c r="R32" t="n">
-        <v>6758032</v>
+        <v>6758387</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3850,11 +3839,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3881,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131591546</v>
+        <v>131604670</v>
       </c>
       <c r="B33" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3892,34 +3876,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464053</v>
+        <v>464483</v>
       </c>
       <c r="R33" t="n">
-        <v>6758144</v>
+        <v>6758032</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3952,6 +3941,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt med ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3978,10 +3972,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131597701</v>
+        <v>131603524</v>
       </c>
       <c r="B34" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3989,34 +3983,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464192</v>
+        <v>464384</v>
       </c>
       <c r="R34" t="n">
-        <v>6758156</v>
+        <v>6758179</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4049,6 +4048,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1 bild, gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4075,48 +4079,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131594493</v>
+        <v>131604756</v>
       </c>
       <c r="B35" t="n">
-        <v>79274</v>
+        <v>57102</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464034</v>
+        <v>464541</v>
       </c>
       <c r="R35" t="n">
-        <v>6758248</v>
+        <v>6758017</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4151,18 +4157,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>2 bilder, bäck</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>131600974</v>
       </c>
       <c r="B36" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>131586494</v>
       </c>
       <c r="B37" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>131586581</v>
       </c>
       <c r="B38" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>131603322</v>
       </c>
       <c r="B39" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>131600594</v>
       </c>
       <c r="B40" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>131599422</v>
       </c>
       <c r="B41" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131600442</v>
+        <v>131603307</v>
       </c>
       <c r="B42" t="n">
-        <v>79864</v>
+        <v>57914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4784,34 +4784,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464251</v>
+        <v>464265</v>
       </c>
       <c r="R42" t="n">
-        <v>6758281</v>
+        <v>6758140</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4844,6 +4849,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4870,10 +4880,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131597848</v>
+        <v>131600442</v>
       </c>
       <c r="B43" t="n">
-        <v>79274</v>
+        <v>79866</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4881,21 +4891,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4905,10 +4915,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464205</v>
+        <v>464251</v>
       </c>
       <c r="R43" t="n">
-        <v>6758160</v>
+        <v>6758281</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4967,10 +4977,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131603971</v>
+        <v>131597848</v>
       </c>
       <c r="B44" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5002,10 +5012,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464384</v>
+        <v>464205</v>
       </c>
       <c r="R44" t="n">
-        <v>6758179</v>
+        <v>6758160</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5038,11 +5048,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5069,10 +5074,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131600551</v>
+        <v>131603971</v>
       </c>
       <c r="B45" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5080,39 +5085,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464263</v>
+        <v>464384</v>
       </c>
       <c r="R45" t="n">
-        <v>6758298</v>
+        <v>6758179</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5145,6 +5145,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,10 +5176,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131603307</v>
+        <v>131600551</v>
       </c>
       <c r="B46" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5211,10 +5216,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464265</v>
+        <v>464263</v>
       </c>
       <c r="R46" t="n">
-        <v>6758140</v>
+        <v>6758298</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5247,11 +5252,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2 bilder, på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5281,7 +5281,7 @@
         <v>131599244</v>
       </c>
       <c r="B47" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>131594252</v>
       </c>
       <c r="B48" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>131586790</v>
       </c>
       <c r="B49" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131586702</v>
+        <v>131605450</v>
       </c>
       <c r="B50" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,42 +5598,40 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464051</v>
+        <v>464189</v>
       </c>
       <c r="R50" t="n">
-        <v>6758034</v>
+        <v>6757919</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5665,12 +5663,18 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131605450</v>
+        <v>131586702</v>
       </c>
       <c r="B51" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5700,40 +5704,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464189</v>
+        <v>464051</v>
       </c>
       <c r="R51" t="n">
-        <v>6757919</v>
+        <v>6758034</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5765,18 +5771,12 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5795,10 +5795,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131586572</v>
+        <v>131601417</v>
       </c>
       <c r="B52" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5830,10 +5830,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464052</v>
+        <v>464317</v>
       </c>
       <c r="R52" t="n">
-        <v>6758021</v>
+        <v>6758312</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5892,10 +5892,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131601417</v>
+        <v>131604599</v>
       </c>
       <c r="B53" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5927,13 +5927,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464317</v>
+        <v>464472</v>
       </c>
       <c r="R53" t="n">
-        <v>6758312</v>
+        <v>6758076</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5963,6 +5963,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5989,10 +5994,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131604599</v>
+        <v>131605027</v>
       </c>
       <c r="B54" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6024,10 +6029,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464472</v>
+        <v>464394</v>
       </c>
       <c r="R54" t="n">
-        <v>6758076</v>
+        <v>6758039</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6064,7 +6069,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 bild, garn i gran. Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6091,10 +6096,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131605027</v>
+        <v>131605468</v>
       </c>
       <c r="B55" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6102,34 +6107,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464394</v>
+        <v>464189</v>
       </c>
       <c r="R55" t="n">
-        <v>6758039</v>
+        <v>6757919</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6162,11 +6175,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6193,10 +6201,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131605468</v>
+        <v>131586572</v>
       </c>
       <c r="B56" t="n">
-        <v>57909</v>
+        <v>79276</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6204,45 +6212,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464189</v>
+        <v>464052</v>
       </c>
       <c r="R56" t="n">
-        <v>6757919</v>
+        <v>6758021</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6298,10 +6298,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131601410</v>
+        <v>131596208</v>
       </c>
       <c r="B57" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6309,39 +6309,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464317</v>
+        <v>464135</v>
       </c>
       <c r="R57" t="n">
-        <v>6758312</v>
+        <v>6758234</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6374,11 +6369,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6405,10 +6395,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131604358</v>
+        <v>131595863</v>
       </c>
       <c r="B58" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6416,39 +6406,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464439</v>
+        <v>464112</v>
       </c>
       <c r="R58" t="n">
-        <v>6758140</v>
+        <v>6758222</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6481,11 +6466,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6512,45 +6492,50 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131596208</v>
+        <v>131587027</v>
       </c>
       <c r="B59" t="n">
-        <v>79274</v>
+        <v>57102</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464135</v>
+        <v>464056</v>
       </c>
       <c r="R59" t="n">
-        <v>6758234</v>
+        <v>6758091</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6583,6 +6568,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning under tjädertall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6609,10 +6599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131595863</v>
+        <v>131586922</v>
       </c>
       <c r="B60" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6620,34 +6610,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464112</v>
+        <v>464054</v>
       </c>
       <c r="R60" t="n">
-        <v>6758222</v>
+        <v>6758066</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6706,10 +6701,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131586922</v>
+        <v>131604358</v>
       </c>
       <c r="B61" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6737,7 +6732,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6746,10 +6741,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464054</v>
+        <v>464439</v>
       </c>
       <c r="R61" t="n">
-        <v>6758066</v>
+        <v>6758140</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6782,6 +6777,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>3 bilder, tall, sista som miljöbild högstubbe</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6808,38 +6808,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131587027</v>
+        <v>131601410</v>
       </c>
       <c r="B62" t="n">
-        <v>57100</v>
+        <v>57914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464056</v>
+        <v>464317</v>
       </c>
       <c r="R62" t="n">
-        <v>6758091</v>
+        <v>6758312</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Spillning under tjädertall</t>
+          <t>1 bild, ringhack och garn</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6918,7 +6918,7 @@
         <v>131602531</v>
       </c>
       <c r="B63" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>131603229</v>
       </c>
       <c r="B64" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>131806044</v>
       </c>
       <c r="B65" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>131806025</v>
       </c>
       <c r="B66" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>131806001</v>
       </c>
       <c r="B67" t="n">
-        <v>92514</v>
+        <v>92516</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7448,10 +7448,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131806043</v>
+        <v>131806066</v>
       </c>
       <c r="B68" t="n">
-        <v>79274</v>
+        <v>78942</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7459,21 +7459,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464078</v>
+        <v>464255</v>
       </c>
       <c r="R68" t="n">
-        <v>6758160</v>
+        <v>6758034</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7555,10 +7555,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131806066</v>
+        <v>131806043</v>
       </c>
       <c r="B69" t="n">
-        <v>78940</v>
+        <v>79276</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7566,21 +7566,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7590,10 +7590,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464255</v>
+        <v>464078</v>
       </c>
       <c r="R69" t="n">
-        <v>6758034</v>
+        <v>6758160</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7662,45 +7662,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131805997</v>
+        <v>131806056</v>
       </c>
       <c r="B70" t="n">
-        <v>92306</v>
+        <v>57914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464284</v>
+        <v>464295</v>
       </c>
       <c r="R70" t="n">
-        <v>6758164</v>
+        <v>6757996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7732,7 +7737,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7742,7 +7747,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7769,32 +7774,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131805980</v>
+        <v>131805997</v>
       </c>
       <c r="B71" t="n">
-        <v>91846</v>
+        <v>92308</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7804,10 +7809,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464132</v>
+        <v>464284</v>
       </c>
       <c r="R71" t="n">
-        <v>6757988</v>
+        <v>6758164</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7839,7 +7844,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7849,7 +7854,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7876,50 +7881,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131805986</v>
+        <v>131805980</v>
       </c>
       <c r="B72" t="n">
-        <v>4775</v>
+        <v>91848</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464254</v>
+        <v>464132</v>
       </c>
       <c r="R72" t="n">
-        <v>6758196</v>
+        <v>6757988</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,38 +7988,38 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131806056</v>
+        <v>131805986</v>
       </c>
       <c r="B73" t="n">
-        <v>57912</v>
+        <v>4775</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464295</v>
+        <v>464254</v>
       </c>
       <c r="R73" t="n">
-        <v>6757996</v>
+        <v>6758196</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8100,10 +8100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131806059</v>
+        <v>131806028</v>
       </c>
       <c r="B74" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,39 +8111,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464438</v>
+        <v>464181</v>
       </c>
       <c r="R74" t="n">
-        <v>6758173</v>
+        <v>6757897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8175,7 +8170,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8185,7 +8180,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8212,10 +8207,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131806028</v>
+        <v>131806059</v>
       </c>
       <c r="B75" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8223,34 +8218,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464181</v>
+        <v>464438</v>
       </c>
       <c r="R75" t="n">
-        <v>6757897</v>
+        <v>6758173</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8319,32 +8319,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131806038</v>
+        <v>131805988</v>
       </c>
       <c r="B76" t="n">
-        <v>79274</v>
+        <v>80410</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464420</v>
+        <v>464189</v>
       </c>
       <c r="R76" t="n">
-        <v>6758206</v>
+        <v>6758149</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8410,6 +8410,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8426,45 +8441,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131805988</v>
+        <v>131806068</v>
       </c>
       <c r="B77" t="n">
-        <v>80408</v>
+        <v>57914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464189</v>
+        <v>464196</v>
       </c>
       <c r="R77" t="n">
-        <v>6758149</v>
+        <v>6757964</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8496,7 +8516,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8506,7 +8526,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8517,21 +8537,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8548,10 +8553,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131806068</v>
+        <v>131806038</v>
       </c>
       <c r="B78" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8559,39 +8564,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464196</v>
+        <v>464420</v>
       </c>
       <c r="R78" t="n">
-        <v>6757964</v>
+        <v>6758206</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8660,10 +8660,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131805976</v>
+        <v>131806042</v>
       </c>
       <c r="B79" t="n">
-        <v>91846</v>
+        <v>79276</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8671,21 +8671,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464319</v>
+        <v>464267</v>
       </c>
       <c r="R79" t="n">
-        <v>6757939</v>
+        <v>6758179</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8767,10 +8767,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131806042</v>
+        <v>131806041</v>
       </c>
       <c r="B80" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464267</v>
+        <v>464305</v>
       </c>
       <c r="R80" t="n">
-        <v>6758179</v>
+        <v>6758161</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8877,7 +8877,7 @@
         <v>131806029</v>
       </c>
       <c r="B81" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8981,32 +8981,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131806041</v>
+        <v>131805999</v>
       </c>
       <c r="B82" t="n">
-        <v>79274</v>
+        <v>97919</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464305</v>
+        <v>464140</v>
       </c>
       <c r="R82" t="n">
-        <v>6758161</v>
+        <v>6758185</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,32 +9088,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131805999</v>
+        <v>131805976</v>
       </c>
       <c r="B83" t="n">
-        <v>97917</v>
+        <v>91848</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464140</v>
+        <v>464319</v>
       </c>
       <c r="R83" t="n">
-        <v>6758185</v>
+        <v>6757939</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9198,7 +9198,7 @@
         <v>131805998</v>
       </c>
       <c r="B84" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9302,10 +9302,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131806060</v>
+        <v>131806050</v>
       </c>
       <c r="B85" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9342,10 +9342,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464263</v>
+        <v>464143</v>
       </c>
       <c r="R85" t="n">
-        <v>6758180</v>
+        <v>6757875</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9414,10 +9414,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131806050</v>
+        <v>131806060</v>
       </c>
       <c r="B86" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464143</v>
+        <v>464263</v>
       </c>
       <c r="R86" t="n">
-        <v>6757875</v>
+        <v>6758180</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9529,7 +9529,7 @@
         <v>131806049</v>
       </c>
       <c r="B87" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>131806057</v>
       </c>
       <c r="B88" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>131805982</v>
       </c>
       <c r="B89" t="n">
-        <v>92569</v>
+        <v>92571</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>131806040</v>
       </c>
       <c r="B90" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>131805971</v>
       </c>
       <c r="B91" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10071,10 +10071,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131805977</v>
+        <v>131806051</v>
       </c>
       <c r="B92" t="n">
-        <v>91846</v>
+        <v>57914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10082,34 +10082,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464313</v>
+        <v>464172</v>
       </c>
       <c r="R92" t="n">
-        <v>6757941</v>
+        <v>6757903</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10141,7 +10146,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10151,7 +10156,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10178,10 +10183,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131806051</v>
+        <v>131806048</v>
       </c>
       <c r="B93" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10209,7 +10214,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10218,10 +10223,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464172</v>
+        <v>464290</v>
       </c>
       <c r="R93" t="n">
-        <v>6757903</v>
+        <v>6758088</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10253,7 +10258,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10263,7 +10268,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10290,10 +10295,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131806048</v>
+        <v>131805977</v>
       </c>
       <c r="B94" t="n">
-        <v>57912</v>
+        <v>91848</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10301,39 +10306,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464290</v>
+        <v>464313</v>
       </c>
       <c r="R94" t="n">
-        <v>6758088</v>
+        <v>6757941</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10402,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806052</v>
+        <v>131806032</v>
       </c>
       <c r="B95" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,39 +10413,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464193</v>
+        <v>464341</v>
       </c>
       <c r="R95" t="n">
-        <v>6757936</v>
+        <v>6757956</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10477,7 +10472,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10487,7 +10482,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10514,32 +10509,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806032</v>
+        <v>131805972</v>
       </c>
       <c r="B96" t="n">
-        <v>79274</v>
+        <v>91811</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10549,10 +10544,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464341</v>
+        <v>464074</v>
       </c>
       <c r="R96" t="n">
-        <v>6757956</v>
+        <v>6758064</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10584,7 +10579,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10594,7 +10589,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10621,10 +10616,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806030</v>
+        <v>131806052</v>
       </c>
       <c r="B97" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10632,34 +10627,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464204</v>
+        <v>464193</v>
       </c>
       <c r="R97" t="n">
-        <v>6758031</v>
+        <v>6757936</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10728,32 +10728,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131805972</v>
+        <v>131806030</v>
       </c>
       <c r="B98" t="n">
-        <v>91809</v>
+        <v>79276</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10763,10 +10763,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464074</v>
+        <v>464204</v>
       </c>
       <c r="R98" t="n">
-        <v>6758064</v>
+        <v>6758031</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10835,10 +10835,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131806000</v>
+        <v>131806002</v>
       </c>
       <c r="B99" t="n">
-        <v>57744</v>
+        <v>79300</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10846,39 +10846,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102622</v>
+        <v>6434</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464154</v>
+        <v>464113</v>
       </c>
       <c r="R99" t="n">
-        <v>6758193</v>
+        <v>6757861</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10910,7 +10905,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10920,7 +10915,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10947,10 +10942,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131806002</v>
+        <v>131806000</v>
       </c>
       <c r="B100" t="n">
-        <v>79298</v>
+        <v>57746</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10958,34 +10953,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6434</v>
+        <v>102622</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464113</v>
+        <v>464154</v>
       </c>
       <c r="R100" t="n">
-        <v>6757861</v>
+        <v>6758193</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11057,7 +11057,7 @@
         <v>131806026</v>
       </c>
       <c r="B101" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>131805978</v>
       </c>
       <c r="B102" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11268,32 +11268,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131806003</v>
+        <v>131806036</v>
       </c>
       <c r="B103" t="n">
-        <v>80415</v>
+        <v>79276</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11303,10 +11303,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464137</v>
+        <v>464459</v>
       </c>
       <c r="R103" t="n">
-        <v>6758186</v>
+        <v>6758165</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11359,21 +11359,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11390,32 +11375,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131806036</v>
+        <v>131806003</v>
       </c>
       <c r="B104" t="n">
-        <v>79274</v>
+        <v>80417</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11425,10 +11410,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464459</v>
+        <v>464137</v>
       </c>
       <c r="R104" t="n">
-        <v>6758165</v>
+        <v>6758186</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11460,7 +11445,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11470,7 +11455,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11481,6 +11466,21 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -11497,38 +11497,38 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806067</v>
+        <v>131806058</v>
       </c>
       <c r="B105" t="n">
-        <v>5179</v>
+        <v>57914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464196</v>
+        <v>464435</v>
       </c>
       <c r="R105" t="n">
-        <v>6757964</v>
+        <v>6758156</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11609,38 +11609,38 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806058</v>
+        <v>131806067</v>
       </c>
       <c r="B106" t="n">
-        <v>57912</v>
+        <v>5179</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11649,10 +11649,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464435</v>
+        <v>464196</v>
       </c>
       <c r="R106" t="n">
-        <v>6758156</v>
+        <v>6757964</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11724,7 +11724,7 @@
         <v>131806007</v>
       </c>
       <c r="B107" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>131805989</v>
       </c>
       <c r="B108" t="n">
-        <v>80408</v>
+        <v>80410</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>131806037</v>
       </c>
       <c r="B109" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>131805979</v>
       </c>
       <c r="B110" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>131806034</v>
       </c>
       <c r="B111" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>131806031</v>
       </c>
       <c r="B112" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12387,32 +12387,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131805990</v>
+        <v>131805970</v>
       </c>
       <c r="B113" t="n">
-        <v>91796</v>
+        <v>91811</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464391</v>
+        <v>464109</v>
       </c>
       <c r="R113" t="n">
-        <v>6758144</v>
+        <v>6757856</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131806004</v>
+        <v>131806033</v>
       </c>
       <c r="B114" t="n">
-        <v>81259</v>
+        <v>79276</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12505,21 +12505,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12529,10 +12529,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464261</v>
+        <v>464363</v>
       </c>
       <c r="R114" t="n">
-        <v>6758029</v>
+        <v>6758150</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12601,10 +12601,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131806039</v>
+        <v>131806035</v>
       </c>
       <c r="B115" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12636,10 +12636,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464338</v>
+        <v>464460</v>
       </c>
       <c r="R115" t="n">
-        <v>6758168</v>
+        <v>6758144</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12708,10 +12708,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131806027</v>
+        <v>131805990</v>
       </c>
       <c r="B116" t="n">
-        <v>79274</v>
+        <v>91798</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12719,21 +12719,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464171</v>
+        <v>464391</v>
       </c>
       <c r="R116" t="n">
-        <v>6757887</v>
+        <v>6758144</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12815,32 +12815,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131805970</v>
+        <v>131806004</v>
       </c>
       <c r="B117" t="n">
-        <v>91809</v>
+        <v>81261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464109</v>
+        <v>464261</v>
       </c>
       <c r="R117" t="n">
-        <v>6757856</v>
+        <v>6758029</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12922,32 +12922,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131805987</v>
+        <v>131806039</v>
       </c>
       <c r="B118" t="n">
-        <v>80408</v>
+        <v>79276</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12957,10 +12957,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464138</v>
+        <v>464338</v>
       </c>
       <c r="R118" t="n">
-        <v>6758188</v>
+        <v>6758168</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13013,21 +13013,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13044,10 +13029,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131806033</v>
+        <v>131806027</v>
       </c>
       <c r="B119" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13079,10 +13064,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464363</v>
+        <v>464171</v>
       </c>
       <c r="R119" t="n">
-        <v>6758150</v>
+        <v>6757887</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13114,7 +13099,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13124,7 +13109,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13151,32 +13136,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131806035</v>
+        <v>131805987</v>
       </c>
       <c r="B120" t="n">
-        <v>79274</v>
+        <v>80410</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13186,10 +13171,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464460</v>
+        <v>464138</v>
       </c>
       <c r="R120" t="n">
-        <v>6758144</v>
+        <v>6758188</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13221,7 +13206,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13231,7 +13216,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13242,6 +13227,21 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
@@ -13261,7 +13261,7 @@
         <v>131806061</v>
       </c>
       <c r="B121" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>131806069</v>
       </c>
       <c r="B122" t="n">
-        <v>91799</v>
+        <v>91801</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -7130,7 +7130,7 @@
         <v>131806044</v>
       </c>
       <c r="B65" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>131806025</v>
       </c>
       <c r="B66" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>131806001</v>
       </c>
       <c r="B67" t="n">
-        <v>92557</v>
+        <v>92560</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>131806066</v>
       </c>
       <c r="B68" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>131806043</v>
       </c>
       <c r="B69" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7662,45 +7662,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131805997</v>
+        <v>131805986</v>
       </c>
       <c r="B70" t="n">
-        <v>92349</v>
+        <v>4775</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>100299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464284</v>
+        <v>464254</v>
       </c>
       <c r="R70" t="n">
-        <v>6758164</v>
+        <v>6758196</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7732,7 +7737,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7742,7 +7747,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7769,10 +7774,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131805980</v>
+        <v>131806056</v>
       </c>
       <c r="B71" t="n">
-        <v>91889</v>
+        <v>57948</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7780,34 +7785,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464132</v>
+        <v>464295</v>
       </c>
       <c r="R71" t="n">
-        <v>6757988</v>
+        <v>6757996</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7839,7 +7849,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7849,7 +7859,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7876,50 +7886,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131806056</v>
+        <v>131805997</v>
       </c>
       <c r="B72" t="n">
-        <v>57948</v>
+        <v>92352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464295</v>
+        <v>464284</v>
       </c>
       <c r="R72" t="n">
-        <v>6757996</v>
+        <v>6758164</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7951,7 +7956,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7961,7 +7966,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,50 +7993,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131805986</v>
+        <v>131805980</v>
       </c>
       <c r="B73" t="n">
-        <v>4775</v>
+        <v>91892</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464254</v>
+        <v>464132</v>
       </c>
       <c r="R73" t="n">
-        <v>6758196</v>
+        <v>6757988</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8100,10 +8100,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131806059</v>
+        <v>131806028</v>
       </c>
       <c r="B74" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8111,39 +8111,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464438</v>
+        <v>464181</v>
       </c>
       <c r="R74" t="n">
-        <v>6758173</v>
+        <v>6757897</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8175,7 +8170,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8185,7 +8180,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8212,10 +8207,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131806028</v>
+        <v>131806059</v>
       </c>
       <c r="B75" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8223,34 +8218,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464181</v>
+        <v>464438</v>
       </c>
       <c r="R75" t="n">
-        <v>6757897</v>
+        <v>6758173</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8282,7 +8282,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8322,7 +8322,7 @@
         <v>131806038</v>
       </c>
       <c r="B76" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>131805988</v>
       </c>
       <c r="B77" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8660,10 +8660,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131806041</v>
+        <v>131805976</v>
       </c>
       <c r="B79" t="n">
-        <v>79315</v>
+        <v>91892</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8671,21 +8671,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464305</v>
+        <v>464319</v>
       </c>
       <c r="R79" t="n">
-        <v>6758161</v>
+        <v>6757939</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8767,32 +8767,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131805976</v>
+        <v>131805999</v>
       </c>
       <c r="B80" t="n">
-        <v>91889</v>
+        <v>97963</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464319</v>
+        <v>464140</v>
       </c>
       <c r="R80" t="n">
-        <v>6757939</v>
+        <v>6758185</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8877,7 +8877,7 @@
         <v>131806042</v>
       </c>
       <c r="B81" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>131806029</v>
       </c>
       <c r="B82" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9088,32 +9088,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131805999</v>
+        <v>131806041</v>
       </c>
       <c r="B83" t="n">
-        <v>97960</v>
+        <v>79317</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464140</v>
+        <v>464305</v>
       </c>
       <c r="R83" t="n">
-        <v>6758185</v>
+        <v>6758161</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9198,7 +9198,7 @@
         <v>131805998</v>
       </c>
       <c r="B84" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131806060</v>
+        <v>131806050</v>
       </c>
       <c r="B85" t="n">
         <v>57948</v>
@@ -9342,10 +9342,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464263</v>
+        <v>464143</v>
       </c>
       <c r="R85" t="n">
-        <v>6758180</v>
+        <v>6757875</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9414,7 +9414,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131806050</v>
+        <v>131806060</v>
       </c>
       <c r="B86" t="n">
         <v>57948</v>
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464143</v>
+        <v>464263</v>
       </c>
       <c r="R86" t="n">
-        <v>6757875</v>
+        <v>6758180</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9750,32 +9750,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131806040</v>
+        <v>131805982</v>
       </c>
       <c r="B89" t="n">
-        <v>79315</v>
+        <v>92615</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9785,10 +9785,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464327</v>
+        <v>464275</v>
       </c>
       <c r="R89" t="n">
-        <v>6758158</v>
+        <v>6758081</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9857,10 +9857,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131805982</v>
+        <v>131805971</v>
       </c>
       <c r="B90" t="n">
-        <v>92612</v>
+        <v>91855</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9868,21 +9868,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3298</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464275</v>
+        <v>464201</v>
       </c>
       <c r="R90" t="n">
-        <v>6758081</v>
+        <v>6757851</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9964,32 +9964,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131805971</v>
+        <v>131806040</v>
       </c>
       <c r="B91" t="n">
-        <v>91852</v>
+        <v>79317</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9999,10 +9999,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464201</v>
+        <v>464327</v>
       </c>
       <c r="R91" t="n">
-        <v>6757851</v>
+        <v>6758158</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10074,7 +10074,7 @@
         <v>131805977</v>
       </c>
       <c r="B92" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10402,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806030</v>
+        <v>131806052</v>
       </c>
       <c r="B95" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,34 +10413,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464204</v>
+        <v>464193</v>
       </c>
       <c r="R95" t="n">
-        <v>6758031</v>
+        <v>6757936</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,7 +10477,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10482,7 +10487,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10509,32 +10514,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131805972</v>
+        <v>131806030</v>
       </c>
       <c r="B96" t="n">
-        <v>91852</v>
+        <v>79317</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10544,10 +10549,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464074</v>
+        <v>464204</v>
       </c>
       <c r="R96" t="n">
-        <v>6758064</v>
+        <v>6758031</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10579,7 +10584,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10589,7 +10594,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10616,32 +10621,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806032</v>
+        <v>131805972</v>
       </c>
       <c r="B97" t="n">
-        <v>79315</v>
+        <v>91855</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10651,10 +10656,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464341</v>
+        <v>464074</v>
       </c>
       <c r="R97" t="n">
-        <v>6757956</v>
+        <v>6758064</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10686,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10696,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10723,10 +10728,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131806052</v>
+        <v>131806032</v>
       </c>
       <c r="B98" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10734,39 +10739,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464193</v>
+        <v>464341</v>
       </c>
       <c r="R98" t="n">
-        <v>6757936</v>
+        <v>6757956</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10838,7 +10838,7 @@
         <v>131806002</v>
       </c>
       <c r="B99" t="n">
-        <v>79339</v>
+        <v>79341</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>131806026</v>
       </c>
       <c r="B101" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11161,45 +11161,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131805978</v>
+        <v>131806067</v>
       </c>
       <c r="B102" t="n">
-        <v>91889</v>
+        <v>5179</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464275</v>
+        <v>464196</v>
       </c>
       <c r="R102" t="n">
-        <v>6758069</v>
+        <v>6757964</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11231,7 +11236,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11241,7 +11246,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11380,50 +11385,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131806067</v>
+        <v>131805978</v>
       </c>
       <c r="B104" t="n">
-        <v>5179</v>
+        <v>91892</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464196</v>
+        <v>464275</v>
       </c>
       <c r="R104" t="n">
-        <v>6757964</v>
+        <v>6758069</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11495,7 +11495,7 @@
         <v>131806036</v>
       </c>
       <c r="B105" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>131806003</v>
       </c>
       <c r="B106" t="n">
-        <v>80456</v>
+        <v>80458</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>131805989</v>
       </c>
       <c r="B107" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>131806007</v>
       </c>
       <c r="B108" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>131806037</v>
       </c>
       <c r="B109" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>131805979</v>
       </c>
       <c r="B110" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>131806034</v>
       </c>
       <c r="B111" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>131806031</v>
       </c>
       <c r="B112" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>131805990</v>
       </c>
       <c r="B113" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>131806004</v>
       </c>
       <c r="B114" t="n">
-        <v>81300</v>
+        <v>81302</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>131806039</v>
       </c>
       <c r="B115" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12708,32 +12708,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131806027</v>
+        <v>131805970</v>
       </c>
       <c r="B116" t="n">
-        <v>79315</v>
+        <v>91855</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12743,10 +12743,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464171</v>
+        <v>464109</v>
       </c>
       <c r="R116" t="n">
-        <v>6757887</v>
+        <v>6757856</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12778,7 +12778,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12815,32 +12815,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131805987</v>
+        <v>131806027</v>
       </c>
       <c r="B117" t="n">
-        <v>80449</v>
+        <v>79317</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12850,10 +12850,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464138</v>
+        <v>464171</v>
       </c>
       <c r="R117" t="n">
-        <v>6758188</v>
+        <v>6757887</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12906,21 +12906,6 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -12937,32 +12922,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131806033</v>
+        <v>131805987</v>
       </c>
       <c r="B118" t="n">
-        <v>79315</v>
+        <v>80451</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12972,10 +12957,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464363</v>
+        <v>464138</v>
       </c>
       <c r="R118" t="n">
-        <v>6758150</v>
+        <v>6758188</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13007,7 +12992,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13017,7 +13002,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13028,6 +13013,21 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13044,10 +13044,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131806035</v>
+        <v>131806033</v>
       </c>
       <c r="B119" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13079,10 +13079,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464460</v>
+        <v>464363</v>
       </c>
       <c r="R119" t="n">
-        <v>6758144</v>
+        <v>6758150</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13151,32 +13151,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131805970</v>
+        <v>131806035</v>
       </c>
       <c r="B120" t="n">
-        <v>91852</v>
+        <v>79317</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13186,10 +13186,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464109</v>
+        <v>464460</v>
       </c>
       <c r="R120" t="n">
-        <v>6757856</v>
+        <v>6758144</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13221,7 +13221,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13373,7 +13373,7 @@
         <v>131806069</v>
       </c>
       <c r="B122" t="n">
-        <v>91842</v>
+        <v>91845</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -7662,50 +7662,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131805986</v>
+        <v>131805997</v>
       </c>
       <c r="B70" t="n">
-        <v>4775</v>
+        <v>92352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100299</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464254</v>
+        <v>464284</v>
       </c>
       <c r="R70" t="n">
-        <v>6758196</v>
+        <v>6758164</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7737,7 +7732,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7747,7 +7742,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7774,10 +7769,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131806056</v>
+        <v>131805980</v>
       </c>
       <c r="B71" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7785,39 +7780,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464295</v>
+        <v>464132</v>
       </c>
       <c r="R71" t="n">
-        <v>6757996</v>
+        <v>6757988</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7849,7 +7839,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7859,7 +7849,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7886,45 +7876,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131805997</v>
+        <v>131805986</v>
       </c>
       <c r="B72" t="n">
-        <v>92352</v>
+        <v>4775</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1209</v>
+        <v>100299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464284</v>
+        <v>464254</v>
       </c>
       <c r="R72" t="n">
-        <v>6758164</v>
+        <v>6758196</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7956,7 +7951,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7966,7 +7961,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7993,10 +7988,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131805980</v>
+        <v>131806056</v>
       </c>
       <c r="B73" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8004,34 +7999,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464132</v>
+        <v>464295</v>
       </c>
       <c r="R73" t="n">
-        <v>6757988</v>
+        <v>6757996</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8319,32 +8319,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131806038</v>
+        <v>131805988</v>
       </c>
       <c r="B76" t="n">
-        <v>79317</v>
+        <v>80451</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464420</v>
+        <v>464189</v>
       </c>
       <c r="R76" t="n">
-        <v>6758206</v>
+        <v>6758149</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8410,6 +8410,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8426,45 +8441,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131805988</v>
+        <v>131806068</v>
       </c>
       <c r="B77" t="n">
-        <v>80451</v>
+        <v>57948</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464189</v>
+        <v>464196</v>
       </c>
       <c r="R77" t="n">
-        <v>6758149</v>
+        <v>6757964</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8496,7 +8516,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8506,7 +8526,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8517,21 +8537,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8548,10 +8553,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131806068</v>
+        <v>131806038</v>
       </c>
       <c r="B78" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8559,39 +8564,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464196</v>
+        <v>464420</v>
       </c>
       <c r="R78" t="n">
-        <v>6757964</v>
+        <v>6758206</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9195,10 +9195,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131805998</v>
+        <v>131806050</v>
       </c>
       <c r="B84" t="n">
-        <v>92191</v>
+        <v>57948</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9206,34 +9206,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464399</v>
+        <v>464143</v>
       </c>
       <c r="R84" t="n">
-        <v>6758179</v>
+        <v>6757875</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9265,7 +9270,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9275,7 +9280,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9302,7 +9307,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131806050</v>
+        <v>131806060</v>
       </c>
       <c r="B85" t="n">
         <v>57948</v>
@@ -9342,10 +9347,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464143</v>
+        <v>464263</v>
       </c>
       <c r="R85" t="n">
-        <v>6757875</v>
+        <v>6758180</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9377,7 +9382,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9387,7 +9392,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9414,7 +9419,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131806060</v>
+        <v>131806049</v>
       </c>
       <c r="B86" t="n">
         <v>57948</v>
@@ -9445,7 +9450,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9454,10 +9459,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464263</v>
+        <v>464099</v>
       </c>
       <c r="R86" t="n">
-        <v>6758180</v>
+        <v>6757847</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9489,7 +9494,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9499,7 +9504,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9526,10 +9531,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131806049</v>
+        <v>131805998</v>
       </c>
       <c r="B87" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9537,39 +9542,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464099</v>
+        <v>464399</v>
       </c>
       <c r="R87" t="n">
-        <v>6757847</v>
+        <v>6758179</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10071,10 +10071,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131805977</v>
+        <v>131806051</v>
       </c>
       <c r="B92" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10082,34 +10082,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464313</v>
+        <v>464172</v>
       </c>
       <c r="R92" t="n">
-        <v>6757941</v>
+        <v>6757903</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10141,7 +10146,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10151,7 +10156,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10178,7 +10183,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131806051</v>
+        <v>131806048</v>
       </c>
       <c r="B93" t="n">
         <v>57948</v>
@@ -10209,7 +10214,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10218,10 +10223,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464172</v>
+        <v>464290</v>
       </c>
       <c r="R93" t="n">
-        <v>6757903</v>
+        <v>6758088</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10253,7 +10258,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10263,7 +10268,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10290,10 +10295,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131806048</v>
+        <v>131805977</v>
       </c>
       <c r="B94" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10301,39 +10306,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464290</v>
+        <v>464313</v>
       </c>
       <c r="R94" t="n">
-        <v>6758088</v>
+        <v>6757941</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10402,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806052</v>
+        <v>131806030</v>
       </c>
       <c r="B95" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,39 +10413,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464193</v>
+        <v>464204</v>
       </c>
       <c r="R95" t="n">
-        <v>6757936</v>
+        <v>6758031</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10477,7 +10472,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10487,7 +10482,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10514,32 +10509,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806030</v>
+        <v>131805972</v>
       </c>
       <c r="B96" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10549,10 +10544,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464204</v>
+        <v>464074</v>
       </c>
       <c r="R96" t="n">
-        <v>6758031</v>
+        <v>6758064</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10584,7 +10579,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10594,7 +10589,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10621,32 +10616,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131805972</v>
+        <v>131806032</v>
       </c>
       <c r="B97" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10656,10 +10651,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464074</v>
+        <v>464341</v>
       </c>
       <c r="R97" t="n">
-        <v>6758064</v>
+        <v>6757956</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10691,7 +10686,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10701,7 +10696,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10728,10 +10723,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131806032</v>
+        <v>131806052</v>
       </c>
       <c r="B98" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10739,34 +10734,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464341</v>
+        <v>464193</v>
       </c>
       <c r="R98" t="n">
-        <v>6757956</v>
+        <v>6757936</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11721,45 +11721,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131805989</v>
+        <v>131806007</v>
       </c>
       <c r="B107" t="n">
-        <v>80451</v>
+        <v>99098</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464196</v>
+        <v>464255</v>
       </c>
       <c r="R107" t="n">
-        <v>6758006</v>
+        <v>6758034</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11791,7 +11800,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11801,7 +11810,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11812,21 +11821,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11843,54 +11837,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131806007</v>
+        <v>131805989</v>
       </c>
       <c r="B108" t="n">
-        <v>99098</v>
+        <v>80451</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464255</v>
+        <v>464196</v>
       </c>
       <c r="R108" t="n">
-        <v>6758034</v>
+        <v>6758006</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11922,7 +11907,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11932,7 +11917,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11943,6 +11928,21 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AY163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8767,32 +8767,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131805999</v>
+        <v>131806042</v>
       </c>
       <c r="B80" t="n">
-        <v>97963</v>
+        <v>79317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464140</v>
+        <v>464267</v>
       </c>
       <c r="R80" t="n">
-        <v>6758185</v>
+        <v>6758179</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8874,7 +8874,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131806042</v>
+        <v>131806029</v>
       </c>
       <c r="B81" t="n">
         <v>79317</v>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464267</v>
+        <v>464204</v>
       </c>
       <c r="R81" t="n">
-        <v>6758179</v>
+        <v>6757960</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8981,7 +8981,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131806029</v>
+        <v>131806041</v>
       </c>
       <c r="B82" t="n">
         <v>79317</v>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464204</v>
+        <v>464305</v>
       </c>
       <c r="R82" t="n">
-        <v>6757960</v>
+        <v>6758161</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,32 +9088,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131806041</v>
+        <v>131805999</v>
       </c>
       <c r="B83" t="n">
-        <v>79317</v>
+        <v>97963</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464305</v>
+        <v>464140</v>
       </c>
       <c r="R83" t="n">
-        <v>6758161</v>
+        <v>6758185</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10071,10 +10071,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131806051</v>
+        <v>131805977</v>
       </c>
       <c r="B92" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10082,39 +10082,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464172</v>
+        <v>464313</v>
       </c>
       <c r="R92" t="n">
-        <v>6757903</v>
+        <v>6757941</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10146,7 +10141,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10156,7 +10151,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10183,7 +10178,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131806048</v>
+        <v>131806051</v>
       </c>
       <c r="B93" t="n">
         <v>57948</v>
@@ -10214,7 +10209,7 @@
       <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10223,10 +10218,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464290</v>
+        <v>464172</v>
       </c>
       <c r="R93" t="n">
-        <v>6758088</v>
+        <v>6757903</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10258,7 +10253,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10268,7 +10263,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10295,10 +10290,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131805977</v>
+        <v>131806048</v>
       </c>
       <c r="B94" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10306,34 +10301,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464313</v>
+        <v>464290</v>
       </c>
       <c r="R94" t="n">
-        <v>6757941</v>
+        <v>6758088</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10402,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806030</v>
+        <v>131806052</v>
       </c>
       <c r="B95" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,34 +10413,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464204</v>
+        <v>464193</v>
       </c>
       <c r="R95" t="n">
-        <v>6758031</v>
+        <v>6757936</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,7 +10477,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10482,7 +10487,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10509,32 +10514,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131805972</v>
+        <v>131806030</v>
       </c>
       <c r="B96" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10544,10 +10549,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464074</v>
+        <v>464204</v>
       </c>
       <c r="R96" t="n">
-        <v>6758064</v>
+        <v>6758031</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10579,7 +10584,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10589,7 +10594,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10616,32 +10621,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131806032</v>
+        <v>131805972</v>
       </c>
       <c r="B97" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10651,10 +10656,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464341</v>
+        <v>464074</v>
       </c>
       <c r="R97" t="n">
-        <v>6757956</v>
+        <v>6758064</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10686,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10696,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10723,10 +10728,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131806052</v>
+        <v>131806032</v>
       </c>
       <c r="B98" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10734,39 +10739,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464193</v>
+        <v>464341</v>
       </c>
       <c r="R98" t="n">
-        <v>6757936</v>
+        <v>6757956</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11161,50 +11161,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131806067</v>
+        <v>131806036</v>
       </c>
       <c r="B102" t="n">
-        <v>5179</v>
+        <v>79317</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464196</v>
+        <v>464459</v>
       </c>
       <c r="R102" t="n">
-        <v>6757964</v>
+        <v>6758165</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11236,7 +11231,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11246,7 +11241,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11273,50 +11268,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131806058</v>
+        <v>131806003</v>
       </c>
       <c r="B103" t="n">
-        <v>57948</v>
+        <v>80458</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464435</v>
+        <v>464137</v>
       </c>
       <c r="R103" t="n">
-        <v>6758156</v>
+        <v>6758186</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11348,7 +11338,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11358,7 +11348,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11369,6 +11359,21 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11492,45 +11497,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806036</v>
+        <v>131806067</v>
       </c>
       <c r="B105" t="n">
-        <v>79317</v>
+        <v>5179</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464459</v>
+        <v>464196</v>
       </c>
       <c r="R105" t="n">
-        <v>6758165</v>
+        <v>6757964</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11562,7 +11572,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11572,7 +11582,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11599,45 +11609,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806003</v>
+        <v>131806058</v>
       </c>
       <c r="B106" t="n">
-        <v>80458</v>
+        <v>57948</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464137</v>
+        <v>464435</v>
       </c>
       <c r="R106" t="n">
-        <v>6758186</v>
+        <v>6758156</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11669,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11679,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11690,21 +11705,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -13488,6 +13488,4096 @@
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>132491919</v>
+      </c>
+      <c r="B123" t="n">
+        <v>91842</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>112</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>464197</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6757865</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>132496183</v>
+      </c>
+      <c r="B124" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>464441</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6758052</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>132497836</v>
+      </c>
+      <c r="B125" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>464333</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6758118</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>132496342</v>
+      </c>
+      <c r="B126" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>464442</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6758015</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>132494581</v>
+      </c>
+      <c r="B127" t="n">
+        <v>58322</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>464499</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6758024</v>
+      </c>
+      <c r="S127" t="n">
+        <v>50</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>132492205</v>
+      </c>
+      <c r="B128" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>464198</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6757941</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>132495215</v>
+      </c>
+      <c r="B129" t="n">
+        <v>83297</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>464514</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6758053</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>132492920</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>464335</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6757949</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>132494714</v>
+      </c>
+      <c r="B131" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>464483</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6758032</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>132492755</v>
+      </c>
+      <c r="B132" t="n">
+        <v>58322</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>464301</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6757948</v>
+      </c>
+      <c r="S132" t="n">
+        <v>50</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132499966</v>
+      </c>
+      <c r="B133" t="n">
+        <v>80451</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>464137</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6758183</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>132499020</v>
+      </c>
+      <c r="B134" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>464187</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6758040</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>132499761</v>
+      </c>
+      <c r="B135" t="n">
+        <v>92352</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>464170</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6758208</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>132492041</v>
+      </c>
+      <c r="B136" t="n">
+        <v>81302</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>464220</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6757896</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>132492033</v>
+      </c>
+      <c r="B137" t="n">
+        <v>78983</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>353</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>464220</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6757896</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>132498299</v>
+      </c>
+      <c r="B138" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>464310</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6758158</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>132498371</v>
+      </c>
+      <c r="B139" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>464292</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6758119</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>132499976</v>
+      </c>
+      <c r="B140" t="n">
+        <v>80382</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>464137</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6758183</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>132495276</v>
+      </c>
+      <c r="B141" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>464505</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6758076</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>132495919</v>
+      </c>
+      <c r="B142" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>464458</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6758060</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>132498302</v>
+      </c>
+      <c r="B143" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>464310</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6758158</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>132494801</v>
+      </c>
+      <c r="B144" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>464477</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6758041</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>132495930</v>
+      </c>
+      <c r="B145" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>464458</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6758060</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>132497843</v>
+      </c>
+      <c r="B146" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>464333</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6758118</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>132493028</v>
+      </c>
+      <c r="B147" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>464364</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6757928</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>132492565</v>
+      </c>
+      <c r="B148" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>464278</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6757899</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>132493206</v>
+      </c>
+      <c r="B149" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>464376</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6757951</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>132499106</v>
+      </c>
+      <c r="B150" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>464208</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6758043</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>132495072</v>
+      </c>
+      <c r="B151" t="n">
+        <v>91912</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>464503</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6758035</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>132491882</v>
+      </c>
+      <c r="B152" t="n">
+        <v>58322</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>464198</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6757876</v>
+      </c>
+      <c r="S152" t="n">
+        <v>50</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>132494061</v>
+      </c>
+      <c r="B153" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>464479</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6758007</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>132495068</v>
+      </c>
+      <c r="B154" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>464503</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6758035</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Flera bilder 3 till 4 meter upp,  ca 4 cm i diameter, 4 hål</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>132493696</v>
+      </c>
+      <c r="B155" t="n">
+        <v>99098</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>464446</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6757982</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>132492528</v>
+      </c>
+      <c r="B156" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>464273</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6757909</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>132499772</v>
+      </c>
+      <c r="B157" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>464170</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6758208</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>132496448</v>
+      </c>
+      <c r="B158" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>464446</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6757993</v>
+      </c>
+      <c r="S158" t="n">
+        <v>10</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Garn vid kolarkoja samt kolbotten</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>132493334</v>
+      </c>
+      <c r="B159" t="n">
+        <v>92191</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>658</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>464393</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6757956</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>132495224</v>
+      </c>
+      <c r="B160" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>464514</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6758053</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>132492586</v>
+      </c>
+      <c r="B161" t="n">
+        <v>78983</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>353</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>464278</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6757899</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>132492923</v>
+      </c>
+      <c r="B162" t="n">
+        <v>78983</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>353</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>464335</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6757949</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>132494856</v>
+      </c>
+      <c r="B163" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>464490</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6758002</v>
+      </c>
+      <c r="S163" t="n">
+        <v>10</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY163"/>
+  <dimension ref="A1:AY172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7127,32 +7127,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131806044</v>
+        <v>131806001</v>
       </c>
       <c r="B65" t="n">
-        <v>79317</v>
+        <v>92560</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106596</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464091</v>
+        <v>464428</v>
       </c>
       <c r="R65" t="n">
-        <v>6758171</v>
+        <v>6758134</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7234,7 +7234,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131806025</v>
+        <v>131806044</v>
       </c>
       <c r="B66" t="n">
         <v>79317</v>
@@ -7269,10 +7269,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464116</v>
+        <v>464091</v>
       </c>
       <c r="R66" t="n">
-        <v>6757815</v>
+        <v>6758171</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7341,32 +7341,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131806001</v>
+        <v>131806025</v>
       </c>
       <c r="B67" t="n">
-        <v>92560</v>
+        <v>79317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106596</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordlig parasitporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464428</v>
+        <v>464116</v>
       </c>
       <c r="R67" t="n">
-        <v>6758134</v>
+        <v>6757815</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7662,45 +7662,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131805997</v>
+        <v>131806056</v>
       </c>
       <c r="B70" t="n">
-        <v>92352</v>
+        <v>57948</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464284</v>
+        <v>464295</v>
       </c>
       <c r="R70" t="n">
-        <v>6758164</v>
+        <v>6757996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7732,7 +7737,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7742,7 +7747,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7769,32 +7774,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131805980</v>
+        <v>131805997</v>
       </c>
       <c r="B71" t="n">
-        <v>91892</v>
+        <v>92352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7804,10 +7809,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464132</v>
+        <v>464284</v>
       </c>
       <c r="R71" t="n">
-        <v>6757988</v>
+        <v>6758164</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7839,7 +7844,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7849,7 +7854,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7876,50 +7881,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131805986</v>
+        <v>131805980</v>
       </c>
       <c r="B72" t="n">
-        <v>4775</v>
+        <v>91892</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464254</v>
+        <v>464132</v>
       </c>
       <c r="R72" t="n">
-        <v>6758196</v>
+        <v>6757988</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7988,38 +7988,38 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131806056</v>
+        <v>131805986</v>
       </c>
       <c r="B73" t="n">
-        <v>57948</v>
+        <v>4775</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464295</v>
+        <v>464254</v>
       </c>
       <c r="R73" t="n">
-        <v>6757996</v>
+        <v>6758196</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8319,45 +8319,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131805988</v>
+        <v>131806068</v>
       </c>
       <c r="B76" t="n">
-        <v>80451</v>
+        <v>57948</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464189</v>
+        <v>464196</v>
       </c>
       <c r="R76" t="n">
-        <v>6758149</v>
+        <v>6757964</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8389,7 +8394,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8399,7 +8404,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8410,21 +8415,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8441,10 +8431,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131806068</v>
+        <v>131806038</v>
       </c>
       <c r="B77" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8452,39 +8442,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464196</v>
+        <v>464420</v>
       </c>
       <c r="R77" t="n">
-        <v>6757964</v>
+        <v>6758206</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8516,7 +8501,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8526,7 +8511,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8553,32 +8538,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131806038</v>
+        <v>131805988</v>
       </c>
       <c r="B78" t="n">
-        <v>79317</v>
+        <v>80451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8588,10 +8573,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464420</v>
+        <v>464189</v>
       </c>
       <c r="R78" t="n">
-        <v>6758206</v>
+        <v>6758149</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8623,7 +8608,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8633,7 +8618,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8644,6 +8629,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -8660,32 +8660,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131805976</v>
+        <v>131805999</v>
       </c>
       <c r="B79" t="n">
-        <v>91892</v>
+        <v>97963</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464319</v>
+        <v>464140</v>
       </c>
       <c r="R79" t="n">
-        <v>6757939</v>
+        <v>6758185</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8767,10 +8767,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131806042</v>
+        <v>131805976</v>
       </c>
       <c r="B80" t="n">
-        <v>79317</v>
+        <v>91892</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8778,21 +8778,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464267</v>
+        <v>464319</v>
       </c>
       <c r="R80" t="n">
-        <v>6758179</v>
+        <v>6757939</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8874,7 +8874,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131806029</v>
+        <v>131806042</v>
       </c>
       <c r="B81" t="n">
         <v>79317</v>
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464204</v>
+        <v>464267</v>
       </c>
       <c r="R81" t="n">
-        <v>6757960</v>
+        <v>6758179</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8954,7 +8954,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8981,7 +8981,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131806041</v>
+        <v>131806029</v>
       </c>
       <c r="B82" t="n">
         <v>79317</v>
@@ -9016,10 +9016,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464305</v>
+        <v>464204</v>
       </c>
       <c r="R82" t="n">
-        <v>6758161</v>
+        <v>6757960</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9088,32 +9088,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131805999</v>
+        <v>131806041</v>
       </c>
       <c r="B83" t="n">
-        <v>97963</v>
+        <v>79317</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9123,10 +9123,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464140</v>
+        <v>464305</v>
       </c>
       <c r="R83" t="n">
-        <v>6758185</v>
+        <v>6758161</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9195,7 +9195,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131806050</v>
+        <v>131806060</v>
       </c>
       <c r="B84" t="n">
         <v>57948</v>
@@ -9235,10 +9235,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464143</v>
+        <v>464263</v>
       </c>
       <c r="R84" t="n">
-        <v>6757875</v>
+        <v>6758180</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9307,7 +9307,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131806060</v>
+        <v>131806050</v>
       </c>
       <c r="B85" t="n">
         <v>57948</v>
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464263</v>
+        <v>464143</v>
       </c>
       <c r="R85" t="n">
-        <v>6758180</v>
+        <v>6757875</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9857,32 +9857,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131805971</v>
+        <v>131806040</v>
       </c>
       <c r="B90" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464201</v>
+        <v>464327</v>
       </c>
       <c r="R90" t="n">
-        <v>6757851</v>
+        <v>6758158</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9964,32 +9964,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131806040</v>
+        <v>131805971</v>
       </c>
       <c r="B91" t="n">
-        <v>79317</v>
+        <v>91855</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9999,10 +9999,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464327</v>
+        <v>464201</v>
       </c>
       <c r="R91" t="n">
-        <v>6758158</v>
+        <v>6757851</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10402,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806052</v>
+        <v>131806032</v>
       </c>
       <c r="B95" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,39 +10413,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464193</v>
+        <v>464341</v>
       </c>
       <c r="R95" t="n">
-        <v>6757936</v>
+        <v>6757956</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10477,7 +10472,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10487,7 +10482,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10728,10 +10723,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131806032</v>
+        <v>131806052</v>
       </c>
       <c r="B98" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10739,34 +10734,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464341</v>
+        <v>464193</v>
       </c>
       <c r="R98" t="n">
-        <v>6757956</v>
+        <v>6757936</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10835,10 +10835,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131806002</v>
+        <v>131806000</v>
       </c>
       <c r="B99" t="n">
-        <v>79341</v>
+        <v>57780</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10846,34 +10846,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6434</v>
+        <v>102622</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464113</v>
+        <v>464154</v>
       </c>
       <c r="R99" t="n">
-        <v>6757861</v>
+        <v>6758193</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10905,7 +10910,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10915,7 +10920,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10942,10 +10947,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131806000</v>
+        <v>131806002</v>
       </c>
       <c r="B100" t="n">
-        <v>57780</v>
+        <v>79341</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10953,39 +10958,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102622</v>
+        <v>6434</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464154</v>
+        <v>464113</v>
       </c>
       <c r="R100" t="n">
-        <v>6758193</v>
+        <v>6757861</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11161,10 +11161,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131806036</v>
+        <v>131805978</v>
       </c>
       <c r="B102" t="n">
-        <v>79317</v>
+        <v>91892</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11172,21 +11172,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11196,10 +11196,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464459</v>
+        <v>464275</v>
       </c>
       <c r="R102" t="n">
-        <v>6758165</v>
+        <v>6758069</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11268,32 +11268,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131806003</v>
+        <v>131806036</v>
       </c>
       <c r="B103" t="n">
-        <v>80458</v>
+        <v>79317</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11303,10 +11303,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464137</v>
+        <v>464459</v>
       </c>
       <c r="R103" t="n">
-        <v>6758186</v>
+        <v>6758165</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11359,21 +11359,6 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11390,32 +11375,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131805978</v>
+        <v>131806003</v>
       </c>
       <c r="B104" t="n">
-        <v>91892</v>
+        <v>80458</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11425,10 +11410,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464275</v>
+        <v>464137</v>
       </c>
       <c r="R104" t="n">
-        <v>6758069</v>
+        <v>6758186</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11460,7 +11445,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11470,7 +11455,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11481,6 +11466,21 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -11497,38 +11497,38 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806067</v>
+        <v>131806058</v>
       </c>
       <c r="B105" t="n">
-        <v>5179</v>
+        <v>57948</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464196</v>
+        <v>464435</v>
       </c>
       <c r="R105" t="n">
-        <v>6757964</v>
+        <v>6758156</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11609,38 +11609,38 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806058</v>
+        <v>131806067</v>
       </c>
       <c r="B106" t="n">
-        <v>57948</v>
+        <v>5179</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11649,10 +11649,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464435</v>
+        <v>464196</v>
       </c>
       <c r="R106" t="n">
-        <v>6758156</v>
+        <v>6757964</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11684,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11721,54 +11721,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131806007</v>
+        <v>131805989</v>
       </c>
       <c r="B107" t="n">
-        <v>99098</v>
+        <v>80451</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>464255</v>
+        <v>464196</v>
       </c>
       <c r="R107" t="n">
-        <v>6758034</v>
+        <v>6758006</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11800,7 +11791,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11810,7 +11801,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11821,6 +11812,21 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -11837,45 +11843,54 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131805989</v>
+        <v>131806007</v>
       </c>
       <c r="B108" t="n">
-        <v>80451</v>
+        <v>99098</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>464196</v>
+        <v>464255</v>
       </c>
       <c r="R108" t="n">
-        <v>6758006</v>
+        <v>6758034</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11907,7 +11922,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11917,7 +11932,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11928,21 +11943,6 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12387,10 +12387,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>131805990</v>
+        <v>131806004</v>
       </c>
       <c r="B113" t="n">
-        <v>91842</v>
+        <v>81302</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12398,21 +12398,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>112</v>
+        <v>1049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12422,10 +12422,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>464391</v>
+        <v>464261</v>
       </c>
       <c r="R113" t="n">
-        <v>6758144</v>
+        <v>6758029</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12494,10 +12494,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>131806004</v>
+        <v>131806061</v>
       </c>
       <c r="B114" t="n">
-        <v>81302</v>
+        <v>57948</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12505,34 +12505,39 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>464261</v>
+        <v>464225</v>
       </c>
       <c r="R114" t="n">
-        <v>6758029</v>
+        <v>6758200</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12564,7 +12569,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12574,7 +12579,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12601,10 +12606,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>131806039</v>
+        <v>131805990</v>
       </c>
       <c r="B115" t="n">
-        <v>79317</v>
+        <v>91842</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12612,21 +12617,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12636,10 +12641,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>464338</v>
+        <v>464391</v>
       </c>
       <c r="R115" t="n">
-        <v>6758168</v>
+        <v>6758144</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12671,7 +12676,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12681,7 +12686,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12708,32 +12713,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>131805970</v>
+        <v>131806027</v>
       </c>
       <c r="B116" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12743,10 +12748,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>464109</v>
+        <v>464171</v>
       </c>
       <c r="R116" t="n">
-        <v>6757856</v>
+        <v>6757887</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12778,7 +12783,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12788,7 +12793,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12815,32 +12820,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>131806027</v>
+        <v>131805987</v>
       </c>
       <c r="B117" t="n">
-        <v>79317</v>
+        <v>80451</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12850,10 +12855,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>464171</v>
+        <v>464138</v>
       </c>
       <c r="R117" t="n">
-        <v>6757887</v>
+        <v>6758188</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12885,7 +12890,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12895,7 +12900,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12906,6 +12911,21 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -12922,32 +12942,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>131805987</v>
+        <v>131806033</v>
       </c>
       <c r="B118" t="n">
-        <v>80451</v>
+        <v>79317</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12957,10 +12977,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>464138</v>
+        <v>464363</v>
       </c>
       <c r="R118" t="n">
-        <v>6758188</v>
+        <v>6758150</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12992,7 +13012,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13002,7 +13022,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13013,21 +13033,6 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
@@ -13044,7 +13049,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>131806033</v>
+        <v>131806035</v>
       </c>
       <c r="B119" t="n">
         <v>79317</v>
@@ -13079,10 +13084,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>464363</v>
+        <v>464460</v>
       </c>
       <c r="R119" t="n">
-        <v>6758150</v>
+        <v>6758144</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13114,7 +13119,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13124,7 +13129,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13151,7 +13156,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>131806035</v>
+        <v>131806039</v>
       </c>
       <c r="B120" t="n">
         <v>79317</v>
@@ -13186,10 +13191,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>464460</v>
+        <v>464338</v>
       </c>
       <c r="R120" t="n">
-        <v>6758144</v>
+        <v>6758168</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13221,7 +13226,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13231,7 +13236,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13258,50 +13263,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>131806061</v>
+        <v>131805970</v>
       </c>
       <c r="B121" t="n">
-        <v>57948</v>
+        <v>91855</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>464225</v>
+        <v>464109</v>
       </c>
       <c r="R121" t="n">
-        <v>6758200</v>
+        <v>6757856</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13689,38 +13689,42 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>132497836</v>
+        <v>132496342</v>
       </c>
       <c r="B125" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -13729,10 +13733,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>464333</v>
+        <v>464442</v>
       </c>
       <c r="R125" t="n">
-        <v>6758118</v>
+        <v>6758015</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13791,42 +13795,38 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>132496342</v>
+        <v>132497836</v>
       </c>
       <c r="B126" t="n">
-        <v>99098</v>
+        <v>57948</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -13835,10 +13835,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>464442</v>
+        <v>464333</v>
       </c>
       <c r="R126" t="n">
-        <v>6758015</v>
+        <v>6758118</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14101,10 +14101,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>132495215</v>
+        <v>132494714</v>
       </c>
       <c r="B129" t="n">
-        <v>83297</v>
+        <v>79317</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14112,21 +14112,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14136,10 +14136,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>464514</v>
+        <v>464483</v>
       </c>
       <c r="R129" t="n">
-        <v>6758053</v>
+        <v>6758032</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14198,50 +14198,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132492920</v>
+        <v>132499966</v>
       </c>
       <c r="B130" t="n">
-        <v>57945</v>
+        <v>80451</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464335</v>
+        <v>464137</v>
       </c>
       <c r="R130" t="n">
-        <v>6757949</v>
+        <v>6758183</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14300,10 +14295,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132494714</v>
+        <v>132495215</v>
       </c>
       <c r="B131" t="n">
-        <v>79317</v>
+        <v>83297</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14311,21 +14306,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14335,10 +14330,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>464483</v>
+        <v>464514</v>
       </c>
       <c r="R131" t="n">
-        <v>6758032</v>
+        <v>6758053</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14499,45 +14494,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132499966</v>
+        <v>132499020</v>
       </c>
       <c r="B133" t="n">
-        <v>80451</v>
+        <v>99098</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>464137</v>
+        <v>464187</v>
       </c>
       <c r="R133" t="n">
-        <v>6758183</v>
+        <v>6758040</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14596,10 +14600,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>132499020</v>
+        <v>132499761</v>
       </c>
       <c r="B134" t="n">
-        <v>99098</v>
+        <v>92352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14607,43 +14611,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>464187</v>
+        <v>464170</v>
       </c>
       <c r="R134" t="n">
-        <v>6758040</v>
+        <v>6758208</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14702,32 +14697,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>132499761</v>
+        <v>132492041</v>
       </c>
       <c r="B135" t="n">
-        <v>92352</v>
+        <v>81302</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1209</v>
+        <v>1049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14737,10 +14732,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>464170</v>
+        <v>464220</v>
       </c>
       <c r="R135" t="n">
-        <v>6758208</v>
+        <v>6757896</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14799,10 +14794,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>132492041</v>
+        <v>132492033</v>
       </c>
       <c r="B136" t="n">
-        <v>81302</v>
+        <v>78983</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14810,21 +14805,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14896,10 +14891,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132492033</v>
+        <v>132498299</v>
       </c>
       <c r="B137" t="n">
-        <v>78983</v>
+        <v>57948</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14907,34 +14902,39 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>464220</v>
+        <v>464310</v>
       </c>
       <c r="R137" t="n">
-        <v>6757896</v>
+        <v>6758158</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14993,10 +14993,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132498299</v>
+        <v>132498302</v>
       </c>
       <c r="B138" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15004,29 +15004,24 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
@@ -15095,50 +15090,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132498371</v>
+        <v>132499976</v>
       </c>
       <c r="B139" t="n">
-        <v>57948</v>
+        <v>80382</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464292</v>
+        <v>464137</v>
       </c>
       <c r="R139" t="n">
-        <v>6758119</v>
+        <v>6758183</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15197,32 +15187,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132499976</v>
+        <v>132495276</v>
       </c>
       <c r="B140" t="n">
-        <v>80382</v>
+        <v>79317</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15232,10 +15222,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464137</v>
+        <v>464505</v>
       </c>
       <c r="R140" t="n">
-        <v>6758183</v>
+        <v>6758076</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15294,10 +15284,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132495276</v>
+        <v>132495919</v>
       </c>
       <c r="B141" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15305,34 +15295,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464505</v>
+        <v>464458</v>
       </c>
       <c r="R141" t="n">
-        <v>6758076</v>
+        <v>6758060</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15391,7 +15386,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132495919</v>
+        <v>132498371</v>
       </c>
       <c r="B142" t="n">
         <v>57948</v>
@@ -15422,7 +15417,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -15431,10 +15426,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464458</v>
+        <v>464292</v>
       </c>
       <c r="R142" t="n">
-        <v>6758060</v>
+        <v>6758119</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15493,7 +15488,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132498302</v>
+        <v>132497843</v>
       </c>
       <c r="B143" t="n">
         <v>79317</v>
@@ -15528,10 +15523,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>464310</v>
+        <v>464333</v>
       </c>
       <c r="R143" t="n">
-        <v>6758158</v>
+        <v>6758118</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15590,10 +15585,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>132494801</v>
+        <v>132495930</v>
       </c>
       <c r="B144" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15601,39 +15596,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>464477</v>
+        <v>464458</v>
       </c>
       <c r="R144" t="n">
-        <v>6758041</v>
+        <v>6758060</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15692,10 +15682,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>132495930</v>
+        <v>132494801</v>
       </c>
       <c r="B145" t="n">
-        <v>79317</v>
+        <v>57945</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15703,34 +15693,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>464458</v>
+        <v>464477</v>
       </c>
       <c r="R145" t="n">
-        <v>6758060</v>
+        <v>6758041</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15789,10 +15784,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132497843</v>
+        <v>132492565</v>
       </c>
       <c r="B146" t="n">
-        <v>79317</v>
+        <v>91892</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15800,21 +15795,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15824,10 +15819,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>464333</v>
+        <v>464278</v>
       </c>
       <c r="R146" t="n">
-        <v>6758118</v>
+        <v>6757899</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15983,10 +15978,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>132492565</v>
+        <v>132493206</v>
       </c>
       <c r="B148" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15994,34 +15989,39 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>464278</v>
+        <v>464376</v>
       </c>
       <c r="R148" t="n">
-        <v>6757899</v>
+        <v>6757951</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16080,7 +16080,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132493206</v>
+        <v>132499106</v>
       </c>
       <c r="B149" t="n">
         <v>57948</v>
@@ -16120,10 +16120,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464376</v>
+        <v>464208</v>
       </c>
       <c r="R149" t="n">
-        <v>6757951</v>
+        <v>6758043</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16182,27 +16182,27 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132499106</v>
+        <v>132491882</v>
       </c>
       <c r="B150" t="n">
-        <v>57948</v>
+        <v>58322</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -16213,7 +16213,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -16222,13 +16222,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464208</v>
+        <v>464198</v>
       </c>
       <c r="R150" t="n">
-        <v>6758043</v>
+        <v>6757876</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16284,10 +16284,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>132495072</v>
+        <v>132494061</v>
       </c>
       <c r="B151" t="n">
-        <v>91912</v>
+        <v>57948</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16295,30 +16295,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>464503</v>
+        <v>464479</v>
       </c>
       <c r="R151" t="n">
-        <v>6758035</v>
+        <v>6758007</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16377,53 +16386,44 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132491882</v>
+        <v>132495072</v>
       </c>
       <c r="B152" t="n">
-        <v>58322</v>
+        <v>91912</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>464198</v>
+        <v>464503</v>
       </c>
       <c r="R152" t="n">
-        <v>6757876</v>
+        <v>6758035</v>
       </c>
       <c r="S152" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16479,38 +16479,42 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>132494061</v>
+        <v>132493696</v>
       </c>
       <c r="B153" t="n">
-        <v>57948</v>
+        <v>99098</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -16519,10 +16523,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>464479</v>
+        <v>464446</v>
       </c>
       <c r="R153" t="n">
-        <v>6758007</v>
+        <v>6757982</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16581,7 +16585,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132495068</v>
+        <v>132492528</v>
       </c>
       <c r="B154" t="n">
         <v>57948</v>
@@ -16612,7 +16616,7 @@
       <c r="I154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -16621,10 +16625,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>464503</v>
+        <v>464273</v>
       </c>
       <c r="R154" t="n">
-        <v>6758035</v>
+        <v>6757909</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16657,11 +16661,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Flera bilder 3 till 4 meter upp,  ca 4 cm i diameter, 4 hål</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16688,54 +16687,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132493696</v>
+        <v>132499772</v>
       </c>
       <c r="B155" t="n">
-        <v>99098</v>
+        <v>79317</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>464446</v>
+        <v>464170</v>
       </c>
       <c r="R155" t="n">
-        <v>6757982</v>
+        <v>6758208</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16794,10 +16784,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132492528</v>
+        <v>132495224</v>
       </c>
       <c r="B156" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16805,39 +16795,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>464273</v>
+        <v>464514</v>
       </c>
       <c r="R156" t="n">
-        <v>6757909</v>
+        <v>6758053</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16896,10 +16881,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132499772</v>
+        <v>132493334</v>
       </c>
       <c r="B157" t="n">
-        <v>79317</v>
+        <v>92191</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16907,21 +16892,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16931,10 +16916,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>464170</v>
+        <v>464393</v>
       </c>
       <c r="R157" t="n">
-        <v>6758208</v>
+        <v>6757956</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16993,7 +16978,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132496448</v>
+        <v>132494856</v>
       </c>
       <c r="B158" t="n">
         <v>79317</v>
@@ -17028,10 +17013,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>464446</v>
+        <v>464490</v>
       </c>
       <c r="R158" t="n">
-        <v>6757993</v>
+        <v>6758002</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17064,11 +17049,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Garn vid kolarkoja samt kolbotten</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17095,10 +17075,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>132493334</v>
+        <v>132492586</v>
       </c>
       <c r="B159" t="n">
-        <v>92191</v>
+        <v>78983</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17106,21 +17086,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17130,10 +17110,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>464393</v>
+        <v>464278</v>
       </c>
       <c r="R159" t="n">
-        <v>6757956</v>
+        <v>6757899</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17192,10 +17172,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>132495224</v>
+        <v>132492923</v>
       </c>
       <c r="B160" t="n">
-        <v>79317</v>
+        <v>78983</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17203,21 +17183,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17227,10 +17207,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>464514</v>
+        <v>464335</v>
       </c>
       <c r="R160" t="n">
-        <v>6758053</v>
+        <v>6757949</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17289,7 +17269,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>132492586</v>
+        <v>132492370</v>
       </c>
       <c r="B161" t="n">
         <v>78983</v>
@@ -17324,13 +17304,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>464278</v>
+        <v>464208</v>
       </c>
       <c r="R161" t="n">
-        <v>6757899</v>
+        <v>6757880</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17357,11 +17337,26 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Silverstubbe</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -17370,48 +17365,63 @@
       </c>
       <c r="AG161" t="b">
         <v>0</v>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>132492923</v>
+        <v>132494783</v>
       </c>
       <c r="B162" t="n">
-        <v>78983</v>
+        <v>5199</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>353</v>
+        <v>105930</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17421,10 +17431,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>464335</v>
+        <v>464408</v>
       </c>
       <c r="R162" t="n">
-        <v>6757949</v>
+        <v>6757965</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17454,11 +17464,21 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AD162" t="b">
         <v>0</v>
       </c>
@@ -17467,48 +17487,68 @@
       </c>
       <c r="AG162" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>132494856</v>
+        <v>132498409</v>
       </c>
       <c r="B163" t="n">
-        <v>79317</v>
+        <v>75423</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17518,10 +17558,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>464490</v>
+        <v>464365</v>
       </c>
       <c r="R163" t="n">
-        <v>6758002</v>
+        <v>6758043</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17551,11 +17591,21 @@
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
@@ -17564,19 +17614,1132 @@
       </c>
       <c r="AG163" t="b">
         <v>0</v>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>132497842</v>
+      </c>
+      <c r="B164" t="n">
+        <v>78983</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>353</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>464365</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6758043</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>132492920</v>
+      </c>
+      <c r="B165" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>464335</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6757949</v>
+      </c>
+      <c r="S165" t="n">
+        <v>10</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
           <t>Håkan Thenander</t>
         </is>
       </c>
-      <c r="AX163" t="inlineStr">
+      <c r="AX165" t="inlineStr">
         <is>
           <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
-      <c r="AY163" t="inlineStr"/>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>132492743</v>
+      </c>
+      <c r="B166" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>464208</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6757880</v>
+      </c>
+      <c r="S166" t="n">
+        <v>5</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>På 2 lågor, rikligt</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>132498524</v>
+      </c>
+      <c r="B167" t="n">
+        <v>75423</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>464483</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6758068</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>132493203</v>
+      </c>
+      <c r="B168" t="n">
+        <v>92352</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>464208</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6757880</v>
+      </c>
+      <c r="S168" t="n">
+        <v>5</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>132495068</v>
+      </c>
+      <c r="B169" t="n">
+        <v>57948</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>464503</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6758035</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Flera bilder 3 till 4 meter upp,  ca 4 cm i diameter, 4 hål</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>132496448</v>
+      </c>
+      <c r="B170" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>464446</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6757993</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Garn vid kolarkoja samt kolbotten</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>132494915</v>
+      </c>
+      <c r="B171" t="n">
+        <v>79317</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>464483</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6758068</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>132494029</v>
+      </c>
+      <c r="B172" t="n">
+        <v>91892</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Hånåfljot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>464408</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6757965</v>
+      </c>
+      <c r="S172" t="n">
+        <v>10</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -8319,10 +8319,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131806068</v>
+        <v>131806038</v>
       </c>
       <c r="B76" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8330,39 +8330,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464196</v>
+        <v>464420</v>
       </c>
       <c r="R76" t="n">
-        <v>6757964</v>
+        <v>6758206</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8394,7 +8389,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8404,7 +8399,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8431,32 +8426,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131806038</v>
+        <v>131805988</v>
       </c>
       <c r="B77" t="n">
-        <v>79317</v>
+        <v>80451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8466,10 +8461,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464420</v>
+        <v>464189</v>
       </c>
       <c r="R77" t="n">
-        <v>6758206</v>
+        <v>6758149</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8501,7 +8496,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8511,7 +8506,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8522,6 +8517,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8538,45 +8548,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131805988</v>
+        <v>131806068</v>
       </c>
       <c r="B78" t="n">
-        <v>80451</v>
+        <v>57948</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464189</v>
+        <v>464196</v>
       </c>
       <c r="R78" t="n">
-        <v>6758149</v>
+        <v>6757964</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8608,7 +8623,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8618,7 +8633,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8629,21 +8644,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -11161,10 +11161,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131805978</v>
+        <v>131806058</v>
       </c>
       <c r="B102" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11172,34 +11172,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464275</v>
+        <v>464435</v>
       </c>
       <c r="R102" t="n">
-        <v>6758069</v>
+        <v>6758156</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11231,7 +11236,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11241,7 +11246,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11268,45 +11273,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131806036</v>
+        <v>131806067</v>
       </c>
       <c r="B103" t="n">
-        <v>79317</v>
+        <v>5179</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464459</v>
+        <v>464196</v>
       </c>
       <c r="R103" t="n">
-        <v>6758165</v>
+        <v>6757964</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11338,7 +11348,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11348,7 +11358,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11375,32 +11385,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131806003</v>
+        <v>131805978</v>
       </c>
       <c r="B104" t="n">
-        <v>80458</v>
+        <v>91892</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11410,10 +11420,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464137</v>
+        <v>464275</v>
       </c>
       <c r="R104" t="n">
-        <v>6758186</v>
+        <v>6758069</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11445,7 +11455,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11455,7 +11465,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11466,21 +11476,6 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -11497,10 +11492,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806058</v>
+        <v>131806036</v>
       </c>
       <c r="B105" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11508,39 +11503,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464435</v>
+        <v>464459</v>
       </c>
       <c r="R105" t="n">
-        <v>6758156</v>
+        <v>6758165</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11572,7 +11562,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11582,7 +11572,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11609,10 +11599,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806067</v>
+        <v>131806003</v>
       </c>
       <c r="B106" t="n">
-        <v>5179</v>
+        <v>80458</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11620,39 +11610,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100526</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464196</v>
+        <v>464137</v>
       </c>
       <c r="R106" t="n">
-        <v>6757964</v>
+        <v>6758186</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11684,7 +11669,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11694,7 +11679,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11705,6 +11690,21 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -8319,10 +8319,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131806038</v>
+        <v>131806068</v>
       </c>
       <c r="B76" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8330,34 +8330,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464420</v>
+        <v>464196</v>
       </c>
       <c r="R76" t="n">
-        <v>6758206</v>
+        <v>6757964</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8389,7 +8394,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8399,7 +8404,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8426,32 +8431,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131805988</v>
+        <v>131806038</v>
       </c>
       <c r="B77" t="n">
-        <v>80451</v>
+        <v>79317</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8461,10 +8466,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464189</v>
+        <v>464420</v>
       </c>
       <c r="R77" t="n">
-        <v>6758149</v>
+        <v>6758206</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8496,7 +8501,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8506,7 +8511,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8517,21 +8522,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8548,50 +8538,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131806068</v>
+        <v>131805988</v>
       </c>
       <c r="B78" t="n">
-        <v>57948</v>
+        <v>80451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464196</v>
+        <v>464189</v>
       </c>
       <c r="R78" t="n">
-        <v>6757964</v>
+        <v>6758149</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8623,7 +8608,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8633,7 +8618,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8644,6 +8629,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -10402,10 +10402,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131806032</v>
+        <v>131806052</v>
       </c>
       <c r="B95" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,34 +10413,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>464341</v>
+        <v>464193</v>
       </c>
       <c r="R95" t="n">
-        <v>6757956</v>
+        <v>6757936</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,7 +10477,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10482,7 +10487,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10509,7 +10514,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131806030</v>
+        <v>131806032</v>
       </c>
       <c r="B96" t="n">
         <v>79317</v>
@@ -10544,10 +10549,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464204</v>
+        <v>464341</v>
       </c>
       <c r="R96" t="n">
-        <v>6758031</v>
+        <v>6757956</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10579,7 +10584,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10589,7 +10594,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10616,32 +10621,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131805972</v>
+        <v>131806030</v>
       </c>
       <c r="B97" t="n">
-        <v>91855</v>
+        <v>79317</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10651,10 +10656,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464074</v>
+        <v>464204</v>
       </c>
       <c r="R97" t="n">
-        <v>6758064</v>
+        <v>6758031</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10686,7 +10691,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10696,7 +10701,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10723,50 +10728,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131806052</v>
+        <v>131805972</v>
       </c>
       <c r="B98" t="n">
-        <v>57948</v>
+        <v>91855</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464193</v>
+        <v>464074</v>
       </c>
       <c r="R98" t="n">
-        <v>6757936</v>
+        <v>6758064</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10835,10 +10835,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131806000</v>
+        <v>131806002</v>
       </c>
       <c r="B99" t="n">
-        <v>57780</v>
+        <v>79341</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10846,39 +10846,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102622</v>
+        <v>6434</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>464154</v>
+        <v>464113</v>
       </c>
       <c r="R99" t="n">
-        <v>6758193</v>
+        <v>6757861</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10910,7 +10905,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10920,7 +10915,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10947,10 +10942,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131806002</v>
+        <v>131806000</v>
       </c>
       <c r="B100" t="n">
-        <v>79341</v>
+        <v>57780</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10958,34 +10953,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6434</v>
+        <v>102622</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>464113</v>
+        <v>464154</v>
       </c>
       <c r="R100" t="n">
-        <v>6757861</v>
+        <v>6758193</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11161,10 +11161,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131806058</v>
+        <v>131805978</v>
       </c>
       <c r="B102" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11172,39 +11172,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>464435</v>
+        <v>464275</v>
       </c>
       <c r="R102" t="n">
-        <v>6758156</v>
+        <v>6758069</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11236,7 +11231,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11246,7 +11241,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11273,50 +11268,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131806067</v>
+        <v>131806036</v>
       </c>
       <c r="B103" t="n">
-        <v>5179</v>
+        <v>79317</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>464196</v>
+        <v>464459</v>
       </c>
       <c r="R103" t="n">
-        <v>6757964</v>
+        <v>6758165</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11348,7 +11338,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11358,7 +11348,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11385,32 +11375,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131805978</v>
+        <v>131806003</v>
       </c>
       <c r="B104" t="n">
-        <v>91892</v>
+        <v>80458</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11420,10 +11410,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>464275</v>
+        <v>464137</v>
       </c>
       <c r="R104" t="n">
-        <v>6758069</v>
+        <v>6758186</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11455,7 +11445,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11465,7 +11455,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11476,6 +11466,21 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -11492,10 +11497,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131806036</v>
+        <v>131806058</v>
       </c>
       <c r="B105" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11503,34 +11508,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>464459</v>
+        <v>464435</v>
       </c>
       <c r="R105" t="n">
-        <v>6758165</v>
+        <v>6758156</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11562,7 +11572,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11572,7 +11582,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11599,10 +11609,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131806003</v>
+        <v>131806067</v>
       </c>
       <c r="B106" t="n">
-        <v>80458</v>
+        <v>5179</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11610,34 +11620,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>100526</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fulåberg, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>464137</v>
+        <v>464196</v>
       </c>
       <c r="R106" t="n">
-        <v>6758186</v>
+        <v>6757964</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11669,7 +11684,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11679,7 +11694,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11690,21 +11705,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">

--- a/artfynd/A 2729-2026 artfynd.xlsx
+++ b/artfynd/A 2729-2026 artfynd.xlsx
@@ -13373,7 +13373,7 @@
         <v>131806069</v>
       </c>
       <c r="B122" t="n">
-        <v>91845</v>
+        <v>91851</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>132491919</v>
       </c>
       <c r="B123" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>132496183</v>
       </c>
       <c r="B124" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>132496342</v>
       </c>
       <c r="B125" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>132497836</v>
       </c>
       <c r="B126" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>132494581</v>
       </c>
       <c r="B127" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>132492205</v>
       </c>
       <c r="B128" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>132494714</v>
       </c>
       <c r="B129" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14198,32 +14198,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132499966</v>
+        <v>132495215</v>
       </c>
       <c r="B130" t="n">
-        <v>80451</v>
+        <v>83299</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14233,10 +14233,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>464137</v>
+        <v>464514</v>
       </c>
       <c r="R130" t="n">
-        <v>6758183</v>
+        <v>6758053</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14295,32 +14295,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>132495215</v>
+        <v>132499966</v>
       </c>
       <c r="B131" t="n">
-        <v>83297</v>
+        <v>80453</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14330,10 +14330,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>464514</v>
+        <v>464137</v>
       </c>
       <c r="R131" t="n">
-        <v>6758053</v>
+        <v>6758183</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14395,7 +14395,7 @@
         <v>132492755</v>
       </c>
       <c r="B132" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>132499020</v>
       </c>
       <c r="B133" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>132499761</v>
       </c>
       <c r="B134" t="n">
-        <v>92352</v>
+        <v>92358</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>132492041</v>
       </c>
       <c r="B135" t="n">
-        <v>81302</v>
+        <v>81304</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>132492033</v>
       </c>
       <c r="B136" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>132498299</v>
       </c>
       <c r="B137" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14993,10 +14993,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>132498302</v>
+        <v>132495919</v>
       </c>
       <c r="B138" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15004,34 +15004,39 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>464310</v>
+        <v>464458</v>
       </c>
       <c r="R138" t="n">
-        <v>6758158</v>
+        <v>6758060</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15090,45 +15095,50 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>132499976</v>
+        <v>132498371</v>
       </c>
       <c r="B139" t="n">
-        <v>80382</v>
+        <v>57949</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>464137</v>
+        <v>464292</v>
       </c>
       <c r="R139" t="n">
-        <v>6758183</v>
+        <v>6758119</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15187,10 +15197,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>132495276</v>
+        <v>132498302</v>
       </c>
       <c r="B140" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15222,10 +15232,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>464505</v>
+        <v>464310</v>
       </c>
       <c r="R140" t="n">
-        <v>6758076</v>
+        <v>6758158</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15284,10 +15294,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>132495919</v>
+        <v>132495276</v>
       </c>
       <c r="B141" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15295,39 +15305,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>464458</v>
+        <v>464505</v>
       </c>
       <c r="R141" t="n">
-        <v>6758060</v>
+        <v>6758076</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15386,50 +15391,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132498371</v>
+        <v>132499976</v>
       </c>
       <c r="B142" t="n">
-        <v>57948</v>
+        <v>80384</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>464292</v>
+        <v>464137</v>
       </c>
       <c r="R142" t="n">
-        <v>6758119</v>
+        <v>6758183</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15491,7 +15491,7 @@
         <v>132497843</v>
       </c>
       <c r="B143" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>132495930</v>
       </c>
       <c r="B144" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>132494801</v>
       </c>
       <c r="B145" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>132492565</v>
       </c>
       <c r="B146" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>132493028</v>
       </c>
       <c r="B147" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>132493206</v>
       </c>
       <c r="B148" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132499106</v>
+        <v>132495072</v>
       </c>
       <c r="B149" t="n">
-        <v>57948</v>
+        <v>91918</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16091,39 +16091,30 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>464208</v>
+        <v>464503</v>
       </c>
       <c r="R149" t="n">
-        <v>6758043</v>
+        <v>6758035</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16182,27 +16173,27 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132491882</v>
+        <v>132499106</v>
       </c>
       <c r="B150" t="n">
-        <v>58322</v>
+        <v>57949</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -16213,7 +16204,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -16222,13 +16213,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>464198</v>
+        <v>464208</v>
       </c>
       <c r="R150" t="n">
-        <v>6757876</v>
+        <v>6758043</v>
       </c>
       <c r="S150" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16287,7 +16278,7 @@
         <v>132494061</v>
       </c>
       <c r="B151" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16386,44 +16377,53 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>132495072</v>
+        <v>132491882</v>
       </c>
       <c r="B152" t="n">
-        <v>91912</v>
+        <v>58323</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr"/>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>464503</v>
+        <v>464198</v>
       </c>
       <c r="R152" t="n">
-        <v>6758035</v>
+        <v>6757876</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>132493696</v>
       </c>
       <c r="B153" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16585,10 +16585,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>132492528</v>
+        <v>132499772</v>
       </c>
       <c r="B154" t="n">
-        <v>57948</v>
+        <v>79319</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16596,39 +16596,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>464273</v>
+        <v>464170</v>
       </c>
       <c r="R154" t="n">
-        <v>6757909</v>
+        <v>6758208</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16687,10 +16682,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>132499772</v>
+        <v>132492528</v>
       </c>
       <c r="B155" t="n">
-        <v>79317</v>
+        <v>57949</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16698,34 +16693,39 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Hånåfljot, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>464170</v>
+        <v>464273</v>
       </c>
       <c r="R155" t="n">
-        <v>6758208</v>
+        <v>6757909</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16784,10 +16784,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>132495224</v>
+        <v>132493334</v>
       </c>
       <c r="B156" t="n">
-        <v>79317</v>
+        <v>92197</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16795,21 +16795,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16819,10 +16819,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>464514</v>
+        <v>464393</v>
       </c>
       <c r="R156" t="n">
-        <v>6758053</v>
+        <v>6757956</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16881,10 +16881,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>132493334</v>
+        <v>132492586</v>
       </c>
       <c r="B157" t="n">
-        <v>92191</v>
+        <v>78985</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16892,21 +16892,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16916,10 +16916,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>464393</v>
+        <v>464278</v>
       </c>
       <c r="R157" t="n">
-        <v>6757956</v>
+        <v>6757899</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16978,10 +16978,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>132494856</v>
+        <v>132492923</v>
       </c>
       <c r="B158" t="n">
-        <v>79317</v>
+        <v>78985</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16989,21 +1